--- a/output/2024-04-02.xlsx
+++ b/output/2024-04-02.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.24</v>
+        <v>3.56</v>
       </c>
       <c r="F14" t="n">
-        <v>8.220000000000001</v>
+        <v>9.51</v>
       </c>
       <c r="G14" t="n">
-        <v>178.8</v>
+        <v>169.8</v>
       </c>
       <c r="H14" t="n">
-        <v>94.59999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-35.2</v>
+        <v>18.87</v>
       </c>
       <c r="K14" t="n">
-        <v>-171.27</v>
+        <v>111.19</v>
       </c>
       <c r="L14" t="n">
-        <v>174.85</v>
+        <v>112.78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:43:00</t>
+          <t>06:43:24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="F15" t="n">
-        <v>9.050000000000001</v>
+        <v>9.34</v>
       </c>
       <c r="G15" t="n">
-        <v>163.7</v>
+        <v>167</v>
       </c>
       <c r="H15" t="n">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>-110.45</v>
+        <v>-45.49</v>
       </c>
       <c r="K15" t="n">
-        <v>-9.32</v>
+        <v>90.34</v>
       </c>
       <c r="L15" t="n">
-        <v>110.84</v>
+        <v>101.15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:45:20</t>
+          <t>06:44:42</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.58</v>
+        <v>3.16</v>
       </c>
       <c r="F16" t="n">
-        <v>9.369999999999999</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>169.9</v>
+        <v>163</v>
       </c>
       <c r="H16" t="n">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>60.73</v>
+        <v>-132.14</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.7</v>
+        <v>3.89</v>
       </c>
       <c r="L16" t="n">
-        <v>60.91</v>
+        <v>132.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:50:28</t>
+          <t>06:50:06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.67</v>
+        <v>2.99</v>
       </c>
       <c r="F17" t="n">
-        <v>9.81</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>165.9</v>
+        <v>169.5</v>
       </c>
       <c r="H17" t="n">
-        <v>97.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>234.48</v>
+        <v>-286.7</v>
       </c>
       <c r="K17" t="n">
-        <v>243.56</v>
+        <v>-54.66</v>
       </c>
       <c r="L17" t="n">
-        <v>338.09</v>
+        <v>291.87</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:52:12</t>
+          <t>06:51:20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.72</v>
+        <v>2.43</v>
       </c>
       <c r="F18" t="n">
-        <v>8.67</v>
+        <v>9.68</v>
       </c>
       <c r="G18" t="n">
-        <v>158.5</v>
+        <v>175.4</v>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-80.62</v>
+        <v>-68.56</v>
       </c>
       <c r="K18" t="n">
-        <v>-87.34999999999999</v>
+        <v>62.69</v>
       </c>
       <c r="L18" t="n">
-        <v>118.87</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:54:34</t>
+          <t>06:52:05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="F19" t="n">
-        <v>9</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>174.1</v>
+        <v>173.4</v>
       </c>
       <c r="H19" t="n">
-        <v>95.8</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-194.62</v>
+        <v>122.96</v>
       </c>
       <c r="K19" t="n">
-        <v>-267.85</v>
+        <v>83.34</v>
       </c>
       <c r="L19" t="n">
-        <v>331.09</v>
+        <v>148.54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:59:18</t>
+          <t>06:58:10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.44</v>
+        <v>3.13</v>
       </c>
       <c r="F20" t="n">
-        <v>9.720000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="G20" t="n">
-        <v>166.6</v>
+        <v>162.7</v>
       </c>
       <c r="H20" t="n">
-        <v>99.90000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>108.58</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>131.23</v>
+        <v>-267.85</v>
       </c>
       <c r="L20" t="n">
-        <v>170.33</v>
+        <v>283.79</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>07:00:03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="F21" t="n">
-        <v>8.73</v>
+        <v>9.26</v>
       </c>
       <c r="G21" t="n">
-        <v>158</v>
+        <v>178.8</v>
       </c>
       <c r="H21" t="n">
-        <v>92.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>42.85</v>
+        <v>33.79</v>
       </c>
       <c r="K21" t="n">
-        <v>-158.45</v>
+        <v>104.17</v>
       </c>
       <c r="L21" t="n">
-        <v>164.14</v>
+        <v>109.51</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:02:28</t>
+          <t>07:02:10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.13</v>
+        <v>3.07</v>
       </c>
       <c r="F22" t="n">
-        <v>9.710000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="G22" t="n">
-        <v>179.4</v>
+        <v>176.1</v>
       </c>
       <c r="H22" t="n">
-        <v>97.09999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="I22" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>243.94</v>
+        <v>-281.28</v>
       </c>
       <c r="K22" t="n">
-        <v>8.33</v>
+        <v>100.09</v>
       </c>
       <c r="L22" t="n">
-        <v>244.08</v>
+        <v>298.56</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:07:58</t>
+          <t>07:07:32</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.02</v>
+        <v>3.56</v>
       </c>
       <c r="F23" t="n">
-        <v>9.81</v>
+        <v>8.56</v>
       </c>
       <c r="G23" t="n">
-        <v>174.7</v>
+        <v>165.2</v>
       </c>
       <c r="H23" t="n">
-        <v>88.40000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-187.82</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>225.25</v>
+        <v>354.73</v>
       </c>
       <c r="L23" t="n">
-        <v>293.28</v>
+        <v>363.09</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:09:27</t>
+          <t>07:09:35</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.13</v>
+        <v>3.97</v>
       </c>
       <c r="F24" t="n">
-        <v>9.24</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="H24" t="n">
-        <v>92.7</v>
+        <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>-44.28</v>
+        <v>69.62</v>
       </c>
       <c r="K24" t="n">
-        <v>-270.8</v>
+        <v>-25.94</v>
       </c>
       <c r="L24" t="n">
-        <v>274.4</v>
+        <v>74.29000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:10:48</t>
+          <t>07:10:45</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.34</v>
+        <v>3.03</v>
       </c>
       <c r="F25" t="n">
-        <v>9.050000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>178.6</v>
+        <v>164.8</v>
       </c>
       <c r="H25" t="n">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-206.74</v>
+        <v>228.74</v>
       </c>
       <c r="K25" t="n">
-        <v>530.29</v>
+        <v>20.09</v>
       </c>
       <c r="L25" t="n">
-        <v>569.17</v>
+        <v>229.62</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:15:25</t>
+          <t>07:16:14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.16</v>
+        <v>2.98</v>
       </c>
       <c r="F26" t="n">
-        <v>9.52</v>
+        <v>9.4</v>
       </c>
       <c r="G26" t="n">
-        <v>150.9</v>
+        <v>179.6</v>
       </c>
       <c r="H26" t="n">
-        <v>85.90000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="I26" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.56</v>
+        <v>428.19</v>
       </c>
       <c r="K26" t="n">
-        <v>788.86</v>
+        <v>338.77</v>
       </c>
       <c r="L26" t="n">
-        <v>788.87</v>
+        <v>545.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:17:11</t>
+          <t>07:17:43</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="F27" t="n">
-        <v>9.300000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="G27" t="n">
-        <v>150</v>
+        <v>172.6</v>
       </c>
       <c r="H27" t="n">
-        <v>93</v>
+        <v>90.2</v>
       </c>
       <c r="I27" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-481.19</v>
+        <v>531.8200000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>-390.36</v>
+        <v>271.43</v>
       </c>
       <c r="L27" t="n">
-        <v>619.62</v>
+        <v>597.08</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:18:35</t>
+          <t>07:18:43</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.2</v>
+        <v>3.62</v>
       </c>
       <c r="F28" t="n">
-        <v>9.5</v>
+        <v>9.24</v>
       </c>
       <c r="G28" t="n">
-        <v>171.9</v>
+        <v>165.1</v>
       </c>
       <c r="H28" t="n">
-        <v>84.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>431.36</v>
+        <v>478.14</v>
       </c>
       <c r="K28" t="n">
-        <v>-1100.84</v>
+        <v>-216.27</v>
       </c>
       <c r="L28" t="n">
-        <v>1182.34</v>
+        <v>524.78</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:27:56</t>
+          <t>07:30:48</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.11</v>
+        <v>3.33</v>
       </c>
       <c r="F29" t="n">
-        <v>9.43</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>170.2</v>
+        <v>161</v>
       </c>
       <c r="H29" t="n">
-        <v>91.90000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-141.91</v>
+        <v>-32.08</v>
       </c>
       <c r="K29" t="n">
-        <v>114.61</v>
+        <v>213.94</v>
       </c>
       <c r="L29" t="n">
-        <v>182.41</v>
+        <v>216.33</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:29:12</t>
+          <t>07:32:16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="F30" t="n">
-        <v>9.289999999999999</v>
+        <v>9.09</v>
       </c>
       <c r="G30" t="n">
-        <v>154.5</v>
+        <v>159.8</v>
       </c>
       <c r="H30" t="n">
-        <v>94.5</v>
+        <v>86.2</v>
       </c>
       <c r="I30" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.47</v>
+        <v>180.22</v>
       </c>
       <c r="K30" t="n">
-        <v>63.87</v>
+        <v>-24.26</v>
       </c>
       <c r="L30" t="n">
-        <v>64.72</v>
+        <v>181.84</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:31:07</t>
+          <t>07:33:58</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.67</v>
+        <v>3.62</v>
       </c>
       <c r="F31" t="n">
-        <v>9.94</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>170.3</v>
+        <v>167</v>
       </c>
       <c r="H31" t="n">
-        <v>95.7</v>
+        <v>94.2</v>
       </c>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-17.51</v>
+        <v>-265.61</v>
       </c>
       <c r="K31" t="n">
-        <v>-64.36</v>
+        <v>-75.76000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>66.7</v>
+        <v>276.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:34:24</t>
+          <t>07:39:42</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.09</v>
+        <v>3.26</v>
       </c>
       <c r="F32" t="n">
-        <v>9.33</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>185.5</v>
+        <v>163.9</v>
       </c>
       <c r="H32" t="n">
-        <v>90.5</v>
+        <v>96.5</v>
       </c>
       <c r="I32" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-32.56</v>
+        <v>27.48</v>
       </c>
       <c r="K32" t="n">
-        <v>87.03</v>
+        <v>130.1</v>
       </c>
       <c r="L32" t="n">
-        <v>92.93000000000001</v>
+        <v>132.97</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:36:52</t>
+          <t>07:40:49</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.87</v>
+        <v>3.34</v>
       </c>
       <c r="F33" t="n">
-        <v>9.050000000000001</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>170.7</v>
+        <v>167</v>
       </c>
       <c r="H33" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-53.51</v>
+        <v>-206.69</v>
       </c>
       <c r="K33" t="n">
-        <v>121.22</v>
+        <v>-180.08</v>
       </c>
       <c r="L33" t="n">
-        <v>132.5</v>
+        <v>274.13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:38:01</t>
+          <t>07:42:11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.74</v>
+        <v>3.16</v>
       </c>
       <c r="F34" t="n">
-        <v>8.75</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>170</v>
+        <v>159.1</v>
       </c>
       <c r="H34" t="n">
-        <v>93.09999999999999</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-189.62</v>
+        <v>242.72</v>
       </c>
       <c r="K34" t="n">
-        <v>114.26</v>
+        <v>-59.9</v>
       </c>
       <c r="L34" t="n">
-        <v>221.38</v>
+        <v>250</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:41:21</t>
+          <t>07:46:46</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.38</v>
+        <v>3.18</v>
       </c>
       <c r="F35" t="n">
-        <v>9.27</v>
+        <v>9.17</v>
       </c>
       <c r="G35" t="n">
-        <v>171.4</v>
+        <v>159</v>
       </c>
       <c r="H35" t="n">
-        <v>96.09999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-632.96</v>
+        <v>-170.4</v>
       </c>
       <c r="K35" t="n">
-        <v>-58.72</v>
+        <v>17.54</v>
       </c>
       <c r="L35" t="n">
-        <v>635.6799999999999</v>
+        <v>171.3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:42:55</t>
+          <t>07:49:09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="F36" t="n">
-        <v>8.77</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>177</v>
+        <v>173.8</v>
       </c>
       <c r="H36" t="n">
-        <v>95</v>
+        <v>89.3</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>327.64</v>
+        <v>-0.34</v>
       </c>
       <c r="K36" t="n">
-        <v>-132.49</v>
+        <v>-314.14</v>
       </c>
       <c r="L36" t="n">
-        <v>353.42</v>
+        <v>314.14</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:45:02</t>
+          <t>07:50:24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.41</v>
+        <v>3.21</v>
       </c>
       <c r="F37" t="n">
-        <v>9.43</v>
+        <v>9.6</v>
       </c>
       <c r="G37" t="n">
-        <v>165.5</v>
+        <v>179.3</v>
       </c>
       <c r="H37" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-33.64</v>
+        <v>143.71</v>
       </c>
       <c r="K37" t="n">
-        <v>-119.12</v>
+        <v>354.89</v>
       </c>
       <c r="L37" t="n">
-        <v>123.78</v>
+        <v>382.88</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:50:33</t>
+          <t>07:54:59</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.13</v>
+        <v>3.89</v>
       </c>
       <c r="F38" t="n">
-        <v>9.199999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>172.2</v>
+        <v>178.9</v>
       </c>
       <c r="H38" t="n">
-        <v>95.59999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-478.81</v>
+        <v>-186.48</v>
       </c>
       <c r="K38" t="n">
-        <v>412.76</v>
+        <v>106.7</v>
       </c>
       <c r="L38" t="n">
-        <v>632.17</v>
+        <v>214.85</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:52:03</t>
+          <t>07:56:17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.71</v>
+        <v>3.29</v>
       </c>
       <c r="F39" t="n">
-        <v>9.210000000000001</v>
+        <v>10.11</v>
       </c>
       <c r="G39" t="n">
-        <v>174.8</v>
+        <v>160</v>
       </c>
       <c r="H39" t="n">
-        <v>98.59999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>460.02</v>
+        <v>276.16</v>
       </c>
       <c r="K39" t="n">
-        <v>65.31</v>
+        <v>-179.45</v>
       </c>
       <c r="L39" t="n">
-        <v>464.63</v>
+        <v>329.35</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:53:58</t>
+          <t>07:57:46</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.04</v>
+        <v>3.27</v>
       </c>
       <c r="F40" t="n">
-        <v>9.5</v>
+        <v>8.48</v>
       </c>
       <c r="G40" t="n">
-        <v>172.2</v>
+        <v>156</v>
       </c>
       <c r="H40" t="n">
-        <v>98.3</v>
+        <v>84</v>
       </c>
       <c r="I40" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-529.79</v>
+        <v>-316.52</v>
       </c>
       <c r="K40" t="n">
-        <v>60.07</v>
+        <v>335.41</v>
       </c>
       <c r="L40" t="n">
-        <v>533.1900000000001</v>
+        <v>461.17</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:59:24</t>
+          <t>08:01:59</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="F41" t="n">
-        <v>8.93</v>
+        <v>9.41</v>
       </c>
       <c r="G41" t="n">
-        <v>176</v>
+        <v>159.8</v>
       </c>
       <c r="H41" t="n">
-        <v>89.59999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>-83.02</v>
+        <v>-218.49</v>
       </c>
       <c r="K41" t="n">
-        <v>139.55</v>
+        <v>170.44</v>
       </c>
       <c r="L41" t="n">
-        <v>162.37</v>
+        <v>277.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:00:08</t>
+          <t>08:03:41</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.02</v>
+        <v>3.51</v>
       </c>
       <c r="F42" t="n">
-        <v>9.07</v>
+        <v>9.23</v>
       </c>
       <c r="G42" t="n">
-        <v>162.3</v>
+        <v>157.5</v>
       </c>
       <c r="H42" t="n">
-        <v>93.40000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>571.53</v>
+        <v>-315.33</v>
       </c>
       <c r="K42" t="n">
-        <v>-53.86</v>
+        <v>-57.76</v>
       </c>
       <c r="L42" t="n">
-        <v>574.0599999999999</v>
+        <v>320.58</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:02:32</t>
+          <t>08:04:34</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.02</v>
+        <v>3.52</v>
       </c>
       <c r="F43" t="n">
-        <v>8.91</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>174.7</v>
+        <v>159</v>
       </c>
       <c r="H43" t="n">
-        <v>96</v>
+        <v>99.7</v>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>25.34</v>
+        <v>418.03</v>
       </c>
       <c r="K43" t="n">
-        <v>-494.29</v>
+        <v>-35.42</v>
       </c>
       <c r="L43" t="n">
-        <v>494.94</v>
+        <v>419.53</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:15:09</t>
+          <t>08:17:11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.99</v>
+        <v>3.27</v>
       </c>
       <c r="F44" t="n">
-        <v>9.65</v>
+        <v>9.59</v>
       </c>
       <c r="G44" t="n">
-        <v>167.9</v>
+        <v>154.5</v>
       </c>
       <c r="H44" t="n">
-        <v>87.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-29.29</v>
+        <v>-111.2</v>
       </c>
       <c r="K44" t="n">
-        <v>221.71</v>
+        <v>39.61</v>
       </c>
       <c r="L44" t="n">
-        <v>223.64</v>
+        <v>118.04</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:16:58</t>
+          <t>08:19:42</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.96</v>
+        <v>3.19</v>
       </c>
       <c r="F45" t="n">
-        <v>9.25</v>
+        <v>9.01</v>
       </c>
       <c r="G45" t="n">
-        <v>171.5</v>
+        <v>180.9</v>
       </c>
       <c r="H45" t="n">
-        <v>96.40000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>96.92</v>
+        <v>11.73</v>
       </c>
       <c r="K45" t="n">
-        <v>-149.54</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>178.2</v>
+        <v>94.06</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:18:47</t>
+          <t>08:21:39</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="F46" t="n">
-        <v>8.949999999999999</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>166.8</v>
+        <v>160.3</v>
       </c>
       <c r="H46" t="n">
-        <v>92.09999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>35.83</v>
+        <v>74.67</v>
       </c>
       <c r="K46" t="n">
-        <v>-141.56</v>
+        <v>187.91</v>
       </c>
       <c r="L46" t="n">
-        <v>146.02</v>
+        <v>202.21</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:24:09</t>
+          <t>08:25:34</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.63</v>
+        <v>3.85</v>
       </c>
       <c r="F47" t="n">
-        <v>9.33</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>177.6</v>
+        <v>167.2</v>
       </c>
       <c r="H47" t="n">
         <v>92.09999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-2.93</v>
+        <v>80.42</v>
       </c>
       <c r="K47" t="n">
-        <v>305.39</v>
+        <v>-56.79</v>
       </c>
       <c r="L47" t="n">
-        <v>305.4</v>
+        <v>98.45</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:26:25</t>
+          <t>08:26:43</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.46</v>
+        <v>3.78</v>
       </c>
       <c r="F48" t="n">
-        <v>8.4</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>174.2</v>
+        <v>173.4</v>
       </c>
       <c r="H48" t="n">
-        <v>96.8</v>
+        <v>86.5</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>192.39</v>
+        <v>-198.17</v>
       </c>
       <c r="K48" t="n">
-        <v>-51.38</v>
+        <v>-10.42</v>
       </c>
       <c r="L48" t="n">
-        <v>199.13</v>
+        <v>198.45</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:28:23</t>
+          <t>08:28:25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.86</v>
+        <v>4.02</v>
       </c>
       <c r="F49" t="n">
-        <v>9.029999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="G49" t="n">
-        <v>165.5</v>
+        <v>163.8</v>
       </c>
       <c r="H49" t="n">
-        <v>93.7</v>
+        <v>92.8</v>
       </c>
       <c r="I49" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-283.88</v>
+        <v>153.13</v>
       </c>
       <c r="K49" t="n">
-        <v>83.04000000000001</v>
+        <v>-289.25</v>
       </c>
       <c r="L49" t="n">
-        <v>295.77</v>
+        <v>327.28</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:33:17</t>
+          <t>08:31:51</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.61</v>
+        <v>3.25</v>
       </c>
       <c r="F50" t="n">
-        <v>10</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>157.7</v>
+        <v>167.4</v>
       </c>
       <c r="H50" t="n">
-        <v>98.5</v>
+        <v>90.7</v>
       </c>
       <c r="I50" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-209</v>
+        <v>181.34</v>
       </c>
       <c r="K50" t="n">
-        <v>334.99</v>
+        <v>-77.39</v>
       </c>
       <c r="L50" t="n">
-        <v>394.84</v>
+        <v>197.16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:34:37</t>
+          <t>08:34:19</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.38</v>
+        <v>2.72</v>
       </c>
       <c r="F51" t="n">
-        <v>9.109999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="G51" t="n">
-        <v>177.9</v>
+        <v>164.2</v>
       </c>
       <c r="H51" t="n">
-        <v>94.2</v>
+        <v>83.5</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>83.92</v>
+        <v>-122.4</v>
       </c>
       <c r="K51" t="n">
-        <v>-364.13</v>
+        <v>63.27</v>
       </c>
       <c r="L51" t="n">
-        <v>373.68</v>
+        <v>137.78</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:35:44</t>
+          <t>08:36:14</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.24</v>
+        <v>3.62</v>
       </c>
       <c r="F52" t="n">
-        <v>8.949999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="H52" t="n">
-        <v>93.09999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="I52" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-24.74</v>
+        <v>-179.05</v>
       </c>
       <c r="K52" t="n">
-        <v>-82.56999999999999</v>
+        <v>-155.86</v>
       </c>
       <c r="L52" t="n">
-        <v>86.19</v>
+        <v>237.38</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:40:21</t>
+          <t>08:40:43</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.51</v>
+        <v>3.47</v>
       </c>
       <c r="F53" t="n">
-        <v>8.73</v>
+        <v>8.56</v>
       </c>
       <c r="G53" t="n">
-        <v>161.9</v>
+        <v>169.3</v>
       </c>
       <c r="H53" t="n">
-        <v>90.8</v>
+        <v>98.5</v>
       </c>
       <c r="I53" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>19.72</v>
+        <v>226.46</v>
       </c>
       <c r="K53" t="n">
-        <v>-95.22</v>
+        <v>-592.5599999999999</v>
       </c>
       <c r="L53" t="n">
-        <v>97.23999999999999</v>
+        <v>634.36</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:42:52</t>
+          <t>08:42:34</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.58</v>
+        <v>3.16</v>
       </c>
       <c r="F54" t="n">
-        <v>9.210000000000001</v>
+        <v>9.94</v>
       </c>
       <c r="G54" t="n">
-        <v>156.9</v>
+        <v>170.3</v>
       </c>
       <c r="H54" t="n">
-        <v>88.8</v>
+        <v>95.7</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>347.47</v>
+        <v>183.35</v>
       </c>
       <c r="K54" t="n">
-        <v>-44.65</v>
+        <v>702.4299999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>350.33</v>
+        <v>725.97</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:43:33</t>
+          <t>08:44:55</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.64</v>
+        <v>3.42</v>
       </c>
       <c r="F55" t="n">
-        <v>9.58</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>148.2</v>
+        <v>162.8</v>
       </c>
       <c r="H55" t="n">
-        <v>88.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-475.31</v>
+        <v>116.76</v>
       </c>
       <c r="K55" t="n">
-        <v>-81.69</v>
+        <v>-273.45</v>
       </c>
       <c r="L55" t="n">
-        <v>482.28</v>
+        <v>297.34</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:48:57</t>
+          <t>08:49:31</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.28</v>
+        <v>3.77</v>
       </c>
       <c r="F56" t="n">
-        <v>9.300000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="G56" t="n">
-        <v>169.6</v>
+        <v>171.5</v>
       </c>
       <c r="H56" t="n">
-        <v>96.40000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>421.58</v>
+        <v>299.28</v>
       </c>
       <c r="K56" t="n">
-        <v>491.29</v>
+        <v>690.75</v>
       </c>
       <c r="L56" t="n">
-        <v>647.37</v>
+        <v>752.8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:49:59</t>
+          <t>08:51:43</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.08</v>
+        <v>3.64</v>
       </c>
       <c r="F57" t="n">
-        <v>9.109999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>168.6</v>
+        <v>165</v>
       </c>
       <c r="H57" t="n">
-        <v>96.59999999999999</v>
+        <v>93</v>
       </c>
       <c r="I57" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-10.62</v>
+        <v>-709.97</v>
       </c>
       <c r="K57" t="n">
-        <v>24.23</v>
+        <v>289.95</v>
       </c>
       <c r="L57" t="n">
-        <v>26.45</v>
+        <v>766.9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:50:49</t>
+          <t>08:53:23</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="F58" t="n">
-        <v>9.33</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>152.8</v>
+        <v>177.6</v>
       </c>
       <c r="H58" t="n">
-        <v>100</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>309.54</v>
+        <v>-531.4400000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>459</v>
+        <v>233.29</v>
       </c>
       <c r="L58" t="n">
-        <v>553.62</v>
+        <v>580.39</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:59:46</t>
+          <t>09:05:34</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.59</v>
+        <v>3.67</v>
       </c>
       <c r="F59" t="n">
-        <v>9.630000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="G59" t="n">
-        <v>170</v>
+        <v>171.4</v>
       </c>
       <c r="H59" t="n">
-        <v>100</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-6.81</v>
+        <v>196.44</v>
       </c>
       <c r="K59" t="n">
-        <v>33.75</v>
+        <v>159.43</v>
       </c>
       <c r="L59" t="n">
-        <v>34.43</v>
+        <v>252.99</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:01:54</t>
+          <t>09:06:47</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.86</v>
+        <v>2.71</v>
       </c>
       <c r="F60" t="n">
-        <v>9.119999999999999</v>
+        <v>9.24</v>
       </c>
       <c r="G60" t="n">
-        <v>167.1</v>
+        <v>153</v>
       </c>
       <c r="H60" t="n">
-        <v>98.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>76.56</v>
+        <v>-126.68</v>
       </c>
       <c r="K60" t="n">
-        <v>-183.42</v>
+        <v>37.46</v>
       </c>
       <c r="L60" t="n">
-        <v>198.76</v>
+        <v>132.1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:03:56</t>
+          <t>09:07:54</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.56</v>
+        <v>3.29</v>
       </c>
       <c r="F61" t="n">
-        <v>9</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G61" t="n">
-        <v>161.4</v>
+        <v>170.7</v>
       </c>
       <c r="H61" t="n">
-        <v>93.90000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>-24.33</v>
+        <v>83.06</v>
       </c>
       <c r="K61" t="n">
-        <v>-184.81</v>
+        <v>-28.27</v>
       </c>
       <c r="L61" t="n">
-        <v>186.4</v>
+        <v>87.73999999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:08:40</t>
+          <t>09:13:12</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.67</v>
+        <v>3.74</v>
       </c>
       <c r="F62" t="n">
-        <v>10.15</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="G62" t="n">
-        <v>168</v>
+        <v>164.4</v>
       </c>
       <c r="H62" t="n">
-        <v>97.59999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="I62" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>184.15</v>
+        <v>-97.43000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>-94.44</v>
+        <v>111.49</v>
       </c>
       <c r="L62" t="n">
-        <v>206.96</v>
+        <v>148.06</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:11:11</t>
+          <t>09:15:09</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="F63" t="n">
-        <v>8.56</v>
+        <v>10.09</v>
       </c>
       <c r="G63" t="n">
-        <v>166.3</v>
+        <v>163.6</v>
       </c>
       <c r="H63" t="n">
-        <v>91.8</v>
+        <v>96.7</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-253.1</v>
+        <v>194.71</v>
       </c>
       <c r="K63" t="n">
-        <v>155</v>
+        <v>202.54</v>
       </c>
       <c r="L63" t="n">
-        <v>296.79</v>
+        <v>280.96</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:12:17</t>
+          <t>09:16:48</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.68</v>
+        <v>3.33</v>
       </c>
       <c r="F64" t="n">
-        <v>8.789999999999999</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G64" t="n">
-        <v>155</v>
+        <v>174.8</v>
       </c>
       <c r="H64" t="n">
-        <v>93.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>112.88</v>
+        <v>-37.52</v>
       </c>
       <c r="K64" t="n">
-        <v>-91.95999999999999</v>
+        <v>63.79</v>
       </c>
       <c r="L64" t="n">
-        <v>145.59</v>
+        <v>74.01000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:16:07</t>
+          <t>09:21:12</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.65</v>
+        <v>4.01</v>
       </c>
       <c r="F65" t="n">
-        <v>8.65</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G65" t="n">
-        <v>154.4</v>
+        <v>174.4</v>
       </c>
       <c r="H65" t="n">
-        <v>92.5</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>100.11</v>
+        <v>-70.56999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>-126.43</v>
+        <v>-277.43</v>
       </c>
       <c r="L65" t="n">
-        <v>161.27</v>
+        <v>286.26</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:17:51</t>
+          <t>09:22:39</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.28</v>
+        <v>3.34</v>
       </c>
       <c r="F66" t="n">
-        <v>9</v>
+        <v>9.02</v>
       </c>
       <c r="G66" t="n">
-        <v>158</v>
+        <v>166.3</v>
       </c>
       <c r="H66" t="n">
-        <v>95.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="I66" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>412</v>
+        <v>-259.66</v>
       </c>
       <c r="K66" t="n">
-        <v>-102.55</v>
+        <v>220.14</v>
       </c>
       <c r="L66" t="n">
-        <v>424.57</v>
+        <v>340.42</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:19:56</t>
+          <t>09:24:17</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.67</v>
+        <v>3.41</v>
       </c>
       <c r="F67" t="n">
-        <v>9.460000000000001</v>
+        <v>9.32</v>
       </c>
       <c r="G67" t="n">
-        <v>148.8</v>
+        <v>165.8</v>
       </c>
       <c r="H67" t="n">
-        <v>92.3</v>
+        <v>100</v>
       </c>
       <c r="I67" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-150.89</v>
+        <v>321.77</v>
       </c>
       <c r="K67" t="n">
-        <v>-125.13</v>
+        <v>-81.20999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>196.02</v>
+        <v>331.86</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:25:01</t>
+          <t>09:28:08</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.78</v>
+        <v>3.44</v>
       </c>
       <c r="F68" t="n">
-        <v>8.93</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="G68" t="n">
-        <v>155.8</v>
+        <v>166.2</v>
       </c>
       <c r="H68" t="n">
-        <v>98.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-279.83</v>
+        <v>-23.13</v>
       </c>
       <c r="K68" t="n">
-        <v>-167.28</v>
+        <v>599.87</v>
       </c>
       <c r="L68" t="n">
-        <v>326.02</v>
+        <v>600.3099999999999</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:27:30</t>
+          <t>09:29:18</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.63</v>
+        <v>3.64</v>
       </c>
       <c r="F69" t="n">
-        <v>8.619999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>165.3</v>
+        <v>161.2</v>
       </c>
       <c r="H69" t="n">
-        <v>94.5</v>
+        <v>98.5</v>
       </c>
       <c r="I69" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>-47.15</v>
+        <v>329.64</v>
       </c>
       <c r="K69" t="n">
-        <v>-293.95</v>
+        <v>-27.78</v>
       </c>
       <c r="L69" t="n">
-        <v>297.71</v>
+        <v>330.81</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:28:36</t>
+          <t>09:30:46</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.65</v>
+        <v>3.24</v>
       </c>
       <c r="F70" t="n">
-        <v>8.68</v>
+        <v>9.24</v>
       </c>
       <c r="G70" t="n">
-        <v>171.1</v>
+        <v>152.9</v>
       </c>
       <c r="H70" t="n">
-        <v>100</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>86.73999999999999</v>
+        <v>10.74</v>
       </c>
       <c r="K70" t="n">
-        <v>-164.91</v>
+        <v>-618.5700000000001</v>
       </c>
       <c r="L70" t="n">
-        <v>186.33</v>
+        <v>618.67</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:32:21</t>
+          <t>09:35:08</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.89</v>
+        <v>3.58</v>
       </c>
       <c r="F71" t="n">
-        <v>9.640000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G71" t="n">
-        <v>162.5</v>
+        <v>163.9</v>
       </c>
       <c r="H71" t="n">
-        <v>92</v>
+        <v>88.8</v>
       </c>
       <c r="I71" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>-372.72</v>
+        <v>287.14</v>
       </c>
       <c r="K71" t="n">
-        <v>71.08</v>
+        <v>-25.68</v>
       </c>
       <c r="L71" t="n">
-        <v>379.43</v>
+        <v>288.29</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:33:50</t>
+          <t>09:36:40</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.28</v>
+        <v>3.73</v>
       </c>
       <c r="F72" t="n">
-        <v>8.779999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="G72" t="n">
-        <v>158.5</v>
+        <v>174</v>
       </c>
       <c r="H72" t="n">
-        <v>92.09999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I72" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-369.02</v>
+        <v>96.48</v>
       </c>
       <c r="K72" t="n">
-        <v>1075.53</v>
+        <v>-389.42</v>
       </c>
       <c r="L72" t="n">
-        <v>1137.07</v>
+        <v>401.19</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:36:04</t>
+          <t>09:38:02</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.5</v>
+        <v>3.63</v>
       </c>
       <c r="F73" t="n">
-        <v>9.32</v>
+        <v>9.33</v>
       </c>
       <c r="G73" t="n">
-        <v>176</v>
+        <v>158.2</v>
       </c>
       <c r="H73" t="n">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="I73" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>563.02</v>
+        <v>304.05</v>
       </c>
       <c r="K73" t="n">
-        <v>286.44</v>
+        <v>-526.35</v>
       </c>
       <c r="L73" t="n">
-        <v>631.7</v>
+        <v>607.86</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:47:04</t>
+          <t>09:48:49</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.69</v>
+        <v>3.5</v>
       </c>
       <c r="F74" t="n">
-        <v>9.69</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="G74" t="n">
-        <v>172.5</v>
+        <v>169.6</v>
       </c>
       <c r="H74" t="n">
-        <v>90.7</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>108.88</v>
+        <v>-269.91</v>
       </c>
       <c r="K74" t="n">
-        <v>-191.33</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>220.14</v>
+        <v>270.06</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:48:45</t>
+          <t>09:51:17</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.67</v>
+        <v>4.26</v>
       </c>
       <c r="F75" t="n">
-        <v>9.07</v>
+        <v>8.4</v>
       </c>
       <c r="G75" t="n">
-        <v>164.4</v>
+        <v>174.2</v>
       </c>
       <c r="H75" t="n">
-        <v>87.2</v>
+        <v>96.8</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.81</v>
+        <v>38.64</v>
       </c>
       <c r="K75" t="n">
-        <v>48.51</v>
+        <v>-135.07</v>
       </c>
       <c r="L75" t="n">
-        <v>49.13</v>
+        <v>140.49</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:49:49</t>
+          <t>09:52:12</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.58</v>
+        <v>4.06</v>
       </c>
       <c r="F76" t="n">
-        <v>9.390000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="G76" t="n">
-        <v>151.6</v>
+        <v>156.9</v>
       </c>
       <c r="H76" t="n">
-        <v>95</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-206.48</v>
+        <v>-35.55</v>
       </c>
       <c r="K76" t="n">
-        <v>-204.12</v>
+        <v>-91</v>
       </c>
       <c r="L76" t="n">
-        <v>290.34</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:52:57</t>
+          <t>09:57:48</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.76</v>
+        <v>4.01</v>
       </c>
       <c r="F77" t="n">
-        <v>9.57</v>
+        <v>9.42</v>
       </c>
       <c r="G77" t="n">
-        <v>172.3</v>
+        <v>171.9</v>
       </c>
       <c r="H77" t="n">
-        <v>92.8</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>117.2</v>
+        <v>170.02</v>
       </c>
       <c r="K77" t="n">
-        <v>172.57</v>
+        <v>-208.77</v>
       </c>
       <c r="L77" t="n">
-        <v>208.61</v>
+        <v>269.24</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:53:39</t>
+          <t>09:59:42</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.87</v>
+        <v>4.29</v>
       </c>
       <c r="F78" t="n">
-        <v>9.82</v>
+        <v>8.83</v>
       </c>
       <c r="G78" t="n">
-        <v>173.9</v>
+        <v>153.5</v>
       </c>
       <c r="H78" t="n">
-        <v>97.3</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>7.58</v>
+        <v>-52.08</v>
       </c>
       <c r="K78" t="n">
-        <v>-177.09</v>
+        <v>173.93</v>
       </c>
       <c r="L78" t="n">
-        <v>177.25</v>
+        <v>181.55</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:54:41</t>
+          <t>10:02:11</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="F79" t="n">
-        <v>9.789999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G79" t="n">
-        <v>164.9</v>
+        <v>152.8</v>
       </c>
       <c r="H79" t="n">
-        <v>95.5</v>
+        <v>93.7</v>
       </c>
       <c r="I79" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>137.2</v>
+        <v>65.56</v>
       </c>
       <c r="K79" t="n">
-        <v>-241.91</v>
+        <v>-253.03</v>
       </c>
       <c r="L79" t="n">
-        <v>278.11</v>
+        <v>261.39</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:58:59</t>
+          <t>10:06:22</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.31</v>
+        <v>3.5</v>
       </c>
       <c r="F80" t="n">
-        <v>9.050000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G80" t="n">
-        <v>158.1</v>
+        <v>156</v>
       </c>
       <c r="H80" t="n">
-        <v>94.7</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>-75.31</v>
+        <v>186.72</v>
       </c>
       <c r="K80" t="n">
-        <v>155.24</v>
+        <v>169.09</v>
       </c>
       <c r="L80" t="n">
-        <v>172.54</v>
+        <v>251.91</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:00:57</t>
+          <t>10:07:12</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.84</v>
+        <v>3.67</v>
       </c>
       <c r="F81" t="n">
-        <v>8.640000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="G81" t="n">
-        <v>170.1</v>
+        <v>157.8</v>
       </c>
       <c r="H81" t="n">
-        <v>98.8</v>
+        <v>91.3</v>
       </c>
       <c r="I81" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>218.84</v>
+        <v>-261.78</v>
       </c>
       <c r="K81" t="n">
-        <v>80.54000000000001</v>
+        <v>18.18</v>
       </c>
       <c r="L81" t="n">
-        <v>233.19</v>
+        <v>262.41</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:02:22</t>
+          <t>10:08:50</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.75</v>
+        <v>3.93</v>
       </c>
       <c r="F82" t="n">
-        <v>9.289999999999999</v>
+        <v>9.34</v>
       </c>
       <c r="G82" t="n">
-        <v>164</v>
+        <v>165.2</v>
       </c>
       <c r="H82" t="n">
-        <v>97.3</v>
+        <v>94.7</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-288.55</v>
+        <v>-369.76</v>
       </c>
       <c r="K82" t="n">
-        <v>-259.44</v>
+        <v>-350.88</v>
       </c>
       <c r="L82" t="n">
-        <v>388.03</v>
+        <v>509.74</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:07:38</t>
+          <t>10:13:19</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.17</v>
+        <v>3.73</v>
       </c>
       <c r="F83" t="n">
-        <v>9.49</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G83" t="n">
-        <v>154</v>
+        <v>176.5</v>
       </c>
       <c r="H83" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I83" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-608.71</v>
+        <v>-248.59</v>
       </c>
       <c r="K83" t="n">
-        <v>80.68000000000001</v>
+        <v>-91.91</v>
       </c>
       <c r="L83" t="n">
-        <v>614.04</v>
+        <v>265.04</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:08:25</t>
+          <t>10:15:39</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="F84" t="n">
-        <v>9.609999999999999</v>
+        <v>9.02</v>
       </c>
       <c r="G84" t="n">
-        <v>171.3</v>
+        <v>159.1</v>
       </c>
       <c r="H84" t="n">
-        <v>88.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-104.3</v>
+        <v>-361.41</v>
       </c>
       <c r="K84" t="n">
-        <v>-223.77</v>
+        <v>-75.59</v>
       </c>
       <c r="L84" t="n">
-        <v>246.88</v>
+        <v>369.23</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:10:24</t>
+          <t>10:17:46</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.26</v>
+        <v>3.52</v>
       </c>
       <c r="F85" t="n">
-        <v>9.630000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="G85" t="n">
-        <v>162.6</v>
+        <v>168.9</v>
       </c>
       <c r="H85" t="n">
-        <v>90.3</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>-374.07</v>
+        <v>-9.94</v>
       </c>
       <c r="K85" t="n">
-        <v>19.37</v>
+        <v>333.95</v>
       </c>
       <c r="L85" t="n">
-        <v>374.57</v>
+        <v>334.1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:15:45</t>
+          <t>10:22:54</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.77</v>
+        <v>4.12</v>
       </c>
       <c r="F86" t="n">
         <v>9.4</v>
       </c>
       <c r="G86" t="n">
-        <v>160.8</v>
+        <v>177.9</v>
       </c>
       <c r="H86" t="n">
-        <v>96.3</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-1258.63</v>
+        <v>-111.4</v>
       </c>
       <c r="K86" t="n">
-        <v>-220.85</v>
+        <v>-310.74</v>
       </c>
       <c r="L86" t="n">
-        <v>1277.86</v>
+        <v>330.11</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:17:10</t>
+          <t>10:25:15</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.04</v>
+        <v>3.84</v>
       </c>
       <c r="F87" t="n">
-        <v>8.43</v>
+        <v>9.41</v>
       </c>
       <c r="G87" t="n">
-        <v>175.2</v>
+        <v>161.6</v>
       </c>
       <c r="H87" t="n">
-        <v>90.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-231.32</v>
+        <v>-786.86</v>
       </c>
       <c r="K87" t="n">
-        <v>-427.03</v>
+        <v>66.27</v>
       </c>
       <c r="L87" t="n">
-        <v>485.66</v>
+        <v>789.64</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:18:17</t>
+          <t>10:26:33</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.99</v>
+        <v>3.53</v>
       </c>
       <c r="F88" t="n">
-        <v>8.85</v>
+        <v>9.67</v>
       </c>
       <c r="G88" t="n">
-        <v>163.8</v>
+        <v>173.1</v>
       </c>
       <c r="H88" t="n">
-        <v>87.7</v>
+        <v>94.8</v>
       </c>
       <c r="I88" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-39.04</v>
+        <v>474.14</v>
       </c>
       <c r="K88" t="n">
-        <v>-425.27</v>
+        <v>-1035.04</v>
       </c>
       <c r="L88" t="n">
-        <v>427.05</v>
+        <v>1138.47</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-02.xlsx
+++ b/output/2024-04-02.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>18.87</v>
+        <v>22.08</v>
       </c>
       <c r="K14" t="n">
-        <v>111.19</v>
+        <v>130.1</v>
       </c>
       <c r="L14" t="n">
-        <v>112.78</v>
+        <v>131.96</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>-45.49</v>
+        <v>-50.1</v>
       </c>
       <c r="K15" t="n">
-        <v>90.34</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>101.15</v>
+        <v>111.41</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>-132.14</v>
+        <v>-145.2</v>
       </c>
       <c r="K16" t="n">
-        <v>3.89</v>
+        <v>4.27</v>
       </c>
       <c r="L16" t="n">
-        <v>132.2</v>
+        <v>145.26</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>-286.7</v>
+        <v>-262.33</v>
       </c>
       <c r="K17" t="n">
-        <v>-54.66</v>
+        <v>-50.02</v>
       </c>
       <c r="L17" t="n">
-        <v>291.87</v>
+        <v>267.06</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-68.56</v>
+        <v>-81.84999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>62.69</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>92.90000000000001</v>
+        <v>110.92</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>122.96</v>
+        <v>116.18</v>
       </c>
       <c r="K19" t="n">
-        <v>83.34</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>148.54</v>
+        <v>140.34</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>93.76000000000001</v>
+        <v>99.73</v>
       </c>
       <c r="K20" t="n">
-        <v>-267.85</v>
+        <v>-284.92</v>
       </c>
       <c r="L20" t="n">
-        <v>283.79</v>
+        <v>301.87</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>33.79</v>
+        <v>61.83</v>
       </c>
       <c r="K21" t="n">
-        <v>104.17</v>
+        <v>190.61</v>
       </c>
       <c r="L21" t="n">
-        <v>109.51</v>
+        <v>200.39</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-281.28</v>
+        <v>-311.14</v>
       </c>
       <c r="K22" t="n">
-        <v>100.09</v>
+        <v>110.72</v>
       </c>
       <c r="L22" t="n">
-        <v>298.56</v>
+        <v>330.25</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>77.48999999999999</v>
+        <v>96.64</v>
       </c>
       <c r="K23" t="n">
-        <v>354.73</v>
+        <v>442.4</v>
       </c>
       <c r="L23" t="n">
-        <v>363.09</v>
+        <v>452.83</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>69.62</v>
+        <v>220.27</v>
       </c>
       <c r="K24" t="n">
-        <v>-25.94</v>
+        <v>-82.08</v>
       </c>
       <c r="L24" t="n">
-        <v>74.29000000000001</v>
+        <v>235.07</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>228.74</v>
+        <v>305.64</v>
       </c>
       <c r="K25" t="n">
-        <v>20.09</v>
+        <v>26.85</v>
       </c>
       <c r="L25" t="n">
-        <v>229.62</v>
+        <v>306.82</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>428.19</v>
+        <v>475.75</v>
       </c>
       <c r="K26" t="n">
-        <v>338.77</v>
+        <v>376.39</v>
       </c>
       <c r="L26" t="n">
-        <v>545.99</v>
+        <v>606.64</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>531.8200000000001</v>
+        <v>670.61</v>
       </c>
       <c r="K27" t="n">
-        <v>271.43</v>
+        <v>342.26</v>
       </c>
       <c r="L27" t="n">
-        <v>597.08</v>
+        <v>752.9</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>478.14</v>
+        <v>611.55</v>
       </c>
       <c r="K28" t="n">
-        <v>-216.27</v>
+        <v>-276.61</v>
       </c>
       <c r="L28" t="n">
-        <v>524.78</v>
+        <v>671.2</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-32.08</v>
+        <v>-30.08</v>
       </c>
       <c r="K29" t="n">
-        <v>213.94</v>
+        <v>200.6</v>
       </c>
       <c r="L29" t="n">
-        <v>216.33</v>
+        <v>202.84</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>180.22</v>
+        <v>188.19</v>
       </c>
       <c r="K30" t="n">
-        <v>-24.26</v>
+        <v>-25.34</v>
       </c>
       <c r="L30" t="n">
-        <v>181.84</v>
+        <v>189.88</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-265.61</v>
+        <v>-253.91</v>
       </c>
       <c r="K31" t="n">
-        <v>-75.76000000000001</v>
+        <v>-72.43000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>276.2</v>
+        <v>264.04</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>27.48</v>
+        <v>30.24</v>
       </c>
       <c r="K32" t="n">
-        <v>130.1</v>
+        <v>143.18</v>
       </c>
       <c r="L32" t="n">
-        <v>132.97</v>
+        <v>146.33</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-206.69</v>
+        <v>-205.87</v>
       </c>
       <c r="K33" t="n">
-        <v>-180.08</v>
+        <v>-179.37</v>
       </c>
       <c r="L33" t="n">
-        <v>274.13</v>
+        <v>273.05</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>242.72</v>
+        <v>225.74</v>
       </c>
       <c r="K34" t="n">
-        <v>-59.9</v>
+        <v>-55.71</v>
       </c>
       <c r="L34" t="n">
-        <v>250</v>
+        <v>232.52</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-170.4</v>
+        <v>-237.89</v>
       </c>
       <c r="K35" t="n">
-        <v>17.54</v>
+        <v>24.49</v>
       </c>
       <c r="L35" t="n">
-        <v>171.3</v>
+        <v>239.15</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.34</v>
+        <v>-0.38</v>
       </c>
       <c r="K36" t="n">
-        <v>-314.14</v>
+        <v>-350.14</v>
       </c>
       <c r="L36" t="n">
-        <v>314.14</v>
+        <v>350.14</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>143.71</v>
+        <v>137.2</v>
       </c>
       <c r="K37" t="n">
-        <v>354.89</v>
+        <v>338.82</v>
       </c>
       <c r="L37" t="n">
-        <v>382.88</v>
+        <v>365.55</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-186.48</v>
+        <v>-341.77</v>
       </c>
       <c r="K38" t="n">
-        <v>106.7</v>
+        <v>195.56</v>
       </c>
       <c r="L38" t="n">
-        <v>214.85</v>
+        <v>393.76</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>276.16</v>
+        <v>370.59</v>
       </c>
       <c r="K39" t="n">
-        <v>-179.45</v>
+        <v>-240.82</v>
       </c>
       <c r="L39" t="n">
-        <v>329.35</v>
+        <v>441.96</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-316.52</v>
+        <v>-367.07</v>
       </c>
       <c r="K40" t="n">
-        <v>335.41</v>
+        <v>388.98</v>
       </c>
       <c r="L40" t="n">
-        <v>461.17</v>
+        <v>534.84</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>-218.49</v>
+        <v>-347.13</v>
       </c>
       <c r="K41" t="n">
-        <v>170.44</v>
+        <v>270.8</v>
       </c>
       <c r="L41" t="n">
-        <v>277.1</v>
+        <v>440.26</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-315.33</v>
+        <v>-498.65</v>
       </c>
       <c r="K42" t="n">
-        <v>-57.76</v>
+        <v>-91.34</v>
       </c>
       <c r="L42" t="n">
-        <v>320.58</v>
+        <v>506.94</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>418.03</v>
+        <v>530.04</v>
       </c>
       <c r="K43" t="n">
-        <v>-35.42</v>
+        <v>-44.91</v>
       </c>
       <c r="L43" t="n">
-        <v>419.53</v>
+        <v>531.9400000000001</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-111.2</v>
+        <v>-139.36</v>
       </c>
       <c r="K44" t="n">
-        <v>39.61</v>
+        <v>49.64</v>
       </c>
       <c r="L44" t="n">
-        <v>118.04</v>
+        <v>147.94</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>11.73</v>
+        <v>12.93</v>
       </c>
       <c r="K45" t="n">
-        <v>93.31999999999999</v>
+        <v>102.91</v>
       </c>
       <c r="L45" t="n">
-        <v>94.06</v>
+        <v>103.72</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>74.67</v>
+        <v>72.73</v>
       </c>
       <c r="K46" t="n">
-        <v>187.91</v>
+        <v>183.01</v>
       </c>
       <c r="L46" t="n">
-        <v>202.21</v>
+        <v>196.93</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>80.42</v>
+        <v>140.94</v>
       </c>
       <c r="K47" t="n">
-        <v>-56.79</v>
+        <v>-99.53</v>
       </c>
       <c r="L47" t="n">
-        <v>98.45</v>
+        <v>172.54</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>-198.17</v>
+        <v>-203.71</v>
       </c>
       <c r="K48" t="n">
-        <v>-10.42</v>
+        <v>-10.71</v>
       </c>
       <c r="L48" t="n">
-        <v>198.45</v>
+        <v>203.99</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>153.13</v>
+        <v>169.57</v>
       </c>
       <c r="K49" t="n">
-        <v>-289.25</v>
+        <v>-320.3</v>
       </c>
       <c r="L49" t="n">
-        <v>327.28</v>
+        <v>362.42</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>181.34</v>
+        <v>249.12</v>
       </c>
       <c r="K50" t="n">
-        <v>-77.39</v>
+        <v>-106.32</v>
       </c>
       <c r="L50" t="n">
-        <v>197.16</v>
+        <v>270.86</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-122.4</v>
+        <v>-143.92</v>
       </c>
       <c r="K51" t="n">
-        <v>63.27</v>
+        <v>74.39</v>
       </c>
       <c r="L51" t="n">
-        <v>137.78</v>
+        <v>162.01</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-179.05</v>
+        <v>-236.05</v>
       </c>
       <c r="K52" t="n">
-        <v>-155.86</v>
+        <v>-205.47</v>
       </c>
       <c r="L52" t="n">
-        <v>237.38</v>
+        <v>312.95</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>226.46</v>
+        <v>262.98</v>
       </c>
       <c r="K53" t="n">
-        <v>-592.5599999999999</v>
+        <v>-688.13</v>
       </c>
       <c r="L53" t="n">
-        <v>634.36</v>
+        <v>736.67</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>183.35</v>
+        <v>195.67</v>
       </c>
       <c r="K54" t="n">
-        <v>702.4299999999999</v>
+        <v>749.64</v>
       </c>
       <c r="L54" t="n">
-        <v>725.97</v>
+        <v>774.76</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>116.76</v>
+        <v>172.33</v>
       </c>
       <c r="K55" t="n">
-        <v>-273.45</v>
+        <v>-403.6</v>
       </c>
       <c r="L55" t="n">
-        <v>297.34</v>
+        <v>438.85</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>299.28</v>
+        <v>358.82</v>
       </c>
       <c r="K56" t="n">
-        <v>690.75</v>
+        <v>828.16</v>
       </c>
       <c r="L56" t="n">
-        <v>752.8</v>
+        <v>902.55</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-709.97</v>
+        <v>-905.99</v>
       </c>
       <c r="K57" t="n">
-        <v>289.95</v>
+        <v>370.01</v>
       </c>
       <c r="L57" t="n">
-        <v>766.9</v>
+        <v>978.64</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-531.4400000000001</v>
+        <v>-594.08</v>
       </c>
       <c r="K58" t="n">
-        <v>233.29</v>
+        <v>260.79</v>
       </c>
       <c r="L58" t="n">
-        <v>580.39</v>
+        <v>648.8</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>196.44</v>
+        <v>183.08</v>
       </c>
       <c r="K59" t="n">
-        <v>159.43</v>
+        <v>148.58</v>
       </c>
       <c r="L59" t="n">
-        <v>252.99</v>
+        <v>235.79</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-126.68</v>
+        <v>-127.77</v>
       </c>
       <c r="K60" t="n">
-        <v>37.46</v>
+        <v>37.78</v>
       </c>
       <c r="L60" t="n">
-        <v>132.1</v>
+        <v>133.24</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>83.06</v>
+        <v>102.28</v>
       </c>
       <c r="K61" t="n">
-        <v>-28.27</v>
+        <v>-34.81</v>
       </c>
       <c r="L61" t="n">
-        <v>87.73999999999999</v>
+        <v>108.04</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-97.43000000000001</v>
+        <v>-120.4</v>
       </c>
       <c r="K62" t="n">
-        <v>111.49</v>
+        <v>137.79</v>
       </c>
       <c r="L62" t="n">
-        <v>148.06</v>
+        <v>182.98</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>194.71</v>
+        <v>188.67</v>
       </c>
       <c r="K63" t="n">
-        <v>202.54</v>
+        <v>196.26</v>
       </c>
       <c r="L63" t="n">
-        <v>280.96</v>
+        <v>272.24</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-37.52</v>
+        <v>-58.91</v>
       </c>
       <c r="K64" t="n">
-        <v>63.79</v>
+        <v>100.15</v>
       </c>
       <c r="L64" t="n">
-        <v>74.01000000000001</v>
+        <v>116.19</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>-70.56999999999999</v>
+        <v>-95.23999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>-277.43</v>
+        <v>-374.43</v>
       </c>
       <c r="L65" t="n">
-        <v>286.26</v>
+        <v>386.36</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-259.66</v>
+        <v>-271.63</v>
       </c>
       <c r="K66" t="n">
-        <v>220.14</v>
+        <v>230.28</v>
       </c>
       <c r="L66" t="n">
-        <v>340.42</v>
+        <v>356.11</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>321.77</v>
+        <v>331.74</v>
       </c>
       <c r="K67" t="n">
-        <v>-81.20999999999999</v>
+        <v>-83.73</v>
       </c>
       <c r="L67" t="n">
-        <v>331.86</v>
+        <v>342.14</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-23.13</v>
+        <v>-24.3</v>
       </c>
       <c r="K68" t="n">
-        <v>599.87</v>
+        <v>630.16</v>
       </c>
       <c r="L68" t="n">
-        <v>600.3099999999999</v>
+        <v>630.63</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>329.64</v>
+        <v>447.19</v>
       </c>
       <c r="K69" t="n">
-        <v>-27.78</v>
+        <v>-37.69</v>
       </c>
       <c r="L69" t="n">
-        <v>330.81</v>
+        <v>448.78</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>10.74</v>
+        <v>10.82</v>
       </c>
       <c r="K70" t="n">
-        <v>-618.5700000000001</v>
+        <v>-623.29</v>
       </c>
       <c r="L70" t="n">
-        <v>618.67</v>
+        <v>623.38</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>287.14</v>
+        <v>486.79</v>
       </c>
       <c r="K71" t="n">
-        <v>-25.68</v>
+        <v>-43.53</v>
       </c>
       <c r="L71" t="n">
-        <v>288.29</v>
+        <v>488.73</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>96.48</v>
+        <v>157.72</v>
       </c>
       <c r="K72" t="n">
-        <v>-389.42</v>
+        <v>-636.61</v>
       </c>
       <c r="L72" t="n">
-        <v>401.19</v>
+        <v>655.86</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>304.05</v>
+        <v>358.88</v>
       </c>
       <c r="K73" t="n">
-        <v>-526.35</v>
+        <v>-621.27</v>
       </c>
       <c r="L73" t="n">
-        <v>607.86</v>
+        <v>717.48</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>-269.91</v>
+        <v>-239.96</v>
       </c>
       <c r="K74" t="n">
-        <v>-8.800000000000001</v>
+        <v>-7.82</v>
       </c>
       <c r="L74" t="n">
-        <v>270.06</v>
+        <v>240.09</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>38.64</v>
+        <v>52.69</v>
       </c>
       <c r="K75" t="n">
-        <v>-135.07</v>
+        <v>-184.18</v>
       </c>
       <c r="L75" t="n">
-        <v>140.49</v>
+        <v>191.56</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-35.55</v>
+        <v>-59.52</v>
       </c>
       <c r="K76" t="n">
-        <v>-91</v>
+        <v>-152.33</v>
       </c>
       <c r="L76" t="n">
-        <v>97.7</v>
+        <v>163.54</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>170.02</v>
+        <v>178.25</v>
       </c>
       <c r="K77" t="n">
-        <v>-208.77</v>
+        <v>-218.87</v>
       </c>
       <c r="L77" t="n">
-        <v>269.24</v>
+        <v>282.27</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-52.08</v>
+        <v>-75</v>
       </c>
       <c r="K78" t="n">
-        <v>173.93</v>
+        <v>250.49</v>
       </c>
       <c r="L78" t="n">
-        <v>181.55</v>
+        <v>261.48</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>65.56</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>-253.03</v>
+        <v>-248.03</v>
       </c>
       <c r="L79" t="n">
-        <v>261.39</v>
+        <v>256.22</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>186.72</v>
+        <v>222.81</v>
       </c>
       <c r="K80" t="n">
-        <v>169.09</v>
+        <v>201.78</v>
       </c>
       <c r="L80" t="n">
-        <v>251.91</v>
+        <v>300.6</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-261.78</v>
+        <v>-305.27</v>
       </c>
       <c r="K81" t="n">
-        <v>18.18</v>
+        <v>21.2</v>
       </c>
       <c r="L81" t="n">
-        <v>262.41</v>
+        <v>306</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-369.76</v>
+        <v>-421.51</v>
       </c>
       <c r="K82" t="n">
-        <v>-350.88</v>
+        <v>-399.99</v>
       </c>
       <c r="L82" t="n">
-        <v>509.74</v>
+        <v>581.09</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-248.59</v>
+        <v>-390.78</v>
       </c>
       <c r="K83" t="n">
-        <v>-91.91</v>
+        <v>-144.48</v>
       </c>
       <c r="L83" t="n">
-        <v>265.04</v>
+        <v>416.64</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-361.41</v>
+        <v>-394.3</v>
       </c>
       <c r="K84" t="n">
-        <v>-75.59</v>
+        <v>-82.47</v>
       </c>
       <c r="L84" t="n">
-        <v>369.23</v>
+        <v>402.83</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>-9.94</v>
+        <v>-14.01</v>
       </c>
       <c r="K85" t="n">
-        <v>333.95</v>
+        <v>470.71</v>
       </c>
       <c r="L85" t="n">
-        <v>334.1</v>
+        <v>470.92</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-111.4</v>
+        <v>-198.61</v>
       </c>
       <c r="K86" t="n">
-        <v>-310.74</v>
+        <v>-554.01</v>
       </c>
       <c r="L86" t="n">
-        <v>330.11</v>
+        <v>588.53</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-786.86</v>
+        <v>-1023.35</v>
       </c>
       <c r="K87" t="n">
-        <v>66.27</v>
+        <v>86.19</v>
       </c>
       <c r="L87" t="n">
-        <v>789.64</v>
+        <v>1026.98</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>474.14</v>
+        <v>530.5700000000001</v>
       </c>
       <c r="K88" t="n">
-        <v>-1035.04</v>
+        <v>-1158.23</v>
       </c>
       <c r="L88" t="n">
-        <v>1138.47</v>
+        <v>1273.97</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-02.xlsx
+++ b/output/2024-04-02.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>22.08</v>
+        <v>17.91</v>
       </c>
       <c r="K14" t="n">
-        <v>130.1</v>
+        <v>105.54</v>
       </c>
       <c r="L14" t="n">
-        <v>131.96</v>
+        <v>107.05</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>-50.1</v>
+        <v>-40.96</v>
       </c>
       <c r="K15" t="n">
-        <v>99.51000000000001</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>111.41</v>
+        <v>91.08</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>-145.2</v>
+        <v>-109.64</v>
       </c>
       <c r="K16" t="n">
-        <v>4.27</v>
+        <v>3.23</v>
       </c>
       <c r="L16" t="n">
-        <v>145.26</v>
+        <v>109.69</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>-262.33</v>
+        <v>-185.44</v>
       </c>
       <c r="K17" t="n">
-        <v>-50.02</v>
+        <v>-35.36</v>
       </c>
       <c r="L17" t="n">
-        <v>267.06</v>
+        <v>188.78</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-81.84999999999999</v>
+        <v>-61.05</v>
       </c>
       <c r="K18" t="n">
-        <v>74.84999999999999</v>
+        <v>55.83</v>
       </c>
       <c r="L18" t="n">
-        <v>110.92</v>
+        <v>82.73</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>116.18</v>
+        <v>97.95</v>
       </c>
       <c r="K19" t="n">
-        <v>78.73999999999999</v>
+        <v>66.38</v>
       </c>
       <c r="L19" t="n">
-        <v>140.34</v>
+        <v>118.32</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>99.73</v>
+        <v>66.39</v>
       </c>
       <c r="K20" t="n">
-        <v>-284.92</v>
+        <v>-189.67</v>
       </c>
       <c r="L20" t="n">
-        <v>301.87</v>
+        <v>200.95</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>61.83</v>
+        <v>36.59</v>
       </c>
       <c r="K21" t="n">
-        <v>190.61</v>
+        <v>112.78</v>
       </c>
       <c r="L21" t="n">
-        <v>200.39</v>
+        <v>118.57</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-311.14</v>
+        <v>-201.15</v>
       </c>
       <c r="K22" t="n">
-        <v>110.72</v>
+        <v>71.58</v>
       </c>
       <c r="L22" t="n">
-        <v>330.25</v>
+        <v>213.51</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>96.64</v>
+        <v>55.46</v>
       </c>
       <c r="K23" t="n">
-        <v>442.4</v>
+        <v>253.89</v>
       </c>
       <c r="L23" t="n">
-        <v>452.83</v>
+        <v>259.88</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>220.27</v>
+        <v>128.45</v>
       </c>
       <c r="K24" t="n">
-        <v>-82.08</v>
+        <v>-47.87</v>
       </c>
       <c r="L24" t="n">
-        <v>235.07</v>
+        <v>137.08</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>305.64</v>
+        <v>181.5</v>
       </c>
       <c r="K25" t="n">
-        <v>26.85</v>
+        <v>15.94</v>
       </c>
       <c r="L25" t="n">
-        <v>306.82</v>
+        <v>182.2</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>475.75</v>
+        <v>267.05</v>
       </c>
       <c r="K26" t="n">
-        <v>376.39</v>
+        <v>211.28</v>
       </c>
       <c r="L26" t="n">
-        <v>606.64</v>
+        <v>340.53</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>670.61</v>
+        <v>333.28</v>
       </c>
       <c r="K27" t="n">
-        <v>342.26</v>
+        <v>170.1</v>
       </c>
       <c r="L27" t="n">
-        <v>752.9</v>
+        <v>374.17</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>611.55</v>
+        <v>321.15</v>
       </c>
       <c r="K28" t="n">
-        <v>-276.61</v>
+        <v>-145.26</v>
       </c>
       <c r="L28" t="n">
-        <v>671.2</v>
+        <v>352.47</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-30.08</v>
+        <v>-23.12</v>
       </c>
       <c r="K29" t="n">
-        <v>200.6</v>
+        <v>154.17</v>
       </c>
       <c r="L29" t="n">
-        <v>202.84</v>
+        <v>155.89</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>188.19</v>
+        <v>133.57</v>
       </c>
       <c r="K30" t="n">
-        <v>-25.34</v>
+        <v>-17.98</v>
       </c>
       <c r="L30" t="n">
-        <v>189.88</v>
+        <v>134.77</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-253.91</v>
+        <v>-185.32</v>
       </c>
       <c r="K31" t="n">
-        <v>-72.43000000000001</v>
+        <v>-52.86</v>
       </c>
       <c r="L31" t="n">
-        <v>264.04</v>
+        <v>192.71</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>30.24</v>
+        <v>23.92</v>
       </c>
       <c r="K32" t="n">
-        <v>143.18</v>
+        <v>113.25</v>
       </c>
       <c r="L32" t="n">
-        <v>146.33</v>
+        <v>115.75</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-205.87</v>
+        <v>-141.77</v>
       </c>
       <c r="K33" t="n">
-        <v>-179.37</v>
+        <v>-123.52</v>
       </c>
       <c r="L33" t="n">
-        <v>273.05</v>
+        <v>188.04</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>225.74</v>
+        <v>167.64</v>
       </c>
       <c r="K34" t="n">
-        <v>-55.71</v>
+        <v>-41.37</v>
       </c>
       <c r="L34" t="n">
-        <v>232.52</v>
+        <v>172.67</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-237.89</v>
+        <v>-147.74</v>
       </c>
       <c r="K35" t="n">
-        <v>24.49</v>
+        <v>15.21</v>
       </c>
       <c r="L35" t="n">
-        <v>239.15</v>
+        <v>148.52</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.38</v>
+        <v>-0.24</v>
       </c>
       <c r="K36" t="n">
-        <v>-350.14</v>
+        <v>-221.45</v>
       </c>
       <c r="L36" t="n">
-        <v>350.14</v>
+        <v>221.45</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>137.2</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>338.82</v>
+        <v>232.49</v>
       </c>
       <c r="L37" t="n">
-        <v>365.55</v>
+        <v>250.83</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-341.77</v>
+        <v>-175.3</v>
       </c>
       <c r="K38" t="n">
-        <v>195.56</v>
+        <v>100.31</v>
       </c>
       <c r="L38" t="n">
-        <v>393.76</v>
+        <v>201.97</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>370.59</v>
+        <v>196.39</v>
       </c>
       <c r="K39" t="n">
-        <v>-240.82</v>
+        <v>-127.62</v>
       </c>
       <c r="L39" t="n">
-        <v>441.96</v>
+        <v>234.21</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-367.07</v>
+        <v>-200.71</v>
       </c>
       <c r="K40" t="n">
-        <v>388.98</v>
+        <v>212.69</v>
       </c>
       <c r="L40" t="n">
-        <v>534.84</v>
+        <v>292.44</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>-347.13</v>
+        <v>-184.48</v>
       </c>
       <c r="K41" t="n">
-        <v>270.8</v>
+        <v>143.91</v>
       </c>
       <c r="L41" t="n">
-        <v>440.26</v>
+        <v>233.97</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-498.65</v>
+        <v>-254.24</v>
       </c>
       <c r="K42" t="n">
-        <v>-91.34</v>
+        <v>-46.57</v>
       </c>
       <c r="L42" t="n">
-        <v>506.94</v>
+        <v>258.47</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>530.04</v>
+        <v>301.18</v>
       </c>
       <c r="K43" t="n">
-        <v>-44.91</v>
+        <v>-25.52</v>
       </c>
       <c r="L43" t="n">
-        <v>531.9400000000001</v>
+        <v>302.26</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-139.36</v>
+        <v>-98.33</v>
       </c>
       <c r="K44" t="n">
-        <v>49.64</v>
+        <v>35.03</v>
       </c>
       <c r="L44" t="n">
-        <v>147.94</v>
+        <v>104.38</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>12.93</v>
+        <v>11.21</v>
       </c>
       <c r="K45" t="n">
-        <v>102.91</v>
+        <v>89.2</v>
       </c>
       <c r="L45" t="n">
-        <v>103.72</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>72.73</v>
+        <v>54.35</v>
       </c>
       <c r="K46" t="n">
-        <v>183.01</v>
+        <v>136.76</v>
       </c>
       <c r="L46" t="n">
-        <v>196.93</v>
+        <v>147.17</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>140.94</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>-99.53</v>
+        <v>-64.39</v>
       </c>
       <c r="L47" t="n">
-        <v>172.54</v>
+        <v>111.62</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>-203.71</v>
+        <v>-161.44</v>
       </c>
       <c r="K48" t="n">
-        <v>-10.71</v>
+        <v>-8.49</v>
       </c>
       <c r="L48" t="n">
-        <v>203.99</v>
+        <v>161.66</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>169.57</v>
+        <v>108.72</v>
       </c>
       <c r="K49" t="n">
-        <v>-320.3</v>
+        <v>-205.36</v>
       </c>
       <c r="L49" t="n">
-        <v>362.42</v>
+        <v>232.36</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>249.12</v>
+        <v>149.39</v>
       </c>
       <c r="K50" t="n">
-        <v>-106.32</v>
+        <v>-63.76</v>
       </c>
       <c r="L50" t="n">
-        <v>270.86</v>
+        <v>162.43</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-143.92</v>
+        <v>-107.04</v>
       </c>
       <c r="K51" t="n">
-        <v>74.39</v>
+        <v>55.32</v>
       </c>
       <c r="L51" t="n">
-        <v>162.01</v>
+        <v>120.49</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-236.05</v>
+        <v>-142.96</v>
       </c>
       <c r="K52" t="n">
-        <v>-205.47</v>
+        <v>-124.44</v>
       </c>
       <c r="L52" t="n">
-        <v>312.95</v>
+        <v>189.53</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>262.98</v>
+        <v>134</v>
       </c>
       <c r="K53" t="n">
-        <v>-688.13</v>
+        <v>-350.62</v>
       </c>
       <c r="L53" t="n">
-        <v>736.67</v>
+        <v>375.35</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>195.67</v>
+        <v>101.68</v>
       </c>
       <c r="K54" t="n">
-        <v>749.64</v>
+        <v>389.54</v>
       </c>
       <c r="L54" t="n">
-        <v>774.76</v>
+        <v>402.59</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>172.33</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>-403.6</v>
+        <v>-206.25</v>
       </c>
       <c r="L55" t="n">
-        <v>438.85</v>
+        <v>224.26</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>358.82</v>
+        <v>181.12</v>
       </c>
       <c r="K56" t="n">
-        <v>828.16</v>
+        <v>418.03</v>
       </c>
       <c r="L56" t="n">
-        <v>902.55</v>
+        <v>455.58</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-905.99</v>
+        <v>-419.94</v>
       </c>
       <c r="K57" t="n">
-        <v>370.01</v>
+        <v>171.5</v>
       </c>
       <c r="L57" t="n">
-        <v>978.64</v>
+        <v>453.61</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-594.08</v>
+        <v>-339.25</v>
       </c>
       <c r="K58" t="n">
-        <v>260.79</v>
+        <v>148.93</v>
       </c>
       <c r="L58" t="n">
-        <v>648.8</v>
+        <v>370.5</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>183.08</v>
+        <v>142.27</v>
       </c>
       <c r="K59" t="n">
-        <v>148.58</v>
+        <v>115.46</v>
       </c>
       <c r="L59" t="n">
-        <v>235.79</v>
+        <v>183.23</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-127.77</v>
+        <v>-95.78</v>
       </c>
       <c r="K60" t="n">
-        <v>37.78</v>
+        <v>28.32</v>
       </c>
       <c r="L60" t="n">
-        <v>133.24</v>
+        <v>99.88</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>102.28</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>-34.81</v>
+        <v>-28.79</v>
       </c>
       <c r="L61" t="n">
-        <v>108.04</v>
+        <v>89.33</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-120.4</v>
+        <v>-88.73999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>137.79</v>
+        <v>101.56</v>
       </c>
       <c r="L62" t="n">
-        <v>182.98</v>
+        <v>134.87</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>188.67</v>
+        <v>139.84</v>
       </c>
       <c r="K63" t="n">
-        <v>196.26</v>
+        <v>145.47</v>
       </c>
       <c r="L63" t="n">
-        <v>272.24</v>
+        <v>201.78</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-58.91</v>
+        <v>-44.68</v>
       </c>
       <c r="K64" t="n">
-        <v>100.15</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>116.19</v>
+        <v>88.12</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>-95.23999999999999</v>
+        <v>-55.01</v>
       </c>
       <c r="K65" t="n">
-        <v>-374.43</v>
+        <v>-216.25</v>
       </c>
       <c r="L65" t="n">
-        <v>386.36</v>
+        <v>223.14</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-271.63</v>
+        <v>-178.31</v>
       </c>
       <c r="K66" t="n">
-        <v>230.28</v>
+        <v>151.17</v>
       </c>
       <c r="L66" t="n">
-        <v>356.11</v>
+        <v>233.77</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>331.74</v>
+        <v>224.91</v>
       </c>
       <c r="K67" t="n">
-        <v>-83.73</v>
+        <v>-56.77</v>
       </c>
       <c r="L67" t="n">
-        <v>342.14</v>
+        <v>231.97</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-24.3</v>
+        <v>-14.04</v>
       </c>
       <c r="K68" t="n">
-        <v>630.16</v>
+        <v>364.13</v>
       </c>
       <c r="L68" t="n">
-        <v>630.63</v>
+        <v>364.4</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>447.19</v>
+        <v>247.03</v>
       </c>
       <c r="K69" t="n">
-        <v>-37.69</v>
+        <v>-20.82</v>
       </c>
       <c r="L69" t="n">
-        <v>448.78</v>
+        <v>247.9</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>10.82</v>
+        <v>6.33</v>
       </c>
       <c r="K70" t="n">
-        <v>-623.29</v>
+        <v>-364.68</v>
       </c>
       <c r="L70" t="n">
-        <v>623.38</v>
+        <v>364.74</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>486.79</v>
+        <v>247.5</v>
       </c>
       <c r="K71" t="n">
-        <v>-43.53</v>
+        <v>-22.13</v>
       </c>
       <c r="L71" t="n">
-        <v>488.73</v>
+        <v>248.48</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>157.72</v>
+        <v>72.86</v>
       </c>
       <c r="K72" t="n">
-        <v>-636.61</v>
+        <v>-294.07</v>
       </c>
       <c r="L72" t="n">
-        <v>655.86</v>
+        <v>302.96</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>358.88</v>
+        <v>195.33</v>
       </c>
       <c r="K73" t="n">
-        <v>-621.27</v>
+        <v>-338.14</v>
       </c>
       <c r="L73" t="n">
-        <v>717.48</v>
+        <v>390.5</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>-239.96</v>
+        <v>-188.49</v>
       </c>
       <c r="K74" t="n">
-        <v>-7.82</v>
+        <v>-6.15</v>
       </c>
       <c r="L74" t="n">
-        <v>240.09</v>
+        <v>188.59</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>52.69</v>
+        <v>37.22</v>
       </c>
       <c r="K75" t="n">
-        <v>-184.18</v>
+        <v>-130.1</v>
       </c>
       <c r="L75" t="n">
-        <v>191.56</v>
+        <v>135.32</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-59.52</v>
+        <v>-40.02</v>
       </c>
       <c r="K76" t="n">
-        <v>-152.33</v>
+        <v>-102.42</v>
       </c>
       <c r="L76" t="n">
-        <v>163.54</v>
+        <v>109.96</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>178.25</v>
+        <v>129.44</v>
       </c>
       <c r="K77" t="n">
-        <v>-218.87</v>
+        <v>-158.94</v>
       </c>
       <c r="L77" t="n">
-        <v>282.27</v>
+        <v>204.98</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-75</v>
+        <v>-47.49</v>
       </c>
       <c r="K78" t="n">
-        <v>250.49</v>
+        <v>158.6</v>
       </c>
       <c r="L78" t="n">
-        <v>261.48</v>
+        <v>165.56</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>64.26000000000001</v>
+        <v>49.02</v>
       </c>
       <c r="K79" t="n">
-        <v>-248.03</v>
+        <v>-189.21</v>
       </c>
       <c r="L79" t="n">
-        <v>256.22</v>
+        <v>195.46</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>222.81</v>
+        <v>145</v>
       </c>
       <c r="K80" t="n">
-        <v>201.78</v>
+        <v>131.3</v>
       </c>
       <c r="L80" t="n">
-        <v>300.6</v>
+        <v>195.61</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-305.27</v>
+        <v>-204.22</v>
       </c>
       <c r="K81" t="n">
-        <v>21.2</v>
+        <v>14.18</v>
       </c>
       <c r="L81" t="n">
-        <v>306</v>
+        <v>204.71</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-421.51</v>
+        <v>-237.44</v>
       </c>
       <c r="K82" t="n">
-        <v>-399.99</v>
+        <v>-225.31</v>
       </c>
       <c r="L82" t="n">
-        <v>581.09</v>
+        <v>327.32</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-390.78</v>
+        <v>-208.14</v>
       </c>
       <c r="K83" t="n">
-        <v>-144.48</v>
+        <v>-76.95</v>
       </c>
       <c r="L83" t="n">
-        <v>416.64</v>
+        <v>221.91</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-394.3</v>
+        <v>-248.48</v>
       </c>
       <c r="K84" t="n">
-        <v>-82.47</v>
+        <v>-51.97</v>
       </c>
       <c r="L84" t="n">
-        <v>402.83</v>
+        <v>253.86</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>-14.01</v>
+        <v>-7.32</v>
       </c>
       <c r="K85" t="n">
-        <v>470.71</v>
+        <v>246.03</v>
       </c>
       <c r="L85" t="n">
-        <v>470.92</v>
+        <v>246.13</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-198.61</v>
+        <v>-95.95</v>
       </c>
       <c r="K86" t="n">
-        <v>-554.01</v>
+        <v>-267.64</v>
       </c>
       <c r="L86" t="n">
-        <v>588.53</v>
+        <v>284.32</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-1023.35</v>
+        <v>-470.83</v>
       </c>
       <c r="K87" t="n">
-        <v>86.19</v>
+        <v>39.65</v>
       </c>
       <c r="L87" t="n">
-        <v>1026.98</v>
+        <v>472.5</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>530.5700000000001</v>
+        <v>254.08</v>
       </c>
       <c r="K88" t="n">
-        <v>-1158.23</v>
+        <v>-554.66</v>
       </c>
       <c r="L88" t="n">
-        <v>1273.97</v>
+        <v>610.09</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-02.xlsx
+++ b/output/2024-04-02.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>17.91</v>
+        <v>18.79</v>
       </c>
       <c r="K14" t="n">
-        <v>105.54</v>
+        <v>110.74</v>
       </c>
       <c r="L14" t="n">
-        <v>107.05</v>
+        <v>112.32</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>-40.96</v>
+        <v>-43</v>
       </c>
       <c r="K15" t="n">
-        <v>81.34999999999999</v>
+        <v>85.39</v>
       </c>
       <c r="L15" t="n">
-        <v>91.08</v>
+        <v>95.61</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>-109.64</v>
+        <v>-116.64</v>
       </c>
       <c r="K16" t="n">
-        <v>3.23</v>
+        <v>3.43</v>
       </c>
       <c r="L16" t="n">
-        <v>109.69</v>
+        <v>116.69</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>-185.44</v>
+        <v>-205.56</v>
       </c>
       <c r="K17" t="n">
-        <v>-35.36</v>
+        <v>-39.19</v>
       </c>
       <c r="L17" t="n">
-        <v>188.78</v>
+        <v>209.26</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-61.05</v>
+        <v>-66.97</v>
       </c>
       <c r="K18" t="n">
-        <v>55.83</v>
+        <v>61.24</v>
       </c>
       <c r="L18" t="n">
-        <v>82.73</v>
+        <v>90.75</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>97.95</v>
+        <v>105.34</v>
       </c>
       <c r="K19" t="n">
-        <v>66.38</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>118.32</v>
+        <v>127.26</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>66.39</v>
+        <v>74.44</v>
       </c>
       <c r="K20" t="n">
-        <v>-189.67</v>
+        <v>-212.66</v>
       </c>
       <c r="L20" t="n">
-        <v>200.95</v>
+        <v>225.31</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>36.59</v>
+        <v>41.68</v>
       </c>
       <c r="K21" t="n">
-        <v>112.78</v>
+        <v>128.48</v>
       </c>
       <c r="L21" t="n">
-        <v>118.57</v>
+        <v>135.08</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-201.15</v>
+        <v>-227.12</v>
       </c>
       <c r="K22" t="n">
-        <v>71.58</v>
+        <v>80.81999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>213.51</v>
+        <v>241.07</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>55.46</v>
+        <v>63.49</v>
       </c>
       <c r="K23" t="n">
-        <v>253.89</v>
+        <v>290.65</v>
       </c>
       <c r="L23" t="n">
-        <v>259.88</v>
+        <v>297.51</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>128.45</v>
+        <v>148.73</v>
       </c>
       <c r="K24" t="n">
-        <v>-47.87</v>
+        <v>-55.42</v>
       </c>
       <c r="L24" t="n">
-        <v>137.08</v>
+        <v>158.72</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>181.5</v>
+        <v>209.43</v>
       </c>
       <c r="K25" t="n">
-        <v>15.94</v>
+        <v>18.4</v>
       </c>
       <c r="L25" t="n">
-        <v>182.2</v>
+        <v>210.24</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>267.05</v>
+        <v>309.35</v>
       </c>
       <c r="K26" t="n">
-        <v>211.28</v>
+        <v>244.74</v>
       </c>
       <c r="L26" t="n">
-        <v>340.53</v>
+        <v>394.46</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>333.28</v>
+        <v>389.89</v>
       </c>
       <c r="K27" t="n">
-        <v>170.1</v>
+        <v>198.99</v>
       </c>
       <c r="L27" t="n">
-        <v>374.17</v>
+        <v>437.73</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>321.15</v>
+        <v>374.05</v>
       </c>
       <c r="K28" t="n">
-        <v>-145.26</v>
+        <v>-169.18</v>
       </c>
       <c r="L28" t="n">
-        <v>352.47</v>
+        <v>410.53</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-23.12</v>
+        <v>-24.37</v>
       </c>
       <c r="K29" t="n">
-        <v>154.17</v>
+        <v>162.48</v>
       </c>
       <c r="L29" t="n">
-        <v>155.89</v>
+        <v>164.29</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>133.57</v>
+        <v>140.82</v>
       </c>
       <c r="K30" t="n">
-        <v>-17.98</v>
+        <v>-18.96</v>
       </c>
       <c r="L30" t="n">
-        <v>134.77</v>
+        <v>142.09</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-185.32</v>
+        <v>-197.62</v>
       </c>
       <c r="K31" t="n">
-        <v>-52.86</v>
+        <v>-56.37</v>
       </c>
       <c r="L31" t="n">
-        <v>192.71</v>
+        <v>205.5</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>23.92</v>
+        <v>26.1</v>
       </c>
       <c r="K32" t="n">
-        <v>113.25</v>
+        <v>123.58</v>
       </c>
       <c r="L32" t="n">
-        <v>115.75</v>
+        <v>126.31</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-141.77</v>
+        <v>-157.27</v>
       </c>
       <c r="K33" t="n">
-        <v>-123.52</v>
+        <v>-137.02</v>
       </c>
       <c r="L33" t="n">
-        <v>188.04</v>
+        <v>208.58</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>167.64</v>
+        <v>182.7</v>
       </c>
       <c r="K34" t="n">
-        <v>-41.37</v>
+        <v>-45.09</v>
       </c>
       <c r="L34" t="n">
-        <v>172.67</v>
+        <v>188.18</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-147.74</v>
+        <v>-167.89</v>
       </c>
       <c r="K35" t="n">
-        <v>15.21</v>
+        <v>17.28</v>
       </c>
       <c r="L35" t="n">
-        <v>148.52</v>
+        <v>168.78</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.24</v>
+        <v>-0.27</v>
       </c>
       <c r="K36" t="n">
-        <v>-221.45</v>
+        <v>-248.89</v>
       </c>
       <c r="L36" t="n">
-        <v>221.45</v>
+        <v>248.89</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>94.15000000000001</v>
+        <v>105.41</v>
       </c>
       <c r="K37" t="n">
-        <v>232.49</v>
+        <v>260.3</v>
       </c>
       <c r="L37" t="n">
-        <v>250.83</v>
+        <v>280.84</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-175.3</v>
+        <v>-204.37</v>
       </c>
       <c r="K38" t="n">
-        <v>100.31</v>
+        <v>116.94</v>
       </c>
       <c r="L38" t="n">
-        <v>201.97</v>
+        <v>235.46</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>196.39</v>
+        <v>227.93</v>
       </c>
       <c r="K39" t="n">
-        <v>-127.62</v>
+        <v>-148.12</v>
       </c>
       <c r="L39" t="n">
-        <v>234.21</v>
+        <v>271.83</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-200.71</v>
+        <v>-229.45</v>
       </c>
       <c r="K40" t="n">
-        <v>212.69</v>
+        <v>243.15</v>
       </c>
       <c r="L40" t="n">
-        <v>292.44</v>
+        <v>334.32</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>-184.48</v>
+        <v>-215.7</v>
       </c>
       <c r="K41" t="n">
-        <v>143.91</v>
+        <v>168.27</v>
       </c>
       <c r="L41" t="n">
-        <v>233.97</v>
+        <v>273.58</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-254.24</v>
+        <v>-296.94</v>
       </c>
       <c r="K42" t="n">
-        <v>-46.57</v>
+        <v>-54.39</v>
       </c>
       <c r="L42" t="n">
-        <v>258.47</v>
+        <v>301.88</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>301.18</v>
+        <v>350.89</v>
       </c>
       <c r="K43" t="n">
-        <v>-25.52</v>
+        <v>-29.73</v>
       </c>
       <c r="L43" t="n">
-        <v>302.26</v>
+        <v>352.14</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-98.33</v>
+        <v>-104.78</v>
       </c>
       <c r="K44" t="n">
-        <v>35.03</v>
+        <v>37.33</v>
       </c>
       <c r="L44" t="n">
-        <v>104.38</v>
+        <v>111.23</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>11.21</v>
+        <v>11.6</v>
       </c>
       <c r="K45" t="n">
-        <v>89.2</v>
+        <v>92.34</v>
       </c>
       <c r="L45" t="n">
-        <v>89.90000000000001</v>
+        <v>93.06</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>54.35</v>
+        <v>57.43</v>
       </c>
       <c r="K46" t="n">
-        <v>136.76</v>
+        <v>144.51</v>
       </c>
       <c r="L46" t="n">
-        <v>147.17</v>
+        <v>155.51</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>91.18000000000001</v>
+        <v>100.7</v>
       </c>
       <c r="K47" t="n">
-        <v>-64.39</v>
+        <v>-71.11</v>
       </c>
       <c r="L47" t="n">
-        <v>111.62</v>
+        <v>123.28</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>-161.44</v>
+        <v>-172.02</v>
       </c>
       <c r="K48" t="n">
-        <v>-8.49</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>161.66</v>
+        <v>172.26</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>108.72</v>
+        <v>120.02</v>
       </c>
       <c r="K49" t="n">
-        <v>-205.36</v>
+        <v>-226.71</v>
       </c>
       <c r="L49" t="n">
-        <v>232.36</v>
+        <v>256.51</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>149.39</v>
+        <v>169.8</v>
       </c>
       <c r="K50" t="n">
-        <v>-63.76</v>
+        <v>-72.45999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>162.43</v>
+        <v>184.61</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-107.04</v>
+        <v>-117.57</v>
       </c>
       <c r="K51" t="n">
-        <v>55.32</v>
+        <v>60.77</v>
       </c>
       <c r="L51" t="n">
-        <v>120.49</v>
+        <v>132.35</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-142.96</v>
+        <v>-162.4</v>
       </c>
       <c r="K52" t="n">
-        <v>-124.44</v>
+        <v>-141.36</v>
       </c>
       <c r="L52" t="n">
-        <v>189.53</v>
+        <v>215.3</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>134</v>
+        <v>157.88</v>
       </c>
       <c r="K53" t="n">
-        <v>-350.62</v>
+        <v>-413.12</v>
       </c>
       <c r="L53" t="n">
-        <v>375.35</v>
+        <v>442.26</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>101.68</v>
+        <v>119.18</v>
       </c>
       <c r="K54" t="n">
-        <v>389.54</v>
+        <v>456.57</v>
       </c>
       <c r="L54" t="n">
-        <v>402.59</v>
+        <v>471.87</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>88.06999999999999</v>
+        <v>103.43</v>
       </c>
       <c r="K55" t="n">
-        <v>-206.25</v>
+        <v>-242.23</v>
       </c>
       <c r="L55" t="n">
-        <v>224.26</v>
+        <v>263.38</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>181.12</v>
+        <v>213.63</v>
       </c>
       <c r="K56" t="n">
-        <v>418.03</v>
+        <v>493.06</v>
       </c>
       <c r="L56" t="n">
-        <v>455.58</v>
+        <v>537.35</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-419.94</v>
+        <v>-500.51</v>
       </c>
       <c r="K57" t="n">
-        <v>171.5</v>
+        <v>204.41</v>
       </c>
       <c r="L57" t="n">
-        <v>453.61</v>
+        <v>540.64</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-339.25</v>
+        <v>-389.3</v>
       </c>
       <c r="K58" t="n">
-        <v>148.93</v>
+        <v>170.9</v>
       </c>
       <c r="L58" t="n">
-        <v>370.5</v>
+        <v>425.16</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>142.27</v>
+        <v>150.81</v>
       </c>
       <c r="K59" t="n">
-        <v>115.46</v>
+        <v>122.39</v>
       </c>
       <c r="L59" t="n">
-        <v>183.23</v>
+        <v>194.22</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-95.78</v>
+        <v>-102.01</v>
       </c>
       <c r="K60" t="n">
-        <v>28.32</v>
+        <v>30.16</v>
       </c>
       <c r="L60" t="n">
-        <v>99.88</v>
+        <v>106.38</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>84.56999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="K61" t="n">
-        <v>-28.79</v>
+        <v>-29.91</v>
       </c>
       <c r="L61" t="n">
-        <v>89.33</v>
+        <v>92.83</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-88.73999999999999</v>
+        <v>-97.2</v>
       </c>
       <c r="K62" t="n">
-        <v>101.56</v>
+        <v>111.23</v>
       </c>
       <c r="L62" t="n">
-        <v>134.87</v>
+        <v>147.72</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>139.84</v>
+        <v>152.78</v>
       </c>
       <c r="K63" t="n">
-        <v>145.47</v>
+        <v>158.92</v>
       </c>
       <c r="L63" t="n">
-        <v>201.78</v>
+        <v>220.44</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-44.68</v>
+        <v>-49.09</v>
       </c>
       <c r="K64" t="n">
-        <v>75.95999999999999</v>
+        <v>83.47</v>
       </c>
       <c r="L64" t="n">
-        <v>88.12</v>
+        <v>96.84</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>-55.01</v>
+        <v>-63.11</v>
       </c>
       <c r="K65" t="n">
-        <v>-216.25</v>
+        <v>-248.11</v>
       </c>
       <c r="L65" t="n">
-        <v>223.14</v>
+        <v>256.01</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-178.31</v>
+        <v>-201.06</v>
       </c>
       <c r="K66" t="n">
-        <v>151.17</v>
+        <v>170.46</v>
       </c>
       <c r="L66" t="n">
-        <v>233.77</v>
+        <v>263.59</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>224.91</v>
+        <v>253.8</v>
       </c>
       <c r="K67" t="n">
-        <v>-56.77</v>
+        <v>-64.06</v>
       </c>
       <c r="L67" t="n">
-        <v>231.97</v>
+        <v>261.76</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-14.04</v>
+        <v>-16.19</v>
       </c>
       <c r="K68" t="n">
-        <v>364.13</v>
+        <v>419.92</v>
       </c>
       <c r="L68" t="n">
-        <v>364.4</v>
+        <v>420.24</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>247.03</v>
+        <v>287.54</v>
       </c>
       <c r="K69" t="n">
-        <v>-20.82</v>
+        <v>-24.24</v>
       </c>
       <c r="L69" t="n">
-        <v>247.9</v>
+        <v>288.56</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>6.33</v>
+        <v>7.21</v>
       </c>
       <c r="K70" t="n">
-        <v>-364.68</v>
+        <v>-415.52</v>
       </c>
       <c r="L70" t="n">
-        <v>364.74</v>
+        <v>415.59</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>247.5</v>
+        <v>288.99</v>
       </c>
       <c r="K71" t="n">
-        <v>-22.13</v>
+        <v>-25.85</v>
       </c>
       <c r="L71" t="n">
-        <v>248.48</v>
+        <v>290.15</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>72.86</v>
+        <v>86.81</v>
       </c>
       <c r="K72" t="n">
-        <v>-294.07</v>
+        <v>-350.39</v>
       </c>
       <c r="L72" t="n">
-        <v>302.96</v>
+        <v>360.98</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>195.33</v>
+        <v>227.35</v>
       </c>
       <c r="K73" t="n">
-        <v>-338.14</v>
+        <v>-393.57</v>
       </c>
       <c r="L73" t="n">
-        <v>390.5</v>
+        <v>454.52</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>-188.49</v>
+        <v>-199.96</v>
       </c>
       <c r="K74" t="n">
-        <v>-6.15</v>
+        <v>-6.52</v>
       </c>
       <c r="L74" t="n">
-        <v>188.59</v>
+        <v>200.07</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>37.22</v>
+        <v>40.34</v>
       </c>
       <c r="K75" t="n">
-        <v>-130.1</v>
+        <v>-140.99</v>
       </c>
       <c r="L75" t="n">
-        <v>135.32</v>
+        <v>146.65</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-40.02</v>
+        <v>-43.04</v>
       </c>
       <c r="K76" t="n">
-        <v>-102.42</v>
+        <v>-110.17</v>
       </c>
       <c r="L76" t="n">
-        <v>109.96</v>
+        <v>118.28</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>129.44</v>
+        <v>139.03</v>
       </c>
       <c r="K77" t="n">
-        <v>-158.94</v>
+        <v>-170.71</v>
       </c>
       <c r="L77" t="n">
-        <v>204.98</v>
+        <v>220.16</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-47.49</v>
+        <v>-52.65</v>
       </c>
       <c r="K78" t="n">
-        <v>158.6</v>
+        <v>175.85</v>
       </c>
       <c r="L78" t="n">
-        <v>165.56</v>
+        <v>183.56</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>49.02</v>
+        <v>53.02</v>
       </c>
       <c r="K79" t="n">
-        <v>-189.21</v>
+        <v>-204.63</v>
       </c>
       <c r="L79" t="n">
-        <v>195.46</v>
+        <v>211.39</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>145</v>
+        <v>162.98</v>
       </c>
       <c r="K80" t="n">
-        <v>131.3</v>
+        <v>147.59</v>
       </c>
       <c r="L80" t="n">
-        <v>195.61</v>
+        <v>219.87</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-204.22</v>
+        <v>-227.84</v>
       </c>
       <c r="K81" t="n">
-        <v>14.18</v>
+        <v>15.82</v>
       </c>
       <c r="L81" t="n">
-        <v>204.71</v>
+        <v>228.39</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-237.44</v>
+        <v>-272.49</v>
       </c>
       <c r="K82" t="n">
-        <v>-225.31</v>
+        <v>-258.57</v>
       </c>
       <c r="L82" t="n">
-        <v>327.32</v>
+        <v>375.64</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-208.14</v>
+        <v>-242.83</v>
       </c>
       <c r="K83" t="n">
-        <v>-76.95</v>
+        <v>-89.78</v>
       </c>
       <c r="L83" t="n">
-        <v>221.91</v>
+        <v>258.9</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-248.48</v>
+        <v>-283.69</v>
       </c>
       <c r="K84" t="n">
-        <v>-51.97</v>
+        <v>-59.33</v>
       </c>
       <c r="L84" t="n">
-        <v>253.86</v>
+        <v>289.83</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.32</v>
+        <v>-8.56</v>
       </c>
       <c r="K85" t="n">
-        <v>246.03</v>
+        <v>287.76</v>
       </c>
       <c r="L85" t="n">
-        <v>246.13</v>
+        <v>287.89</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-95.95</v>
+        <v>-114.39</v>
       </c>
       <c r="K86" t="n">
-        <v>-267.64</v>
+        <v>-319.1</v>
       </c>
       <c r="L86" t="n">
-        <v>284.32</v>
+        <v>338.99</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-470.83</v>
+        <v>-564.75</v>
       </c>
       <c r="K87" t="n">
-        <v>39.65</v>
+        <v>47.56</v>
       </c>
       <c r="L87" t="n">
-        <v>472.5</v>
+        <v>566.75</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>254.08</v>
+        <v>301.53</v>
       </c>
       <c r="K88" t="n">
-        <v>-554.66</v>
+        <v>-658.22</v>
       </c>
       <c r="L88" t="n">
-        <v>610.09</v>
+        <v>724</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-02.xlsx
+++ b/output/2024-04-02.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>18.79</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>110.74</v>
+        <v>55.68</v>
       </c>
       <c r="L14" t="n">
-        <v>112.32</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>-43</v>
+        <v>-24.24</v>
       </c>
       <c r="K15" t="n">
-        <v>85.39</v>
+        <v>48.14</v>
       </c>
       <c r="L15" t="n">
-        <v>95.61</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>-116.64</v>
+        <v>-64.42</v>
       </c>
       <c r="K16" t="n">
-        <v>3.43</v>
+        <v>1.9</v>
       </c>
       <c r="L16" t="n">
-        <v>116.69</v>
+        <v>64.44</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>-205.56</v>
+        <v>-116.2</v>
       </c>
       <c r="K17" t="n">
-        <v>-39.19</v>
+        <v>-22.15</v>
       </c>
       <c r="L17" t="n">
-        <v>209.26</v>
+        <v>118.29</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-66.97</v>
+        <v>-42.62</v>
       </c>
       <c r="K18" t="n">
-        <v>61.24</v>
+        <v>38.97</v>
       </c>
       <c r="L18" t="n">
-        <v>90.75</v>
+        <v>57.75</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>105.34</v>
+        <v>60.34</v>
       </c>
       <c r="K19" t="n">
-        <v>71.40000000000001</v>
+        <v>40.89</v>
       </c>
       <c r="L19" t="n">
-        <v>127.26</v>
+        <v>72.89</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>74.44</v>
+        <v>39.3</v>
       </c>
       <c r="K20" t="n">
-        <v>-212.66</v>
+        <v>-112.28</v>
       </c>
       <c r="L20" t="n">
-        <v>225.31</v>
+        <v>118.96</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>41.68</v>
+        <v>22.37</v>
       </c>
       <c r="K21" t="n">
-        <v>128.48</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>135.08</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-227.12</v>
+        <v>-121.4</v>
       </c>
       <c r="K22" t="n">
-        <v>80.81999999999999</v>
+        <v>43.2</v>
       </c>
       <c r="L22" t="n">
-        <v>241.07</v>
+        <v>128.85</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>63.49</v>
+        <v>34.26</v>
       </c>
       <c r="K23" t="n">
-        <v>290.65</v>
+        <v>156.85</v>
       </c>
       <c r="L23" t="n">
-        <v>297.51</v>
+        <v>160.54</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>148.73</v>
+        <v>21.02</v>
       </c>
       <c r="K24" t="n">
-        <v>-55.42</v>
+        <v>-7.83</v>
       </c>
       <c r="L24" t="n">
-        <v>158.72</v>
+        <v>22.43</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>209.43</v>
+        <v>124.94</v>
       </c>
       <c r="K25" t="n">
-        <v>18.4</v>
+        <v>10.97</v>
       </c>
       <c r="L25" t="n">
-        <v>210.24</v>
+        <v>125.42</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>309.35</v>
+        <v>183.61</v>
       </c>
       <c r="K26" t="n">
-        <v>244.74</v>
+        <v>145.26</v>
       </c>
       <c r="L26" t="n">
-        <v>394.46</v>
+        <v>234.12</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>389.89</v>
+        <v>219.65</v>
       </c>
       <c r="K27" t="n">
-        <v>198.99</v>
+        <v>112.1</v>
       </c>
       <c r="L27" t="n">
-        <v>437.73</v>
+        <v>246.6</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>374.05</v>
+        <v>207.68</v>
       </c>
       <c r="K28" t="n">
-        <v>-169.18</v>
+        <v>-93.94</v>
       </c>
       <c r="L28" t="n">
-        <v>410.53</v>
+        <v>227.94</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-24.37</v>
+        <v>-13</v>
       </c>
       <c r="K29" t="n">
-        <v>162.48</v>
+        <v>86.69</v>
       </c>
       <c r="L29" t="n">
-        <v>164.29</v>
+        <v>87.66</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>140.82</v>
+        <v>77.33</v>
       </c>
       <c r="K30" t="n">
-        <v>-18.96</v>
+        <v>-10.41</v>
       </c>
       <c r="L30" t="n">
-        <v>142.09</v>
+        <v>78.03</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-197.62</v>
+        <v>-97.94</v>
       </c>
       <c r="K31" t="n">
-        <v>-56.37</v>
+        <v>-27.94</v>
       </c>
       <c r="L31" t="n">
-        <v>205.5</v>
+        <v>101.85</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>26.1</v>
+        <v>14.06</v>
       </c>
       <c r="K32" t="n">
-        <v>123.58</v>
+        <v>66.58</v>
       </c>
       <c r="L32" t="n">
-        <v>126.31</v>
+        <v>68.05</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-157.27</v>
+        <v>-83.18000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>-137.02</v>
+        <v>-72.47</v>
       </c>
       <c r="L33" t="n">
-        <v>208.58</v>
+        <v>110.32</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>182.7</v>
+        <v>100.18</v>
       </c>
       <c r="K34" t="n">
-        <v>-45.09</v>
+        <v>-24.72</v>
       </c>
       <c r="L34" t="n">
-        <v>188.18</v>
+        <v>103.18</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-167.89</v>
+        <v>-87.76000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>17.28</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>168.78</v>
+        <v>88.22</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.27</v>
+        <v>-0.14</v>
       </c>
       <c r="K36" t="n">
-        <v>-248.89</v>
+        <v>-127.07</v>
       </c>
       <c r="L36" t="n">
-        <v>248.89</v>
+        <v>127.07</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>105.41</v>
+        <v>54.78</v>
       </c>
       <c r="K37" t="n">
-        <v>260.3</v>
+        <v>135.27</v>
       </c>
       <c r="L37" t="n">
-        <v>280.84</v>
+        <v>145.94</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-204.37</v>
+        <v>-103.12</v>
       </c>
       <c r="K38" t="n">
-        <v>116.94</v>
+        <v>59.01</v>
       </c>
       <c r="L38" t="n">
-        <v>235.46</v>
+        <v>118.81</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>227.93</v>
+        <v>130.64</v>
       </c>
       <c r="K39" t="n">
-        <v>-148.12</v>
+        <v>-84.89</v>
       </c>
       <c r="L39" t="n">
-        <v>271.83</v>
+        <v>155.8</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-229.45</v>
+        <v>-132.13</v>
       </c>
       <c r="K40" t="n">
-        <v>243.15</v>
+        <v>140.02</v>
       </c>
       <c r="L40" t="n">
-        <v>334.32</v>
+        <v>192.52</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>-215.7</v>
+        <v>-121.73</v>
       </c>
       <c r="K41" t="n">
-        <v>168.27</v>
+        <v>94.97</v>
       </c>
       <c r="L41" t="n">
-        <v>273.58</v>
+        <v>154.4</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-296.94</v>
+        <v>-165.86</v>
       </c>
       <c r="K42" t="n">
-        <v>-54.39</v>
+        <v>-30.38</v>
       </c>
       <c r="L42" t="n">
-        <v>301.88</v>
+        <v>168.62</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>350.89</v>
+        <v>195.89</v>
       </c>
       <c r="K43" t="n">
-        <v>-29.73</v>
+        <v>-16.6</v>
       </c>
       <c r="L43" t="n">
-        <v>352.14</v>
+        <v>196.59</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-104.78</v>
+        <v>-56.84</v>
       </c>
       <c r="K44" t="n">
-        <v>37.33</v>
+        <v>20.25</v>
       </c>
       <c r="L44" t="n">
-        <v>111.23</v>
+        <v>60.33</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>11.6</v>
+        <v>6.38</v>
       </c>
       <c r="K45" t="n">
-        <v>92.34</v>
+        <v>50.78</v>
       </c>
       <c r="L45" t="n">
-        <v>93.06</v>
+        <v>51.18</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>57.43</v>
+        <v>31.06</v>
       </c>
       <c r="K46" t="n">
-        <v>144.51</v>
+        <v>78.17</v>
       </c>
       <c r="L46" t="n">
-        <v>155.51</v>
+        <v>84.12</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>100.7</v>
+        <v>48.02</v>
       </c>
       <c r="K47" t="n">
-        <v>-71.11</v>
+        <v>-33.91</v>
       </c>
       <c r="L47" t="n">
-        <v>123.28</v>
+        <v>58.78</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>-172.02</v>
+        <v>-83.09999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>-9.039999999999999</v>
+        <v>-4.37</v>
       </c>
       <c r="L48" t="n">
-        <v>172.26</v>
+        <v>83.20999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>120.02</v>
+        <v>55.53</v>
       </c>
       <c r="K49" t="n">
-        <v>-226.71</v>
+        <v>-104.89</v>
       </c>
       <c r="L49" t="n">
-        <v>256.51</v>
+        <v>118.69</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>169.8</v>
+        <v>87.55</v>
       </c>
       <c r="K50" t="n">
-        <v>-72.45999999999999</v>
+        <v>-37.36</v>
       </c>
       <c r="L50" t="n">
-        <v>184.61</v>
+        <v>95.19</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-117.57</v>
+        <v>-67.94</v>
       </c>
       <c r="K51" t="n">
-        <v>60.77</v>
+        <v>35.12</v>
       </c>
       <c r="L51" t="n">
-        <v>132.35</v>
+        <v>76.48</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-162.4</v>
+        <v>-81.8</v>
       </c>
       <c r="K52" t="n">
-        <v>-141.36</v>
+        <v>-71.2</v>
       </c>
       <c r="L52" t="n">
-        <v>215.3</v>
+        <v>108.45</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>157.88</v>
+        <v>86.88</v>
       </c>
       <c r="K53" t="n">
-        <v>-413.12</v>
+        <v>-227.33</v>
       </c>
       <c r="L53" t="n">
-        <v>442.26</v>
+        <v>243.36</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>119.18</v>
+        <v>69.8</v>
       </c>
       <c r="K54" t="n">
-        <v>456.57</v>
+        <v>267.4</v>
       </c>
       <c r="L54" t="n">
-        <v>471.87</v>
+        <v>276.36</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>103.43</v>
+        <v>57.55</v>
       </c>
       <c r="K55" t="n">
-        <v>-242.23</v>
+        <v>-134.78</v>
       </c>
       <c r="L55" t="n">
-        <v>263.38</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>213.63</v>
+        <v>117.69</v>
       </c>
       <c r="K56" t="n">
-        <v>493.06</v>
+        <v>271.63</v>
       </c>
       <c r="L56" t="n">
-        <v>537.35</v>
+        <v>296.03</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-500.51</v>
+        <v>-277.6</v>
       </c>
       <c r="K57" t="n">
-        <v>204.41</v>
+        <v>113.37</v>
       </c>
       <c r="L57" t="n">
-        <v>540.64</v>
+        <v>299.86</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-389.3</v>
+        <v>-218.81</v>
       </c>
       <c r="K58" t="n">
-        <v>170.9</v>
+        <v>96.05</v>
       </c>
       <c r="L58" t="n">
-        <v>425.16</v>
+        <v>238.96</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>150.81</v>
+        <v>73.86</v>
       </c>
       <c r="K59" t="n">
-        <v>122.39</v>
+        <v>59.94</v>
       </c>
       <c r="L59" t="n">
-        <v>194.22</v>
+        <v>95.12</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-102.01</v>
+        <v>-60.63</v>
       </c>
       <c r="K60" t="n">
-        <v>30.16</v>
+        <v>17.93</v>
       </c>
       <c r="L60" t="n">
-        <v>106.38</v>
+        <v>63.22</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>87.88</v>
+        <v>47.41</v>
       </c>
       <c r="K61" t="n">
-        <v>-29.91</v>
+        <v>-16.14</v>
       </c>
       <c r="L61" t="n">
-        <v>92.83</v>
+        <v>50.08</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-97.2</v>
+        <v>-47.31</v>
       </c>
       <c r="K62" t="n">
-        <v>111.23</v>
+        <v>54.14</v>
       </c>
       <c r="L62" t="n">
-        <v>147.72</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>152.78</v>
+        <v>75.67</v>
       </c>
       <c r="K63" t="n">
-        <v>158.92</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>220.44</v>
+        <v>109.19</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-49.09</v>
+        <v>-26.02</v>
       </c>
       <c r="K64" t="n">
-        <v>83.47</v>
+        <v>44.25</v>
       </c>
       <c r="L64" t="n">
-        <v>96.84</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>-63.11</v>
+        <v>-31.13</v>
       </c>
       <c r="K65" t="n">
-        <v>-248.11</v>
+        <v>-122.36</v>
       </c>
       <c r="L65" t="n">
-        <v>256.01</v>
+        <v>126.26</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-201.06</v>
+        <v>-103.05</v>
       </c>
       <c r="K66" t="n">
-        <v>170.46</v>
+        <v>87.36</v>
       </c>
       <c r="L66" t="n">
-        <v>263.59</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>253.8</v>
+        <v>129.49</v>
       </c>
       <c r="K67" t="n">
-        <v>-64.06</v>
+        <v>-32.68</v>
       </c>
       <c r="L67" t="n">
-        <v>261.76</v>
+        <v>133.55</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-16.19</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>419.92</v>
+        <v>232.61</v>
       </c>
       <c r="L68" t="n">
-        <v>420.24</v>
+        <v>232.78</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>287.54</v>
+        <v>152.57</v>
       </c>
       <c r="K69" t="n">
-        <v>-24.24</v>
+        <v>-12.86</v>
       </c>
       <c r="L69" t="n">
-        <v>288.56</v>
+        <v>153.11</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>7.21</v>
+        <v>4.18</v>
       </c>
       <c r="K70" t="n">
-        <v>-415.52</v>
+        <v>-240.73</v>
       </c>
       <c r="L70" t="n">
-        <v>415.59</v>
+        <v>240.77</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>288.99</v>
+        <v>160.8</v>
       </c>
       <c r="K71" t="n">
-        <v>-25.85</v>
+        <v>-14.38</v>
       </c>
       <c r="L71" t="n">
-        <v>290.15</v>
+        <v>161.45</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>86.81</v>
+        <v>47.92</v>
       </c>
       <c r="K72" t="n">
-        <v>-350.39</v>
+        <v>-193.43</v>
       </c>
       <c r="L72" t="n">
-        <v>360.98</v>
+        <v>199.27</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>227.35</v>
+        <v>126.17</v>
       </c>
       <c r="K73" t="n">
-        <v>-393.57</v>
+        <v>-218.41</v>
       </c>
       <c r="L73" t="n">
-        <v>454.52</v>
+        <v>252.23</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>-199.96</v>
+        <v>-102.06</v>
       </c>
       <c r="K74" t="n">
-        <v>-6.52</v>
+        <v>-3.33</v>
       </c>
       <c r="L74" t="n">
-        <v>200.07</v>
+        <v>102.12</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>40.34</v>
+        <v>17.45</v>
       </c>
       <c r="K75" t="n">
-        <v>-140.99</v>
+        <v>-60.98</v>
       </c>
       <c r="L75" t="n">
-        <v>146.65</v>
+        <v>63.43</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-43.04</v>
+        <v>-19.36</v>
       </c>
       <c r="K76" t="n">
-        <v>-110.17</v>
+        <v>-49.55</v>
       </c>
       <c r="L76" t="n">
-        <v>118.28</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>139.03</v>
+        <v>64.44</v>
       </c>
       <c r="K77" t="n">
-        <v>-170.71</v>
+        <v>-79.12</v>
       </c>
       <c r="L77" t="n">
-        <v>220.16</v>
+        <v>102.04</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-52.65</v>
+        <v>-23.31</v>
       </c>
       <c r="K78" t="n">
-        <v>175.85</v>
+        <v>77.86</v>
       </c>
       <c r="L78" t="n">
-        <v>183.56</v>
+        <v>81.28</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>53.02</v>
+        <v>25.66</v>
       </c>
       <c r="K79" t="n">
-        <v>-204.63</v>
+        <v>-99.03</v>
       </c>
       <c r="L79" t="n">
-        <v>211.39</v>
+        <v>102.3</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>162.98</v>
+        <v>82.69</v>
       </c>
       <c r="K80" t="n">
-        <v>147.59</v>
+        <v>74.88</v>
       </c>
       <c r="L80" t="n">
-        <v>219.87</v>
+        <v>111.55</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-227.84</v>
+        <v>-114.44</v>
       </c>
       <c r="K81" t="n">
-        <v>15.82</v>
+        <v>7.95</v>
       </c>
       <c r="L81" t="n">
-        <v>228.39</v>
+        <v>114.71</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-272.49</v>
+        <v>-134.93</v>
       </c>
       <c r="K82" t="n">
-        <v>-258.57</v>
+        <v>-128.04</v>
       </c>
       <c r="L82" t="n">
-        <v>375.64</v>
+        <v>186.02</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-242.83</v>
+        <v>-126.48</v>
       </c>
       <c r="K83" t="n">
-        <v>-89.78</v>
+        <v>-46.76</v>
       </c>
       <c r="L83" t="n">
-        <v>258.9</v>
+        <v>134.85</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-283.69</v>
+        <v>-164.14</v>
       </c>
       <c r="K84" t="n">
-        <v>-59.33</v>
+        <v>-34.33</v>
       </c>
       <c r="L84" t="n">
-        <v>289.83</v>
+        <v>167.69</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>-8.56</v>
+        <v>-4.66</v>
       </c>
       <c r="K85" t="n">
-        <v>287.76</v>
+        <v>156.63</v>
       </c>
       <c r="L85" t="n">
-        <v>287.89</v>
+        <v>156.7</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-114.39</v>
+        <v>-61.97</v>
       </c>
       <c r="K86" t="n">
-        <v>-319.1</v>
+        <v>-172.86</v>
       </c>
       <c r="L86" t="n">
-        <v>338.99</v>
+        <v>183.64</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-564.75</v>
+        <v>-310.03</v>
       </c>
       <c r="K87" t="n">
-        <v>47.56</v>
+        <v>26.11</v>
       </c>
       <c r="L87" t="n">
-        <v>566.75</v>
+        <v>311.13</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>301.53</v>
+        <v>168.24</v>
       </c>
       <c r="K88" t="n">
-        <v>-658.22</v>
+        <v>-367.26</v>
       </c>
       <c r="L88" t="n">
-        <v>724</v>
+        <v>403.96</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-02.xlsx
+++ b/output/2024-04-02.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>9.449999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="K14" t="n">
-        <v>55.68</v>
+        <v>56.84</v>
       </c>
       <c r="L14" t="n">
-        <v>56.48</v>
+        <v>57.65</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>-24.24</v>
+        <v>-24.96</v>
       </c>
       <c r="K15" t="n">
-        <v>48.14</v>
+        <v>49.58</v>
       </c>
       <c r="L15" t="n">
-        <v>53.9</v>
+        <v>55.51</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>-64.42</v>
+        <v>-65.38</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="L16" t="n">
-        <v>64.44</v>
+        <v>65.41</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>-116.2</v>
+        <v>-112.1</v>
       </c>
       <c r="K17" t="n">
-        <v>-22.15</v>
+        <v>-21.37</v>
       </c>
       <c r="L17" t="n">
-        <v>118.29</v>
+        <v>114.12</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-42.62</v>
+        <v>-44.49</v>
       </c>
       <c r="K18" t="n">
-        <v>38.97</v>
+        <v>40.68</v>
       </c>
       <c r="L18" t="n">
-        <v>57.75</v>
+        <v>60.29</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>60.34</v>
+        <v>60.59</v>
       </c>
       <c r="K19" t="n">
-        <v>40.89</v>
+        <v>41.06</v>
       </c>
       <c r="L19" t="n">
-        <v>72.89</v>
+        <v>73.19</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>39.3</v>
+        <v>39.01</v>
       </c>
       <c r="K20" t="n">
-        <v>-112.28</v>
+        <v>-111.45</v>
       </c>
       <c r="L20" t="n">
-        <v>118.96</v>
+        <v>118.08</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>22.37</v>
+        <v>24.15</v>
       </c>
       <c r="K21" t="n">
-        <v>68.95999999999999</v>
+        <v>74.45</v>
       </c>
       <c r="L21" t="n">
-        <v>72.5</v>
+        <v>78.27</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-121.4</v>
+        <v>-114.11</v>
       </c>
       <c r="K22" t="n">
-        <v>43.2</v>
+        <v>40.61</v>
       </c>
       <c r="L22" t="n">
-        <v>128.85</v>
+        <v>121.12</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>34.26</v>
+        <v>34.41</v>
       </c>
       <c r="K23" t="n">
-        <v>156.85</v>
+        <v>157.53</v>
       </c>
       <c r="L23" t="n">
-        <v>160.54</v>
+        <v>161.25</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>21.02</v>
+        <v>20.78</v>
       </c>
       <c r="K24" t="n">
-        <v>-7.83</v>
+        <v>-7.74</v>
       </c>
       <c r="L24" t="n">
-        <v>22.43</v>
+        <v>22.18</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>124.94</v>
+        <v>128.62</v>
       </c>
       <c r="K25" t="n">
-        <v>10.97</v>
+        <v>11.3</v>
       </c>
       <c r="L25" t="n">
-        <v>125.42</v>
+        <v>129.12</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>183.61</v>
+        <v>180.65</v>
       </c>
       <c r="K26" t="n">
-        <v>145.26</v>
+        <v>142.92</v>
       </c>
       <c r="L26" t="n">
-        <v>234.12</v>
+        <v>230.35</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>219.65</v>
+        <v>218.47</v>
       </c>
       <c r="K27" t="n">
-        <v>112.1</v>
+        <v>111.5</v>
       </c>
       <c r="L27" t="n">
-        <v>246.6</v>
+        <v>245.28</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>207.68</v>
+        <v>211.59</v>
       </c>
       <c r="K28" t="n">
-        <v>-93.94</v>
+        <v>-95.7</v>
       </c>
       <c r="L28" t="n">
-        <v>227.94</v>
+        <v>232.22</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-13</v>
+        <v>-12.66</v>
       </c>
       <c r="K29" t="n">
-        <v>86.69</v>
+        <v>84.45</v>
       </c>
       <c r="L29" t="n">
-        <v>87.66</v>
+        <v>85.39</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>77.33</v>
+        <v>76.73</v>
       </c>
       <c r="K30" t="n">
-        <v>-10.41</v>
+        <v>-10.33</v>
       </c>
       <c r="L30" t="n">
-        <v>78.03</v>
+        <v>77.42</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-97.94</v>
+        <v>-93.53</v>
       </c>
       <c r="K31" t="n">
-        <v>-27.94</v>
+        <v>-26.68</v>
       </c>
       <c r="L31" t="n">
-        <v>101.85</v>
+        <v>97.27</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>14.06</v>
+        <v>14.34</v>
       </c>
       <c r="K32" t="n">
-        <v>66.58</v>
+        <v>67.89</v>
       </c>
       <c r="L32" t="n">
-        <v>68.05</v>
+        <v>69.39</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-83.18000000000001</v>
+        <v>-80.7</v>
       </c>
       <c r="K33" t="n">
-        <v>-72.47</v>
+        <v>-70.31</v>
       </c>
       <c r="L33" t="n">
-        <v>110.32</v>
+        <v>107.03</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>100.18</v>
+        <v>97.48</v>
       </c>
       <c r="K34" t="n">
-        <v>-24.72</v>
+        <v>-24.06</v>
       </c>
       <c r="L34" t="n">
-        <v>103.18</v>
+        <v>100.41</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-87.76000000000001</v>
+        <v>-91.06</v>
       </c>
       <c r="K35" t="n">
-        <v>9.029999999999999</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>88.22</v>
+        <v>91.54000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1567,10 +1567,10 @@
         <v>-0.14</v>
       </c>
       <c r="K36" t="n">
-        <v>-127.07</v>
+        <v>-125.49</v>
       </c>
       <c r="L36" t="n">
-        <v>127.07</v>
+        <v>125.49</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>54.78</v>
+        <v>53.07</v>
       </c>
       <c r="K37" t="n">
-        <v>135.27</v>
+        <v>131.05</v>
       </c>
       <c r="L37" t="n">
-        <v>145.94</v>
+        <v>141.39</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-103.12</v>
+        <v>-109.54</v>
       </c>
       <c r="K38" t="n">
-        <v>59.01</v>
+        <v>62.68</v>
       </c>
       <c r="L38" t="n">
-        <v>118.81</v>
+        <v>126.2</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>130.64</v>
+        <v>131.83</v>
       </c>
       <c r="K39" t="n">
-        <v>-84.89</v>
+        <v>-85.67</v>
       </c>
       <c r="L39" t="n">
-        <v>155.8</v>
+        <v>157.22</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-132.13</v>
+        <v>-129.57</v>
       </c>
       <c r="K40" t="n">
-        <v>140.02</v>
+        <v>137.3</v>
       </c>
       <c r="L40" t="n">
-        <v>192.52</v>
+        <v>188.78</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>-121.73</v>
+        <v>-127.87</v>
       </c>
       <c r="K41" t="n">
-        <v>94.97</v>
+        <v>99.75</v>
       </c>
       <c r="L41" t="n">
-        <v>154.4</v>
+        <v>162.18</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-165.86</v>
+        <v>-174.68</v>
       </c>
       <c r="K42" t="n">
-        <v>-30.38</v>
+        <v>-32</v>
       </c>
       <c r="L42" t="n">
-        <v>168.62</v>
+        <v>177.59</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>195.89</v>
+        <v>200.64</v>
       </c>
       <c r="K43" t="n">
-        <v>-16.6</v>
+        <v>-17</v>
       </c>
       <c r="L43" t="n">
-        <v>196.59</v>
+        <v>201.36</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-56.84</v>
+        <v>-58.44</v>
       </c>
       <c r="K44" t="n">
-        <v>20.25</v>
+        <v>20.82</v>
       </c>
       <c r="L44" t="n">
-        <v>60.33</v>
+        <v>62.03</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>6.38</v>
+        <v>6.6</v>
       </c>
       <c r="K45" t="n">
-        <v>50.78</v>
+        <v>52.5</v>
       </c>
       <c r="L45" t="n">
-        <v>51.18</v>
+        <v>52.91</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>31.06</v>
+        <v>30.48</v>
       </c>
       <c r="K46" t="n">
-        <v>78.17</v>
+        <v>76.69</v>
       </c>
       <c r="L46" t="n">
-        <v>84.12</v>
+        <v>82.52</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>48.02</v>
+        <v>50.38</v>
       </c>
       <c r="K47" t="n">
-        <v>-33.91</v>
+        <v>-35.57</v>
       </c>
       <c r="L47" t="n">
-        <v>58.78</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>-83.09999999999999</v>
+        <v>-81.37</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.37</v>
+        <v>-4.28</v>
       </c>
       <c r="L48" t="n">
-        <v>83.20999999999999</v>
+        <v>81.48999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>55.53</v>
+        <v>52.8</v>
       </c>
       <c r="K49" t="n">
-        <v>-104.89</v>
+        <v>-99.73</v>
       </c>
       <c r="L49" t="n">
-        <v>118.69</v>
+        <v>112.84</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>87.55</v>
+        <v>90.05</v>
       </c>
       <c r="K50" t="n">
-        <v>-37.36</v>
+        <v>-38.43</v>
       </c>
       <c r="L50" t="n">
-        <v>95.19</v>
+        <v>97.91</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-67.94</v>
+        <v>-70.48999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>35.12</v>
+        <v>36.43</v>
       </c>
       <c r="L51" t="n">
-        <v>76.48</v>
+        <v>79.34999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-81.8</v>
+        <v>-82.81</v>
       </c>
       <c r="K52" t="n">
-        <v>-71.2</v>
+        <v>-72.08</v>
       </c>
       <c r="L52" t="n">
-        <v>108.45</v>
+        <v>109.79</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>86.88</v>
+        <v>83.95</v>
       </c>
       <c r="K53" t="n">
-        <v>-227.33</v>
+        <v>-219.66</v>
       </c>
       <c r="L53" t="n">
-        <v>243.36</v>
+        <v>235.15</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>69.8</v>
+        <v>66.42</v>
       </c>
       <c r="K54" t="n">
-        <v>267.4</v>
+        <v>254.46</v>
       </c>
       <c r="L54" t="n">
-        <v>276.36</v>
+        <v>262.99</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>57.55</v>
+        <v>58.86</v>
       </c>
       <c r="K55" t="n">
-        <v>-134.78</v>
+        <v>-137.85</v>
       </c>
       <c r="L55" t="n">
-        <v>146.55</v>
+        <v>149.89</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>117.69</v>
+        <v>117.79</v>
       </c>
       <c r="K56" t="n">
-        <v>271.63</v>
+        <v>271.86</v>
       </c>
       <c r="L56" t="n">
-        <v>296.03</v>
+        <v>296.28</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-277.6</v>
+        <v>-276.6</v>
       </c>
       <c r="K57" t="n">
-        <v>113.37</v>
+        <v>112.96</v>
       </c>
       <c r="L57" t="n">
-        <v>299.86</v>
+        <v>298.78</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-218.81</v>
+        <v>-216.63</v>
       </c>
       <c r="K58" t="n">
-        <v>96.05</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>238.96</v>
+        <v>236.58</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>73.86</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>59.94</v>
+        <v>57.47</v>
       </c>
       <c r="L59" t="n">
-        <v>95.12</v>
+        <v>91.20999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-60.63</v>
+        <v>-61.1</v>
       </c>
       <c r="K60" t="n">
-        <v>17.93</v>
+        <v>18.06</v>
       </c>
       <c r="L60" t="n">
-        <v>63.22</v>
+        <v>63.71</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>47.41</v>
+        <v>49.59</v>
       </c>
       <c r="K61" t="n">
-        <v>-16.14</v>
+        <v>-16.88</v>
       </c>
       <c r="L61" t="n">
-        <v>50.08</v>
+        <v>52.38</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-47.31</v>
+        <v>-47.79</v>
       </c>
       <c r="K62" t="n">
-        <v>54.14</v>
+        <v>54.69</v>
       </c>
       <c r="L62" t="n">
-        <v>71.90000000000001</v>
+        <v>72.63</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>75.67</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>78.70999999999999</v>
+        <v>75.69</v>
       </c>
       <c r="L63" t="n">
-        <v>109.19</v>
+        <v>104.99</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-26.02</v>
+        <v>-27.95</v>
       </c>
       <c r="K64" t="n">
-        <v>44.25</v>
+        <v>47.53</v>
       </c>
       <c r="L64" t="n">
-        <v>51.33</v>
+        <v>55.14</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>-31.13</v>
+        <v>-31.22</v>
       </c>
       <c r="K65" t="n">
-        <v>-122.36</v>
+        <v>-122.75</v>
       </c>
       <c r="L65" t="n">
-        <v>126.26</v>
+        <v>126.66</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-103.05</v>
+        <v>-101.17</v>
       </c>
       <c r="K66" t="n">
-        <v>87.36</v>
+        <v>85.77</v>
       </c>
       <c r="L66" t="n">
-        <v>135.1</v>
+        <v>132.63</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>129.49</v>
+        <v>127.15</v>
       </c>
       <c r="K67" t="n">
-        <v>-32.68</v>
+        <v>-32.09</v>
       </c>
       <c r="L67" t="n">
-        <v>133.55</v>
+        <v>131.14</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-8.970000000000001</v>
+        <v>-8.66</v>
       </c>
       <c r="K68" t="n">
-        <v>232.61</v>
+        <v>224.5</v>
       </c>
       <c r="L68" t="n">
-        <v>232.78</v>
+        <v>224.66</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>152.57</v>
+        <v>155.11</v>
       </c>
       <c r="K69" t="n">
-        <v>-12.86</v>
+        <v>-13.07</v>
       </c>
       <c r="L69" t="n">
-        <v>153.11</v>
+        <v>155.66</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>4.18</v>
+        <v>4.01</v>
       </c>
       <c r="K70" t="n">
-        <v>-240.73</v>
+        <v>-230.79</v>
       </c>
       <c r="L70" t="n">
-        <v>240.77</v>
+        <v>230.82</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>160.8</v>
+        <v>172.09</v>
       </c>
       <c r="K71" t="n">
-        <v>-14.38</v>
+        <v>-15.39</v>
       </c>
       <c r="L71" t="n">
-        <v>161.45</v>
+        <v>172.77</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>47.92</v>
+        <v>50.68</v>
       </c>
       <c r="K72" t="n">
-        <v>-193.43</v>
+        <v>-204.57</v>
       </c>
       <c r="L72" t="n">
-        <v>199.27</v>
+        <v>210.76</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>126.17</v>
+        <v>126.98</v>
       </c>
       <c r="K73" t="n">
-        <v>-218.41</v>
+        <v>-219.82</v>
       </c>
       <c r="L73" t="n">
-        <v>252.23</v>
+        <v>253.86</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>-102.06</v>
+        <v>-97.76000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-3.33</v>
+        <v>-3.19</v>
       </c>
       <c r="L74" t="n">
-        <v>102.12</v>
+        <v>97.81999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>17.45</v>
+        <v>17.48</v>
       </c>
       <c r="K75" t="n">
-        <v>-60.98</v>
+        <v>-61.1</v>
       </c>
       <c r="L75" t="n">
-        <v>63.43</v>
+        <v>63.55</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-19.36</v>
+        <v>-20.12</v>
       </c>
       <c r="K76" t="n">
-        <v>-49.55</v>
+        <v>-51.48</v>
       </c>
       <c r="L76" t="n">
-        <v>53.2</v>
+        <v>55.27</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>64.44</v>
+        <v>61.94</v>
       </c>
       <c r="K77" t="n">
-        <v>-79.12</v>
+        <v>-76.06</v>
       </c>
       <c r="L77" t="n">
-        <v>102.04</v>
+        <v>98.09</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-23.31</v>
+        <v>-23.24</v>
       </c>
       <c r="K78" t="n">
-        <v>77.86</v>
+        <v>77.62</v>
       </c>
       <c r="L78" t="n">
-        <v>81.28</v>
+        <v>81.02</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>25.66</v>
+        <v>24.75</v>
       </c>
       <c r="K79" t="n">
-        <v>-99.03</v>
+        <v>-95.51000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>102.3</v>
+        <v>98.66</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>82.69</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>74.88</v>
+        <v>75.39</v>
       </c>
       <c r="L80" t="n">
-        <v>111.55</v>
+        <v>112.32</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-114.44</v>
+        <v>-114.68</v>
       </c>
       <c r="K81" t="n">
-        <v>7.95</v>
+        <v>7.96</v>
       </c>
       <c r="L81" t="n">
-        <v>114.71</v>
+        <v>114.95</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-134.93</v>
+        <v>-129.84</v>
       </c>
       <c r="K82" t="n">
-        <v>-128.04</v>
+        <v>-123.21</v>
       </c>
       <c r="L82" t="n">
-        <v>186.02</v>
+        <v>179</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-126.48</v>
+        <v>-131.7</v>
       </c>
       <c r="K83" t="n">
-        <v>-46.76</v>
+        <v>-48.69</v>
       </c>
       <c r="L83" t="n">
-        <v>134.85</v>
+        <v>140.42</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-164.14</v>
+        <v>-162.9</v>
       </c>
       <c r="K84" t="n">
-        <v>-34.33</v>
+        <v>-34.07</v>
       </c>
       <c r="L84" t="n">
-        <v>167.69</v>
+        <v>166.43</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.66</v>
+        <v>-4.74</v>
       </c>
       <c r="K85" t="n">
-        <v>156.63</v>
+        <v>159.41</v>
       </c>
       <c r="L85" t="n">
-        <v>156.7</v>
+        <v>159.48</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-61.97</v>
+        <v>-68.04000000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>-172.86</v>
+        <v>-189.8</v>
       </c>
       <c r="L86" t="n">
-        <v>183.64</v>
+        <v>201.62</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-310.03</v>
+        <v>-313.22</v>
       </c>
       <c r="K87" t="n">
-        <v>26.11</v>
+        <v>26.38</v>
       </c>
       <c r="L87" t="n">
-        <v>311.13</v>
+        <v>314.33</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>168.24</v>
+        <v>162.39</v>
       </c>
       <c r="K88" t="n">
-        <v>-367.26</v>
+        <v>-354.5</v>
       </c>
       <c r="L88" t="n">
-        <v>403.96</v>
+        <v>389.93</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-02.xlsx
+++ b/output/2024-04-02.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>9.65</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>56.84</v>
+        <v>58.73</v>
       </c>
       <c r="L14" t="n">
-        <v>57.65</v>
+        <v>59.57</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>-24.96</v>
+        <v>-25.79</v>
       </c>
       <c r="K15" t="n">
-        <v>49.58</v>
+        <v>51.23</v>
       </c>
       <c r="L15" t="n">
-        <v>55.51</v>
+        <v>57.36</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>-65.38</v>
+        <v>-66.48</v>
       </c>
       <c r="K16" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="L16" t="n">
-        <v>65.41</v>
+        <v>66.51000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>-112.1</v>
+        <v>-107.42</v>
       </c>
       <c r="K17" t="n">
-        <v>-21.37</v>
+        <v>-20.48</v>
       </c>
       <c r="L17" t="n">
-        <v>114.12</v>
+        <v>109.35</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-44.49</v>
+        <v>-46.63</v>
       </c>
       <c r="K18" t="n">
-        <v>40.68</v>
+        <v>42.64</v>
       </c>
       <c r="L18" t="n">
-        <v>60.29</v>
+        <v>63.18</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>60.59</v>
+        <v>60.87</v>
       </c>
       <c r="K19" t="n">
-        <v>41.06</v>
+        <v>41.26</v>
       </c>
       <c r="L19" t="n">
-        <v>73.19</v>
+        <v>73.54000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>39.01</v>
+        <v>38.68</v>
       </c>
       <c r="K20" t="n">
-        <v>-111.45</v>
+        <v>-110.51</v>
       </c>
       <c r="L20" t="n">
-        <v>118.08</v>
+        <v>117.08</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>24.15</v>
+        <v>26.19</v>
       </c>
       <c r="K21" t="n">
-        <v>74.45</v>
+        <v>80.72</v>
       </c>
       <c r="L21" t="n">
-        <v>78.27</v>
+        <v>84.86</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-114.11</v>
+        <v>-115.04</v>
       </c>
       <c r="K22" t="n">
-        <v>40.61</v>
+        <v>40.94</v>
       </c>
       <c r="L22" t="n">
-        <v>121.12</v>
+        <v>122.1</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>34.41</v>
+        <v>34.49</v>
       </c>
       <c r="K23" t="n">
-        <v>157.53</v>
+        <v>157.91</v>
       </c>
       <c r="L23" t="n">
-        <v>161.25</v>
+        <v>161.63</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>20.78</v>
+        <v>22.2</v>
       </c>
       <c r="K24" t="n">
-        <v>-7.74</v>
+        <v>-8.27</v>
       </c>
       <c r="L24" t="n">
-        <v>22.18</v>
+        <v>23.69</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>128.62</v>
+        <v>132.83</v>
       </c>
       <c r="K25" t="n">
-        <v>11.3</v>
+        <v>11.67</v>
       </c>
       <c r="L25" t="n">
-        <v>129.12</v>
+        <v>133.34</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>180.65</v>
+        <v>177.27</v>
       </c>
       <c r="K26" t="n">
-        <v>142.92</v>
+        <v>140.25</v>
       </c>
       <c r="L26" t="n">
-        <v>230.35</v>
+        <v>226.04</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>218.47</v>
+        <v>215.62</v>
       </c>
       <c r="K27" t="n">
-        <v>111.5</v>
+        <v>110.05</v>
       </c>
       <c r="L27" t="n">
-        <v>245.28</v>
+        <v>242.08</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>211.59</v>
+        <v>211.48</v>
       </c>
       <c r="K28" t="n">
-        <v>-95.7</v>
+        <v>-95.65000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>232.22</v>
+        <v>232.1</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-12.66</v>
+        <v>-12.32</v>
       </c>
       <c r="K29" t="n">
-        <v>84.45</v>
+        <v>82.13</v>
       </c>
       <c r="L29" t="n">
-        <v>85.39</v>
+        <v>83.05</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
+        <v>76.04000000000001</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-10.24</v>
+      </c>
+      <c r="L30" t="n">
         <v>76.73</v>
-      </c>
-      <c r="K30" t="n">
-        <v>-10.33</v>
-      </c>
-      <c r="L30" t="n">
-        <v>77.42</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-93.53</v>
+        <v>-89.73</v>
       </c>
       <c r="K31" t="n">
-        <v>-26.68</v>
+        <v>-25.6</v>
       </c>
       <c r="L31" t="n">
-        <v>97.27</v>
+        <v>93.31</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>14.34</v>
+        <v>14.66</v>
       </c>
       <c r="K32" t="n">
-        <v>67.89</v>
+        <v>69.41</v>
       </c>
       <c r="L32" t="n">
-        <v>69.39</v>
+        <v>70.94</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-80.7</v>
+        <v>-78.13</v>
       </c>
       <c r="K33" t="n">
-        <v>-70.31</v>
+        <v>-68.08</v>
       </c>
       <c r="L33" t="n">
-        <v>107.03</v>
+        <v>103.63</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>97.48</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>-24.06</v>
+        <v>-23.3</v>
       </c>
       <c r="L34" t="n">
-        <v>100.41</v>
+        <v>97.23</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-91.06</v>
+        <v>-94.83</v>
       </c>
       <c r="K35" t="n">
-        <v>9.369999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="L35" t="n">
-        <v>91.54000000000001</v>
+        <v>95.34</v>
       </c>
     </row>
     <row r="36">
@@ -1567,10 +1567,10 @@
         <v>-0.14</v>
       </c>
       <c r="K36" t="n">
-        <v>-125.49</v>
+        <v>-123.94</v>
       </c>
       <c r="L36" t="n">
-        <v>125.49</v>
+        <v>123.94</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>53.07</v>
+        <v>51.12</v>
       </c>
       <c r="K37" t="n">
-        <v>131.05</v>
+        <v>126.23</v>
       </c>
       <c r="L37" t="n">
-        <v>141.39</v>
+        <v>136.19</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-109.54</v>
+        <v>-116.34</v>
       </c>
       <c r="K38" t="n">
-        <v>62.68</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>126.2</v>
+        <v>134.04</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>131.83</v>
+        <v>133.14</v>
       </c>
       <c r="K39" t="n">
-        <v>-85.67</v>
+        <v>-86.52</v>
       </c>
       <c r="L39" t="n">
-        <v>157.22</v>
+        <v>158.78</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-129.57</v>
+        <v>-126.61</v>
       </c>
       <c r="K40" t="n">
-        <v>137.3</v>
+        <v>134.17</v>
       </c>
       <c r="L40" t="n">
-        <v>188.78</v>
+        <v>184.48</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>-127.87</v>
+        <v>-134.29</v>
       </c>
       <c r="K41" t="n">
-        <v>99.75</v>
+        <v>104.76</v>
       </c>
       <c r="L41" t="n">
-        <v>162.18</v>
+        <v>170.31</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-174.68</v>
+        <v>-182.17</v>
       </c>
       <c r="K42" t="n">
-        <v>-32</v>
+        <v>-33.37</v>
       </c>
       <c r="L42" t="n">
-        <v>177.59</v>
+        <v>185.21</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>200.64</v>
+        <v>202.88</v>
       </c>
       <c r="K43" t="n">
-        <v>-17</v>
+        <v>-17.19</v>
       </c>
       <c r="L43" t="n">
-        <v>201.36</v>
+        <v>203.61</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-58.44</v>
+        <v>-60.31</v>
       </c>
       <c r="K44" t="n">
-        <v>20.82</v>
+        <v>21.48</v>
       </c>
       <c r="L44" t="n">
-        <v>62.03</v>
+        <v>64.02</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>6.6</v>
+        <v>6.84</v>
       </c>
       <c r="K45" t="n">
-        <v>52.5</v>
+        <v>54.46</v>
       </c>
       <c r="L45" t="n">
-        <v>52.91</v>
+        <v>54.89</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>30.48</v>
+        <v>29.84</v>
       </c>
       <c r="K46" t="n">
-        <v>76.69</v>
+        <v>75.08</v>
       </c>
       <c r="L46" t="n">
-        <v>82.52</v>
+        <v>80.79000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>50.38</v>
+        <v>54.02</v>
       </c>
       <c r="K47" t="n">
-        <v>-35.57</v>
+        <v>-38.14</v>
       </c>
       <c r="L47" t="n">
-        <v>61.67</v>
+        <v>66.13</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>-81.37</v>
+        <v>-80.88</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.28</v>
+        <v>-4.25</v>
       </c>
       <c r="L48" t="n">
-        <v>81.48999999999999</v>
+        <v>80.98999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>52.8</v>
+        <v>51.08</v>
       </c>
       <c r="K49" t="n">
-        <v>-99.73</v>
+        <v>-96.48</v>
       </c>
       <c r="L49" t="n">
-        <v>112.84</v>
+        <v>109.17</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>90.05</v>
+        <v>92.91</v>
       </c>
       <c r="K50" t="n">
-        <v>-38.43</v>
+        <v>-39.65</v>
       </c>
       <c r="L50" t="n">
-        <v>97.91</v>
+        <v>101.01</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-70.48999999999999</v>
+        <v>-73.39</v>
       </c>
       <c r="K51" t="n">
-        <v>36.43</v>
+        <v>37.94</v>
       </c>
       <c r="L51" t="n">
-        <v>79.34999999999999</v>
+        <v>82.62</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-82.81</v>
+        <v>-84.34999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>-72.08</v>
+        <v>-73.42</v>
       </c>
       <c r="L52" t="n">
-        <v>109.79</v>
+        <v>111.82</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>83.95</v>
+        <v>80.44</v>
       </c>
       <c r="K53" t="n">
-        <v>-219.66</v>
+        <v>-210.47</v>
       </c>
       <c r="L53" t="n">
-        <v>235.15</v>
+        <v>225.32</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>66.42</v>
+        <v>62.56</v>
       </c>
       <c r="K54" t="n">
-        <v>254.46</v>
+        <v>239.68</v>
       </c>
       <c r="L54" t="n">
-        <v>262.99</v>
+        <v>247.71</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>58.86</v>
+        <v>60.27</v>
       </c>
       <c r="K55" t="n">
-        <v>-137.85</v>
+        <v>-141.16</v>
       </c>
       <c r="L55" t="n">
-        <v>149.89</v>
+        <v>153.49</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>117.79</v>
+        <v>114.32</v>
       </c>
       <c r="K56" t="n">
-        <v>271.86</v>
+        <v>263.85</v>
       </c>
       <c r="L56" t="n">
-        <v>296.28</v>
+        <v>287.55</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-276.6</v>
+        <v>-269</v>
       </c>
       <c r="K57" t="n">
-        <v>112.96</v>
+        <v>109.86</v>
       </c>
       <c r="L57" t="n">
-        <v>298.78</v>
+        <v>290.57</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-216.63</v>
+        <v>-212.11</v>
       </c>
       <c r="K58" t="n">
-        <v>95.09999999999999</v>
+        <v>93.12</v>
       </c>
       <c r="L58" t="n">
-        <v>236.58</v>
+        <v>231.65</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>70.81999999999999</v>
+        <v>68.39</v>
       </c>
       <c r="K59" t="n">
-        <v>57.47</v>
+        <v>55.5</v>
       </c>
       <c r="L59" t="n">
-        <v>91.20999999999999</v>
+        <v>88.08</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-61.1</v>
+        <v>-61.63</v>
       </c>
       <c r="K60" t="n">
-        <v>18.06</v>
+        <v>18.22</v>
       </c>
       <c r="L60" t="n">
-        <v>63.71</v>
+        <v>64.27</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>49.59</v>
+        <v>52.15</v>
       </c>
       <c r="K61" t="n">
-        <v>-16.88</v>
+        <v>-17.75</v>
       </c>
       <c r="L61" t="n">
-        <v>52.38</v>
+        <v>55.09</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-47.79</v>
+        <v>-49.12</v>
       </c>
       <c r="K62" t="n">
-        <v>54.69</v>
+        <v>56.22</v>
       </c>
       <c r="L62" t="n">
-        <v>72.63</v>
+        <v>74.65000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>72.76000000000001</v>
+        <v>70.47</v>
       </c>
       <c r="K63" t="n">
-        <v>75.69</v>
+        <v>73.3</v>
       </c>
       <c r="L63" t="n">
-        <v>104.99</v>
+        <v>101.68</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-27.95</v>
+        <v>-30.23</v>
       </c>
       <c r="K64" t="n">
-        <v>47.53</v>
+        <v>51.4</v>
       </c>
       <c r="L64" t="n">
-        <v>55.14</v>
+        <v>59.63</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>-31.22</v>
+        <v>-31.61</v>
       </c>
       <c r="K65" t="n">
-        <v>-122.75</v>
+        <v>-124.28</v>
       </c>
       <c r="L65" t="n">
-        <v>126.66</v>
+        <v>128.24</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-101.17</v>
+        <v>-99.14</v>
       </c>
       <c r="K66" t="n">
-        <v>85.77</v>
+        <v>84.05</v>
       </c>
       <c r="L66" t="n">
-        <v>132.63</v>
+        <v>129.98</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>127.15</v>
+        <v>124.75</v>
       </c>
       <c r="K67" t="n">
-        <v>-32.09</v>
+        <v>-31.49</v>
       </c>
       <c r="L67" t="n">
-        <v>131.14</v>
+        <v>128.66</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-8.66</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>224.5</v>
+        <v>214.85</v>
       </c>
       <c r="L68" t="n">
-        <v>224.66</v>
+        <v>215.01</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>155.11</v>
+        <v>157.52</v>
       </c>
       <c r="K69" t="n">
-        <v>-13.07</v>
+        <v>-13.28</v>
       </c>
       <c r="L69" t="n">
-        <v>155.66</v>
+        <v>158.08</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>4.01</v>
+        <v>3.81</v>
       </c>
       <c r="K70" t="n">
-        <v>-230.79</v>
+        <v>-219.43</v>
       </c>
       <c r="L70" t="n">
-        <v>230.82</v>
+        <v>219.46</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>172.09</v>
+        <v>181.84</v>
       </c>
       <c r="K71" t="n">
-        <v>-15.39</v>
+        <v>-16.26</v>
       </c>
       <c r="L71" t="n">
-        <v>172.77</v>
+        <v>182.56</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>50.68</v>
+        <v>52.5</v>
       </c>
       <c r="K72" t="n">
-        <v>-204.57</v>
+        <v>-211.91</v>
       </c>
       <c r="L72" t="n">
-        <v>210.76</v>
+        <v>218.32</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>126.98</v>
+        <v>125.06</v>
       </c>
       <c r="K73" t="n">
-        <v>-219.82</v>
+        <v>-216.49</v>
       </c>
       <c r="L73" t="n">
-        <v>253.86</v>
+        <v>250.01</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>-97.76000000000001</v>
+        <v>-93.72</v>
       </c>
       <c r="K74" t="n">
-        <v>-3.19</v>
+        <v>-3.06</v>
       </c>
       <c r="L74" t="n">
-        <v>97.81999999999999</v>
+        <v>93.77</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>17.48</v>
+        <v>18.08</v>
       </c>
       <c r="K75" t="n">
-        <v>-61.1</v>
+        <v>-63.19</v>
       </c>
       <c r="L75" t="n">
-        <v>63.55</v>
+        <v>65.73</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-20.12</v>
+        <v>-21.48</v>
       </c>
       <c r="K76" t="n">
-        <v>-51.48</v>
+        <v>-54.98</v>
       </c>
       <c r="L76" t="n">
-        <v>55.27</v>
+        <v>59.03</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>61.94</v>
+        <v>60.7</v>
       </c>
       <c r="K77" t="n">
-        <v>-76.06</v>
+        <v>-74.53</v>
       </c>
       <c r="L77" t="n">
-        <v>98.09</v>
+        <v>96.12</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-23.24</v>
+        <v>-23.92</v>
       </c>
       <c r="K78" t="n">
-        <v>77.62</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>81.02</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>24.75</v>
+        <v>24.15</v>
       </c>
       <c r="K79" t="n">
-        <v>-95.51000000000001</v>
+        <v>-93.20999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>98.66</v>
+        <v>96.28</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>83.26000000000001</v>
+        <v>84.17</v>
       </c>
       <c r="K80" t="n">
-        <v>75.39</v>
+        <v>76.22</v>
       </c>
       <c r="L80" t="n">
-        <v>112.32</v>
+        <v>113.55</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-114.68</v>
+        <v>-115.55</v>
       </c>
       <c r="K81" t="n">
-        <v>7.96</v>
+        <v>8.02</v>
       </c>
       <c r="L81" t="n">
-        <v>114.95</v>
+        <v>115.83</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-129.84</v>
+        <v>-125.13</v>
       </c>
       <c r="K82" t="n">
-        <v>-123.21</v>
+        <v>-118.74</v>
       </c>
       <c r="L82" t="n">
-        <v>179</v>
+        <v>172.5</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-131.7</v>
+        <v>-137.17</v>
       </c>
       <c r="K83" t="n">
-        <v>-48.69</v>
+        <v>-50.72</v>
       </c>
       <c r="L83" t="n">
-        <v>140.42</v>
+        <v>146.25</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-162.9</v>
+        <v>-161.49</v>
       </c>
       <c r="K84" t="n">
-        <v>-34.07</v>
+        <v>-33.78</v>
       </c>
       <c r="L84" t="n">
-        <v>166.43</v>
+        <v>164.99</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.74</v>
+        <v>-4.83</v>
       </c>
       <c r="K85" t="n">
-        <v>159.41</v>
+        <v>162.25</v>
       </c>
       <c r="L85" t="n">
-        <v>159.48</v>
+        <v>162.32</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-68.04000000000001</v>
+        <v>-72.01000000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>-189.8</v>
+        <v>-200.88</v>
       </c>
       <c r="L86" t="n">
-        <v>201.62</v>
+        <v>213.4</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-313.22</v>
+        <v>-306.27</v>
       </c>
       <c r="K87" t="n">
-        <v>26.38</v>
+        <v>25.79</v>
       </c>
       <c r="L87" t="n">
-        <v>314.33</v>
+        <v>307.36</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>162.39</v>
+        <v>152.85</v>
       </c>
       <c r="K88" t="n">
-        <v>-354.5</v>
+        <v>-333.67</v>
       </c>
       <c r="L88" t="n">
-        <v>389.93</v>
+        <v>367.01</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-02.xlsx
+++ b/output/2024-04-02.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.56</v>
+        <v>3.07</v>
       </c>
       <c r="F14" t="n">
-        <v>9.51</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>169.8</v>
+        <v>161.2</v>
       </c>
       <c r="H14" t="n">
-        <v>94.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>9.970000000000001</v>
+        <v>70.39</v>
       </c>
       <c r="K14" t="n">
-        <v>58.73</v>
+        <v>-3.74</v>
       </c>
       <c r="L14" t="n">
-        <v>59.57</v>
+        <v>70.48999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:43:24</t>
+          <t>06:42:23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.02</v>
+        <v>3.14</v>
       </c>
       <c r="F15" t="n">
-        <v>9.34</v>
+        <v>7.36</v>
       </c>
       <c r="G15" t="n">
-        <v>167</v>
+        <v>157.1</v>
       </c>
       <c r="H15" t="n">
-        <v>97.09999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-25.79</v>
+        <v>-26.67</v>
       </c>
       <c r="K15" t="n">
-        <v>51.23</v>
+        <v>-93.05</v>
       </c>
       <c r="L15" t="n">
-        <v>57.36</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:44:42</t>
+          <t>06:43:36</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.16</v>
+        <v>2.74</v>
       </c>
       <c r="F16" t="n">
-        <v>8.539999999999999</v>
+        <v>7.05</v>
       </c>
       <c r="G16" t="n">
-        <v>163</v>
+        <v>164.3</v>
       </c>
       <c r="H16" t="n">
-        <v>100</v>
+        <v>93.5</v>
       </c>
       <c r="I16" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>-66.48</v>
+        <v>47.04</v>
       </c>
       <c r="K16" t="n">
-        <v>1.96</v>
+        <v>37.98</v>
       </c>
       <c r="L16" t="n">
-        <v>66.51000000000001</v>
+        <v>60.45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:50:06</t>
+          <t>06:47:05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.99</v>
+        <v>3.18</v>
       </c>
       <c r="F17" t="n">
-        <v>9.359999999999999</v>
+        <v>4.66</v>
       </c>
       <c r="G17" t="n">
-        <v>169.5</v>
+        <v>167.3</v>
       </c>
       <c r="H17" t="n">
-        <v>96</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>-107.42</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-20.48</v>
+        <v>70.91</v>
       </c>
       <c r="L17" t="n">
-        <v>109.35</v>
+        <v>98.18000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:51:20</t>
+          <t>06:49:07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.43</v>
+        <v>3.12</v>
       </c>
       <c r="F18" t="n">
-        <v>9.68</v>
+        <v>8.76</v>
       </c>
       <c r="G18" t="n">
-        <v>175.4</v>
+        <v>167</v>
       </c>
       <c r="H18" t="n">
-        <v>94.59999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="I18" t="n">
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-46.63</v>
+        <v>-53.81</v>
       </c>
       <c r="K18" t="n">
-        <v>42.64</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>63.18</v>
+        <v>90.43000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:52:05</t>
+          <t>06:50:59</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.92</v>
+        <v>3.27</v>
       </c>
       <c r="F19" t="n">
-        <v>9.470000000000001</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>173.4</v>
+        <v>160.9</v>
       </c>
       <c r="H19" t="n">
-        <v>92.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="I19" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>60.87</v>
+        <v>-67.12</v>
       </c>
       <c r="K19" t="n">
-        <v>41.26</v>
+        <v>61.14</v>
       </c>
       <c r="L19" t="n">
-        <v>73.54000000000001</v>
+        <v>90.79000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:58:10</t>
+          <t>06:55:56</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.13</v>
+        <v>2.81</v>
       </c>
       <c r="F20" t="n">
-        <v>9.42</v>
+        <v>5.19</v>
       </c>
       <c r="G20" t="n">
-        <v>162.7</v>
+        <v>167.9</v>
       </c>
       <c r="H20" t="n">
-        <v>91.2</v>
+        <v>93.8</v>
       </c>
       <c r="I20" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>38.68</v>
+        <v>-111.49</v>
       </c>
       <c r="K20" t="n">
-        <v>-110.51</v>
+        <v>108.32</v>
       </c>
       <c r="L20" t="n">
-        <v>117.08</v>
+        <v>155.44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:00:03</t>
+          <t>06:58:07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="F21" t="n">
-        <v>9.26</v>
+        <v>8.27</v>
       </c>
       <c r="G21" t="n">
-        <v>178.8</v>
+        <v>178.6</v>
       </c>
       <c r="H21" t="n">
-        <v>89.09999999999999</v>
+        <v>94</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>26.19</v>
+        <v>123.31</v>
       </c>
       <c r="K21" t="n">
-        <v>80.72</v>
+        <v>-90.84</v>
       </c>
       <c r="L21" t="n">
-        <v>84.86</v>
+        <v>153.16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:02:10</t>
+          <t>07:00:10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="F22" t="n">
-        <v>8.94</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>176.1</v>
+        <v>166.4</v>
       </c>
       <c r="H22" t="n">
-        <v>92.8</v>
+        <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-115.04</v>
+        <v>-132.31</v>
       </c>
       <c r="K22" t="n">
-        <v>40.94</v>
+        <v>-51.21</v>
       </c>
       <c r="L22" t="n">
-        <v>122.1</v>
+        <v>141.87</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:07:32</t>
+          <t>07:05:08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.56</v>
+        <v>2.66</v>
       </c>
       <c r="F23" t="n">
-        <v>8.56</v>
+        <v>7.25</v>
       </c>
       <c r="G23" t="n">
-        <v>165.2</v>
+        <v>162.3</v>
       </c>
       <c r="H23" t="n">
-        <v>90.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>34.49</v>
+        <v>97.44</v>
       </c>
       <c r="K23" t="n">
-        <v>157.91</v>
+        <v>-123.38</v>
       </c>
       <c r="L23" t="n">
-        <v>161.63</v>
+        <v>157.22</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:09:35</t>
+          <t>07:06:55</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.97</v>
+        <v>3.26</v>
       </c>
       <c r="F24" t="n">
-        <v>9.140000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>169</v>
+        <v>155.8</v>
       </c>
       <c r="H24" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I24" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>22.2</v>
+        <v>157.36</v>
       </c>
       <c r="K24" t="n">
-        <v>-8.27</v>
+        <v>-116.49</v>
       </c>
       <c r="L24" t="n">
-        <v>23.69</v>
+        <v>195.79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:10:45</t>
+          <t>07:08:25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.03</v>
+        <v>2.96</v>
       </c>
       <c r="F25" t="n">
-        <v>8.960000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>164.8</v>
+        <v>176.8</v>
       </c>
       <c r="H25" t="n">
-        <v>97.2</v>
+        <v>92</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>132.83</v>
+        <v>106.31</v>
       </c>
       <c r="K25" t="n">
-        <v>11.67</v>
+        <v>138.26</v>
       </c>
       <c r="L25" t="n">
-        <v>133.34</v>
+        <v>174.41</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:16:14</t>
+          <t>07:13:03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.98</v>
+        <v>3.52</v>
       </c>
       <c r="F26" t="n">
-        <v>9.4</v>
+        <v>10.16</v>
       </c>
       <c r="G26" t="n">
-        <v>179.6</v>
+        <v>171.2</v>
       </c>
       <c r="H26" t="n">
-        <v>94.3</v>
+        <v>97</v>
       </c>
       <c r="I26" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>177.27</v>
+        <v>140.74</v>
       </c>
       <c r="K26" t="n">
-        <v>140.25</v>
+        <v>-323.47</v>
       </c>
       <c r="L26" t="n">
-        <v>226.04</v>
+        <v>352.76</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:17:43</t>
+          <t>07:15:21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.36</v>
+        <v>2.93</v>
       </c>
       <c r="F27" t="n">
-        <v>8.66</v>
+        <v>9.01</v>
       </c>
       <c r="G27" t="n">
-        <v>172.6</v>
+        <v>157.8</v>
       </c>
       <c r="H27" t="n">
-        <v>90.2</v>
+        <v>93.5</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>215.62</v>
+        <v>141.39</v>
       </c>
       <c r="K27" t="n">
-        <v>110.05</v>
+        <v>-162.72</v>
       </c>
       <c r="L27" t="n">
-        <v>242.08</v>
+        <v>215.57</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:18:43</t>
+          <t>07:16:33</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.62</v>
+        <v>3.51</v>
       </c>
       <c r="F28" t="n">
-        <v>9.24</v>
+        <v>9.74</v>
       </c>
       <c r="G28" t="n">
-        <v>165.1</v>
+        <v>170.6</v>
       </c>
       <c r="H28" t="n">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>211.48</v>
+        <v>-211.85</v>
       </c>
       <c r="K28" t="n">
-        <v>-95.65000000000001</v>
+        <v>-195.13</v>
       </c>
       <c r="L28" t="n">
-        <v>232.1</v>
+        <v>288.02</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:30:48</t>
+          <t>07:26:57</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.33</v>
+        <v>3.16</v>
       </c>
       <c r="F29" t="n">
-        <v>9.109999999999999</v>
+        <v>10.58</v>
       </c>
       <c r="G29" t="n">
-        <v>161</v>
+        <v>150.2</v>
       </c>
       <c r="H29" t="n">
-        <v>94.59999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>-12.32</v>
+        <v>-26.28</v>
       </c>
       <c r="K29" t="n">
-        <v>82.13</v>
+        <v>-78.04000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>83.05</v>
+        <v>82.34999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:32:16</t>
+          <t>07:29:16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.2</v>
+        <v>3.63</v>
       </c>
       <c r="F30" t="n">
-        <v>9.09</v>
+        <v>10.58</v>
       </c>
       <c r="G30" t="n">
-        <v>159.8</v>
+        <v>167.3</v>
       </c>
       <c r="H30" t="n">
-        <v>86.2</v>
+        <v>94.8</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>76.04000000000001</v>
+        <v>0.93</v>
       </c>
       <c r="K30" t="n">
-        <v>-10.24</v>
+        <v>110.43</v>
       </c>
       <c r="L30" t="n">
-        <v>76.73</v>
+        <v>110.44</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:33:58</t>
+          <t>07:30:23</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.62</v>
+        <v>2.54</v>
       </c>
       <c r="F31" t="n">
-        <v>9.890000000000001</v>
+        <v>5.81</v>
       </c>
       <c r="G31" t="n">
-        <v>167</v>
+        <v>170.8</v>
       </c>
       <c r="H31" t="n">
-        <v>94.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>-89.73</v>
+        <v>55.06</v>
       </c>
       <c r="K31" t="n">
-        <v>-25.6</v>
+        <v>53.64</v>
       </c>
       <c r="L31" t="n">
-        <v>93.31</v>
+        <v>76.87</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:39:42</t>
+          <t>07:34:02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.26</v>
+        <v>3.29</v>
       </c>
       <c r="F32" t="n">
-        <v>9.609999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="G32" t="n">
-        <v>163.9</v>
+        <v>172.6</v>
       </c>
       <c r="H32" t="n">
-        <v>96.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>14.66</v>
+        <v>0.92</v>
       </c>
       <c r="K32" t="n">
-        <v>69.41</v>
+        <v>107.53</v>
       </c>
       <c r="L32" t="n">
-        <v>70.94</v>
+        <v>107.53</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:40:49</t>
+          <t>07:36:06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.34</v>
+        <v>2.52</v>
       </c>
       <c r="F33" t="n">
-        <v>9.789999999999999</v>
+        <v>4.74</v>
       </c>
       <c r="G33" t="n">
-        <v>167</v>
+        <v>154.9</v>
       </c>
       <c r="H33" t="n">
-        <v>95</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>-78.13</v>
+        <v>-40.73</v>
       </c>
       <c r="K33" t="n">
-        <v>-68.08</v>
+        <v>117.21</v>
       </c>
       <c r="L33" t="n">
-        <v>103.63</v>
+        <v>124.09</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:42:11</t>
+          <t>07:38:28</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.16</v>
+        <v>4.12</v>
       </c>
       <c r="F34" t="n">
-        <v>8.859999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="G34" t="n">
-        <v>159.1</v>
+        <v>166.1</v>
       </c>
       <c r="H34" t="n">
-        <v>88.59999999999999</v>
+        <v>87</v>
       </c>
       <c r="I34" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>94.40000000000001</v>
+        <v>-4.21</v>
       </c>
       <c r="K34" t="n">
-        <v>-23.3</v>
+        <v>-118.97</v>
       </c>
       <c r="L34" t="n">
-        <v>97.23</v>
+        <v>119.04</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:46:46</t>
+          <t>07:43:18</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="F35" t="n">
-        <v>9.17</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>159</v>
+        <v>173.8</v>
       </c>
       <c r="H35" t="n">
-        <v>94.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-94.83</v>
+        <v>120.11</v>
       </c>
       <c r="K35" t="n">
-        <v>9.76</v>
+        <v>-36.27</v>
       </c>
       <c r="L35" t="n">
-        <v>95.34</v>
+        <v>125.47</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:49:09</t>
+          <t>07:44:15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.4</v>
+        <v>2.87</v>
       </c>
       <c r="F36" t="n">
-        <v>8.880000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="G36" t="n">
-        <v>173.8</v>
+        <v>165.9</v>
       </c>
       <c r="H36" t="n">
-        <v>89.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.14</v>
+        <v>129.37</v>
       </c>
       <c r="K36" t="n">
-        <v>-123.94</v>
+        <v>-52.7</v>
       </c>
       <c r="L36" t="n">
-        <v>123.94</v>
+        <v>139.69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:50:24</t>
+          <t>07:45:33</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.21</v>
+        <v>3.5</v>
       </c>
       <c r="F37" t="n">
-        <v>9.6</v>
+        <v>10.58</v>
       </c>
       <c r="G37" t="n">
-        <v>179.3</v>
+        <v>178.9</v>
       </c>
       <c r="H37" t="n">
-        <v>94</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>51.12</v>
+        <v>-148.8</v>
       </c>
       <c r="K37" t="n">
-        <v>126.23</v>
+        <v>-79.18000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>136.19</v>
+        <v>168.55</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:54:59</t>
+          <t>07:49:27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.89</v>
+        <v>3.42</v>
       </c>
       <c r="F38" t="n">
-        <v>8.779999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="G38" t="n">
-        <v>178.9</v>
+        <v>161.3</v>
       </c>
       <c r="H38" t="n">
-        <v>90.90000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>-116.34</v>
+        <v>282.64</v>
       </c>
       <c r="K38" t="n">
-        <v>66.56999999999999</v>
+        <v>-4.74</v>
       </c>
       <c r="L38" t="n">
-        <v>134.04</v>
+        <v>282.68</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:56:17</t>
+          <t>07:51:33</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.29</v>
+        <v>3.56</v>
       </c>
       <c r="F39" t="n">
-        <v>10.11</v>
+        <v>9.24</v>
       </c>
       <c r="G39" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="H39" t="n">
-        <v>91.8</v>
+        <v>84</v>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>133.14</v>
+        <v>-243.66</v>
       </c>
       <c r="K39" t="n">
-        <v>-86.52</v>
+        <v>-178.13</v>
       </c>
       <c r="L39" t="n">
-        <v>158.78</v>
+        <v>301.83</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:57:46</t>
+          <t>07:53:14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.27</v>
+        <v>3.7</v>
       </c>
       <c r="F40" t="n">
-        <v>8.48</v>
+        <v>10.58</v>
       </c>
       <c r="G40" t="n">
-        <v>156</v>
+        <v>173.3</v>
       </c>
       <c r="H40" t="n">
-        <v>84</v>
+        <v>96.2</v>
       </c>
       <c r="I40" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-126.61</v>
+        <v>146.65</v>
       </c>
       <c r="K40" t="n">
-        <v>134.17</v>
+        <v>89.09</v>
       </c>
       <c r="L40" t="n">
-        <v>184.48</v>
+        <v>171.59</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:01:59</t>
+          <t>07:56:39</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.33</v>
+        <v>3.15</v>
       </c>
       <c r="F41" t="n">
-        <v>9.41</v>
+        <v>9.4</v>
       </c>
       <c r="G41" t="n">
-        <v>159.8</v>
+        <v>157.5</v>
       </c>
       <c r="H41" t="n">
-        <v>97.7</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-134.29</v>
+        <v>-329.91</v>
       </c>
       <c r="K41" t="n">
-        <v>104.76</v>
+        <v>-43.8</v>
       </c>
       <c r="L41" t="n">
-        <v>170.31</v>
+        <v>332.8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:03:41</t>
+          <t>07:59:03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.51</v>
+        <v>3.43</v>
       </c>
       <c r="F42" t="n">
-        <v>9.23</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>157.5</v>
+        <v>171.9</v>
       </c>
       <c r="H42" t="n">
-        <v>90.09999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-182.17</v>
+        <v>246.73</v>
       </c>
       <c r="K42" t="n">
-        <v>-33.37</v>
+        <v>-258.56</v>
       </c>
       <c r="L42" t="n">
-        <v>185.21</v>
+        <v>357.39</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:04:34</t>
+          <t>08:01:27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.52</v>
+        <v>3.83</v>
       </c>
       <c r="F43" t="n">
-        <v>9.869999999999999</v>
+        <v>10.58</v>
       </c>
       <c r="G43" t="n">
-        <v>159</v>
+        <v>152.5</v>
       </c>
       <c r="H43" t="n">
-        <v>99.7</v>
+        <v>93</v>
       </c>
       <c r="I43" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>202.88</v>
+        <v>-297.22</v>
       </c>
       <c r="K43" t="n">
-        <v>-17.19</v>
+        <v>132.43</v>
       </c>
       <c r="L43" t="n">
-        <v>203.61</v>
+        <v>325.39</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:17:11</t>
+          <t>08:11:04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.27</v>
+        <v>3.82</v>
       </c>
       <c r="F44" t="n">
-        <v>9.59</v>
+        <v>10.58</v>
       </c>
       <c r="G44" t="n">
-        <v>154.5</v>
+        <v>162</v>
       </c>
       <c r="H44" t="n">
-        <v>93.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="I44" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-60.31</v>
+        <v>-1.4</v>
       </c>
       <c r="K44" t="n">
-        <v>21.48</v>
+        <v>101.6</v>
       </c>
       <c r="L44" t="n">
-        <v>64.02</v>
+        <v>101.61</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:19:42</t>
+          <t>08:12:37</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.19</v>
+        <v>3.24</v>
       </c>
       <c r="F45" t="n">
-        <v>9.01</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>180.9</v>
+        <v>166.6</v>
       </c>
       <c r="H45" t="n">
-        <v>94.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="I45" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>6.84</v>
+        <v>-63.04</v>
       </c>
       <c r="K45" t="n">
-        <v>54.46</v>
+        <v>47.41</v>
       </c>
       <c r="L45" t="n">
-        <v>54.89</v>
+        <v>78.88</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:21:39</t>
+          <t>08:13:45</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.28</v>
+        <v>3.57</v>
       </c>
       <c r="F46" t="n">
-        <v>9.460000000000001</v>
+        <v>10.58</v>
       </c>
       <c r="G46" t="n">
-        <v>160.3</v>
+        <v>164</v>
       </c>
       <c r="H46" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>29.84</v>
+        <v>-78.09999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>75.08</v>
+        <v>-2.66</v>
       </c>
       <c r="L46" t="n">
-        <v>80.79000000000001</v>
+        <v>78.14</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:25:34</t>
+          <t>08:18:22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.85</v>
+        <v>3.22</v>
       </c>
       <c r="F47" t="n">
-        <v>8.960000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>167.2</v>
+        <v>149.6</v>
       </c>
       <c r="H47" t="n">
-        <v>92.09999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>54.02</v>
+        <v>96.09</v>
       </c>
       <c r="K47" t="n">
-        <v>-38.14</v>
+        <v>-1.03</v>
       </c>
       <c r="L47" t="n">
-        <v>66.13</v>
+        <v>96.09999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:26:43</t>
+          <t>08:19:37</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.78</v>
+        <v>3.48</v>
       </c>
       <c r="F48" t="n">
-        <v>9.220000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>173.4</v>
+        <v>173.6</v>
       </c>
       <c r="H48" t="n">
-        <v>86.5</v>
+        <v>100</v>
       </c>
       <c r="I48" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-80.88</v>
+        <v>-60.1</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.25</v>
+        <v>-67.33</v>
       </c>
       <c r="L48" t="n">
-        <v>80.98999999999999</v>
+        <v>90.25</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:28:25</t>
+          <t>08:22:05</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.02</v>
+        <v>2.78</v>
       </c>
       <c r="F49" t="n">
-        <v>8.35</v>
+        <v>8.99</v>
       </c>
       <c r="G49" t="n">
-        <v>163.8</v>
+        <v>157.7</v>
       </c>
       <c r="H49" t="n">
-        <v>92.8</v>
+        <v>92</v>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>51.08</v>
+        <v>4.96</v>
       </c>
       <c r="K49" t="n">
-        <v>-96.48</v>
+        <v>-133.56</v>
       </c>
       <c r="L49" t="n">
-        <v>109.17</v>
+        <v>133.65</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:31:51</t>
+          <t>08:26:37</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.25</v>
+        <v>3.61</v>
       </c>
       <c r="F50" t="n">
-        <v>8.369999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="G50" t="n">
-        <v>167.4</v>
+        <v>159</v>
       </c>
       <c r="H50" t="n">
-        <v>90.7</v>
+        <v>84.7</v>
       </c>
       <c r="I50" t="n">
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>92.91</v>
+        <v>-199.83</v>
       </c>
       <c r="K50" t="n">
-        <v>-39.65</v>
+        <v>-41.1</v>
       </c>
       <c r="L50" t="n">
-        <v>101.01</v>
+        <v>204.01</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:34:19</t>
+          <t>08:28:19</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="F51" t="n">
-        <v>8.73</v>
+        <v>7.37</v>
       </c>
       <c r="G51" t="n">
-        <v>164.2</v>
+        <v>181.7</v>
       </c>
       <c r="H51" t="n">
-        <v>83.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-73.39</v>
+        <v>35.02</v>
       </c>
       <c r="K51" t="n">
-        <v>37.94</v>
+        <v>-158.29</v>
       </c>
       <c r="L51" t="n">
-        <v>82.62</v>
+        <v>162.12</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:36:14</t>
+          <t>08:30:10</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.62</v>
+        <v>3.79</v>
       </c>
       <c r="F52" t="n">
-        <v>8.609999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="G52" t="n">
-        <v>170</v>
+        <v>154.5</v>
       </c>
       <c r="H52" t="n">
-        <v>93.8</v>
+        <v>94.5</v>
       </c>
       <c r="I52" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-84.34999999999999</v>
+        <v>150.41</v>
       </c>
       <c r="K52" t="n">
-        <v>-73.42</v>
+        <v>11.61</v>
       </c>
       <c r="L52" t="n">
-        <v>111.82</v>
+        <v>150.86</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:40:43</t>
+          <t>08:35:09</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.47</v>
+        <v>2.99</v>
       </c>
       <c r="F53" t="n">
-        <v>8.56</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>169.3</v>
+        <v>174</v>
       </c>
       <c r="H53" t="n">
-        <v>98.5</v>
+        <v>90.3</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>80.44</v>
+        <v>61.47</v>
       </c>
       <c r="K53" t="n">
-        <v>-210.47</v>
+        <v>214.27</v>
       </c>
       <c r="L53" t="n">
-        <v>225.32</v>
+        <v>222.91</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:42:34</t>
+          <t>08:35:51</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.16</v>
+        <v>3.59</v>
       </c>
       <c r="F54" t="n">
-        <v>9.94</v>
+        <v>10.58</v>
       </c>
       <c r="G54" t="n">
-        <v>170.3</v>
+        <v>160.6</v>
       </c>
       <c r="H54" t="n">
-        <v>95.7</v>
+        <v>93.7</v>
       </c>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>62.56</v>
+        <v>109.48</v>
       </c>
       <c r="K54" t="n">
-        <v>239.68</v>
+        <v>-170.98</v>
       </c>
       <c r="L54" t="n">
-        <v>247.71</v>
+        <v>203.03</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:44:55</t>
+          <t>08:38:03</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.42</v>
+        <v>3.16</v>
       </c>
       <c r="F55" t="n">
-        <v>8.789999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>162.8</v>
+        <v>166.1</v>
       </c>
       <c r="H55" t="n">
-        <v>96.40000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="I55" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>60.27</v>
+        <v>89.7</v>
       </c>
       <c r="K55" t="n">
-        <v>-141.16</v>
+        <v>-225.39</v>
       </c>
       <c r="L55" t="n">
-        <v>153.49</v>
+        <v>242.59</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:49:31</t>
+          <t>08:42:30</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.77</v>
+        <v>3.58</v>
       </c>
       <c r="F56" t="n">
-        <v>8.68</v>
+        <v>10.58</v>
       </c>
       <c r="G56" t="n">
-        <v>171.5</v>
+        <v>162.9</v>
       </c>
       <c r="H56" t="n">
-        <v>93.59999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>114.32</v>
+        <v>-43.8</v>
       </c>
       <c r="K56" t="n">
-        <v>263.85</v>
+        <v>-244.18</v>
       </c>
       <c r="L56" t="n">
-        <v>287.55</v>
+        <v>248.07</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:51:43</t>
+          <t>08:44:49</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="F57" t="n">
-        <v>9.050000000000001</v>
+        <v>10.58</v>
       </c>
       <c r="G57" t="n">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="H57" t="n">
-        <v>93</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I57" t="n">
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-269</v>
+        <v>290.21</v>
       </c>
       <c r="K57" t="n">
-        <v>109.86</v>
+        <v>122.43</v>
       </c>
       <c r="L57" t="n">
-        <v>290.57</v>
+        <v>314.98</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:53:23</t>
+          <t>08:46:51</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="F58" t="n">
-        <v>9.699999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="G58" t="n">
-        <v>177.6</v>
+        <v>166.8</v>
       </c>
       <c r="H58" t="n">
-        <v>90.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="I58" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-212.11</v>
+        <v>219.55</v>
       </c>
       <c r="K58" t="n">
-        <v>93.12</v>
+        <v>-71.95</v>
       </c>
       <c r="L58" t="n">
-        <v>231.65</v>
+        <v>231.04</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:05:34</t>
+          <t>08:55:27</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="F59" t="n">
-        <v>9.27</v>
+        <v>10.58</v>
       </c>
       <c r="G59" t="n">
-        <v>171.4</v>
+        <v>165.7</v>
       </c>
       <c r="H59" t="n">
-        <v>96.09999999999999</v>
+        <v>93.3</v>
       </c>
       <c r="I59" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>68.39</v>
+        <v>7.74</v>
       </c>
       <c r="K59" t="n">
-        <v>55.5</v>
+        <v>88.19</v>
       </c>
       <c r="L59" t="n">
-        <v>88.08</v>
+        <v>88.52</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:06:47</t>
+          <t>08:58:13</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.71</v>
+        <v>3.21</v>
       </c>
       <c r="F60" t="n">
-        <v>9.24</v>
+        <v>7.5</v>
       </c>
       <c r="G60" t="n">
-        <v>153</v>
+        <v>178.8</v>
       </c>
       <c r="H60" t="n">
-        <v>93.90000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>-61.63</v>
+        <v>24.45</v>
       </c>
       <c r="K60" t="n">
-        <v>18.22</v>
+        <v>-100.96</v>
       </c>
       <c r="L60" t="n">
-        <v>64.27</v>
+        <v>103.88</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:07:54</t>
+          <t>09:00:10</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.29</v>
+        <v>4.08</v>
       </c>
       <c r="F61" t="n">
-        <v>8.449999999999999</v>
+        <v>10.58</v>
       </c>
       <c r="G61" t="n">
-        <v>170.7</v>
+        <v>176.5</v>
       </c>
       <c r="H61" t="n">
-        <v>92.40000000000001</v>
+        <v>89</v>
       </c>
       <c r="I61" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>52.15</v>
+        <v>-24.99</v>
       </c>
       <c r="K61" t="n">
-        <v>-17.75</v>
+        <v>-67.68000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>55.09</v>
+        <v>72.15000000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:13:12</t>
+          <t>09:04:53</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.74</v>
+        <v>3.38</v>
       </c>
       <c r="F62" t="n">
-        <v>9.119999999999999</v>
+        <v>9.92</v>
       </c>
       <c r="G62" t="n">
-        <v>164.4</v>
+        <v>166.9</v>
       </c>
       <c r="H62" t="n">
-        <v>99.3</v>
+        <v>97.2</v>
       </c>
       <c r="I62" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-49.12</v>
+        <v>-23.85</v>
       </c>
       <c r="K62" t="n">
-        <v>56.22</v>
+        <v>128.13</v>
       </c>
       <c r="L62" t="n">
-        <v>74.65000000000001</v>
+        <v>130.34</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:15:09</t>
+          <t>09:06:14</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.65</v>
+        <v>3.09</v>
       </c>
       <c r="F63" t="n">
-        <v>10.09</v>
+        <v>10.58</v>
       </c>
       <c r="G63" t="n">
-        <v>163.6</v>
+        <v>175</v>
       </c>
       <c r="H63" t="n">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>70.47</v>
+        <v>9.58</v>
       </c>
       <c r="K63" t="n">
-        <v>73.3</v>
+        <v>-81.06</v>
       </c>
       <c r="L63" t="n">
-        <v>101.68</v>
+        <v>81.63</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:16:48</t>
+          <t>09:07:41</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.33</v>
+        <v>3.49</v>
       </c>
       <c r="F64" t="n">
-        <v>9.210000000000001</v>
+        <v>10.58</v>
       </c>
       <c r="G64" t="n">
-        <v>174.8</v>
+        <v>159.7</v>
       </c>
       <c r="H64" t="n">
-        <v>98.59999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="I64" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-30.23</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>51.4</v>
+        <v>56.05</v>
       </c>
       <c r="L64" t="n">
-        <v>59.63</v>
+        <v>108.67</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:21:12</t>
+          <t>09:12:50</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.01</v>
+        <v>3.79</v>
       </c>
       <c r="F65" t="n">
-        <v>9.460000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="G65" t="n">
-        <v>174.4</v>
+        <v>168.9</v>
       </c>
       <c r="H65" t="n">
-        <v>97.90000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>-31.61</v>
+        <v>-28.61</v>
       </c>
       <c r="K65" t="n">
-        <v>-124.28</v>
+        <v>-230.63</v>
       </c>
       <c r="L65" t="n">
-        <v>128.24</v>
+        <v>232.4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:22:39</t>
+          <t>09:14:37</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.34</v>
+        <v>3.21</v>
       </c>
       <c r="F66" t="n">
-        <v>9.02</v>
+        <v>7.99</v>
       </c>
       <c r="G66" t="n">
-        <v>166.3</v>
+        <v>155.9</v>
       </c>
       <c r="H66" t="n">
-        <v>95.5</v>
+        <v>96</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-99.14</v>
+        <v>-16.21</v>
       </c>
       <c r="K66" t="n">
-        <v>84.05</v>
+        <v>28.08</v>
       </c>
       <c r="L66" t="n">
-        <v>129.98</v>
+        <v>32.42</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:24:17</t>
+          <t>09:15:47</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.41</v>
+        <v>4.26</v>
       </c>
       <c r="F67" t="n">
-        <v>9.32</v>
+        <v>10.58</v>
       </c>
       <c r="G67" t="n">
-        <v>165.8</v>
+        <v>171.1</v>
       </c>
       <c r="H67" t="n">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="I67" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>124.75</v>
+        <v>-48.47</v>
       </c>
       <c r="K67" t="n">
-        <v>-31.49</v>
+        <v>165.1</v>
       </c>
       <c r="L67" t="n">
-        <v>128.66</v>
+        <v>172.07</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:28:08</t>
+          <t>09:20:48</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.44</v>
+        <v>3.56</v>
       </c>
       <c r="F68" t="n">
-        <v>9.039999999999999</v>
+        <v>10.25</v>
       </c>
       <c r="G68" t="n">
-        <v>166.2</v>
+        <v>169.9</v>
       </c>
       <c r="H68" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I68" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J68" t="n">
-        <v>-8.279999999999999</v>
+        <v>-106.04</v>
       </c>
       <c r="K68" t="n">
-        <v>214.85</v>
+        <v>-196.01</v>
       </c>
       <c r="L68" t="n">
-        <v>215.01</v>
+        <v>222.86</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:29:18</t>
+          <t>09:22:43</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.64</v>
+        <v>3.73</v>
       </c>
       <c r="F69" t="n">
-        <v>8.859999999999999</v>
+        <v>10.58</v>
       </c>
       <c r="G69" t="n">
-        <v>161.2</v>
+        <v>155.6</v>
       </c>
       <c r="H69" t="n">
-        <v>98.5</v>
+        <v>89.2</v>
       </c>
       <c r="I69" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>157.52</v>
+        <v>63.69</v>
       </c>
       <c r="K69" t="n">
-        <v>-13.28</v>
+        <v>181.77</v>
       </c>
       <c r="L69" t="n">
-        <v>158.08</v>
+        <v>192.61</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:30:46</t>
+          <t>09:24:15</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="F70" t="n">
-        <v>9.24</v>
+        <v>9.92</v>
       </c>
       <c r="G70" t="n">
-        <v>152.9</v>
+        <v>183.8</v>
       </c>
       <c r="H70" t="n">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>3.81</v>
+        <v>-63.18</v>
       </c>
       <c r="K70" t="n">
-        <v>-219.43</v>
+        <v>202.43</v>
       </c>
       <c r="L70" t="n">
-        <v>219.46</v>
+        <v>212.06</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:35:08</t>
+          <t>09:29:31</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="F71" t="n">
-        <v>9.880000000000001</v>
+        <v>10.58</v>
       </c>
       <c r="G71" t="n">
-        <v>163.9</v>
+        <v>160.5</v>
       </c>
       <c r="H71" t="n">
-        <v>88.8</v>
+        <v>97.7</v>
       </c>
       <c r="I71" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>181.84</v>
+        <v>-294.31</v>
       </c>
       <c r="K71" t="n">
-        <v>-16.26</v>
+        <v>-11.56</v>
       </c>
       <c r="L71" t="n">
-        <v>182.56</v>
+        <v>294.54</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:36:40</t>
+          <t>09:31:25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.73</v>
+        <v>3.68</v>
       </c>
       <c r="F72" t="n">
-        <v>8.65</v>
+        <v>10.46</v>
       </c>
       <c r="G72" t="n">
-        <v>174</v>
+        <v>158.4</v>
       </c>
       <c r="H72" t="n">
-        <v>91.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I72" t="n">
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>52.5</v>
+        <v>-263.98</v>
       </c>
       <c r="K72" t="n">
-        <v>-211.91</v>
+        <v>-13.55</v>
       </c>
       <c r="L72" t="n">
-        <v>218.32</v>
+        <v>264.33</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:38:02</t>
+          <t>09:32:43</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.63</v>
+        <v>3.29</v>
       </c>
       <c r="F73" t="n">
-        <v>9.33</v>
+        <v>7.46</v>
       </c>
       <c r="G73" t="n">
-        <v>158.2</v>
+        <v>177.6</v>
       </c>
       <c r="H73" t="n">
-        <v>93.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>125.06</v>
+        <v>-116.66</v>
       </c>
       <c r="K73" t="n">
-        <v>-216.49</v>
+        <v>59.28</v>
       </c>
       <c r="L73" t="n">
-        <v>250.01</v>
+        <v>130.86</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:48:49</t>
+          <t>09:41:06</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.5</v>
+        <v>3.03</v>
       </c>
       <c r="F74" t="n">
-        <v>9.119999999999999</v>
+        <v>10.58</v>
       </c>
       <c r="G74" t="n">
-        <v>169.6</v>
+        <v>167.5</v>
       </c>
       <c r="H74" t="n">
-        <v>99.90000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>-93.72</v>
+        <v>46.46</v>
       </c>
       <c r="K74" t="n">
-        <v>-3.06</v>
+        <v>-104.61</v>
       </c>
       <c r="L74" t="n">
-        <v>93.77</v>
+        <v>114.46</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:51:17</t>
+          <t>09:42:57</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.26</v>
+        <v>3.16</v>
       </c>
       <c r="F75" t="n">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="G75" t="n">
-        <v>174.2</v>
+        <v>151.5</v>
       </c>
       <c r="H75" t="n">
-        <v>96.8</v>
+        <v>93.3</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J75" t="n">
-        <v>18.08</v>
+        <v>-126.81</v>
       </c>
       <c r="K75" t="n">
-        <v>-63.19</v>
+        <v>-12.53</v>
       </c>
       <c r="L75" t="n">
-        <v>65.73</v>
+        <v>127.43</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:52:12</t>
+          <t>09:44:50</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.06</v>
+        <v>3.6</v>
       </c>
       <c r="F76" t="n">
-        <v>8.1</v>
+        <v>10.58</v>
       </c>
       <c r="G76" t="n">
-        <v>156.9</v>
+        <v>165.6</v>
       </c>
       <c r="H76" t="n">
-        <v>86.90000000000001</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>-21.48</v>
+        <v>63.78</v>
       </c>
       <c r="K76" t="n">
-        <v>-54.98</v>
+        <v>51.78</v>
       </c>
       <c r="L76" t="n">
-        <v>59.03</v>
+        <v>82.15000000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:57:48</t>
+          <t>09:50:18</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.01</v>
+        <v>3.76</v>
       </c>
       <c r="F77" t="n">
-        <v>9.42</v>
+        <v>8.92</v>
       </c>
       <c r="G77" t="n">
-        <v>171.9</v>
+        <v>173</v>
       </c>
       <c r="H77" t="n">
-        <v>86.09999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="I77" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>60.7</v>
+        <v>-61.21</v>
       </c>
       <c r="K77" t="n">
-        <v>-74.53</v>
+        <v>94.8</v>
       </c>
       <c r="L77" t="n">
-        <v>96.12</v>
+        <v>112.84</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:59:42</t>
+          <t>09:51:18</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.29</v>
+        <v>3.6</v>
       </c>
       <c r="F78" t="n">
-        <v>8.83</v>
+        <v>10.58</v>
       </c>
       <c r="G78" t="n">
-        <v>153.5</v>
+        <v>177.9</v>
       </c>
       <c r="H78" t="n">
-        <v>97.59999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="I78" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-23.92</v>
+        <v>-124.18</v>
       </c>
       <c r="K78" t="n">
-        <v>79.90000000000001</v>
+        <v>-62.4</v>
       </c>
       <c r="L78" t="n">
-        <v>83.40000000000001</v>
+        <v>138.98</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:02:11</t>
+          <t>09:52:09</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.77</v>
+        <v>3.84</v>
       </c>
       <c r="F79" t="n">
-        <v>8.880000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="G79" t="n">
-        <v>152.8</v>
+        <v>164.1</v>
       </c>
       <c r="H79" t="n">
-        <v>93.7</v>
+        <v>92.3</v>
       </c>
       <c r="I79" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>24.15</v>
+        <v>-55.6</v>
       </c>
       <c r="K79" t="n">
-        <v>-93.20999999999999</v>
+        <v>-75.8</v>
       </c>
       <c r="L79" t="n">
-        <v>96.28</v>
+        <v>94</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:06:22</t>
+          <t>09:56:03</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.5</v>
+        <v>3.91</v>
       </c>
       <c r="F80" t="n">
-        <v>8.949999999999999</v>
+        <v>10.58</v>
       </c>
       <c r="G80" t="n">
-        <v>156</v>
+        <v>168.1</v>
       </c>
       <c r="H80" t="n">
-        <v>93.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="I80" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>84.17</v>
+        <v>-126.42</v>
       </c>
       <c r="K80" t="n">
-        <v>76.22</v>
+        <v>-135.45</v>
       </c>
       <c r="L80" t="n">
-        <v>113.55</v>
+        <v>185.28</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:07:12</t>
+          <t>09:58:03</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="F81" t="n">
-        <v>8.82</v>
+        <v>10.37</v>
       </c>
       <c r="G81" t="n">
-        <v>157.8</v>
+        <v>167.2</v>
       </c>
       <c r="H81" t="n">
-        <v>91.3</v>
+        <v>88.3</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-115.55</v>
+        <v>105.81</v>
       </c>
       <c r="K81" t="n">
-        <v>8.02</v>
+        <v>-60.62</v>
       </c>
       <c r="L81" t="n">
-        <v>115.83</v>
+        <v>121.94</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:08:50</t>
+          <t>10:00:23</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.93</v>
+        <v>3.27</v>
       </c>
       <c r="F82" t="n">
-        <v>9.34</v>
+        <v>9.5</v>
       </c>
       <c r="G82" t="n">
-        <v>165.2</v>
+        <v>149.3</v>
       </c>
       <c r="H82" t="n">
-        <v>94.7</v>
+        <v>98.7</v>
       </c>
       <c r="I82" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-125.13</v>
+        <v>148.86</v>
       </c>
       <c r="K82" t="n">
-        <v>-118.74</v>
+        <v>-37.56</v>
       </c>
       <c r="L82" t="n">
-        <v>172.5</v>
+        <v>153.52</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:13:19</t>
+          <t>10:05:31</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.73</v>
+        <v>3.87</v>
       </c>
       <c r="F83" t="n">
-        <v>9.140000000000001</v>
+        <v>10.58</v>
       </c>
       <c r="G83" t="n">
-        <v>176.5</v>
+        <v>174.5</v>
       </c>
       <c r="H83" t="n">
-        <v>96</v>
+        <v>85.2</v>
       </c>
       <c r="I83" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J83" t="n">
-        <v>-137.17</v>
+        <v>-58.18</v>
       </c>
       <c r="K83" t="n">
-        <v>-50.72</v>
+        <v>-248.87</v>
       </c>
       <c r="L83" t="n">
-        <v>146.25</v>
+        <v>255.58</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:15:39</t>
+          <t>10:07:16</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="F84" t="n">
-        <v>9.02</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G84" t="n">
-        <v>159.1</v>
+        <v>170.6</v>
       </c>
       <c r="H84" t="n">
-        <v>98.40000000000001</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>-161.49</v>
+        <v>45.9</v>
       </c>
       <c r="K84" t="n">
-        <v>-33.78</v>
+        <v>192.83</v>
       </c>
       <c r="L84" t="n">
-        <v>164.99</v>
+        <v>198.22</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:17:46</t>
+          <t>10:09:37</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="F85" t="n">
-        <v>9.83</v>
+        <v>10.58</v>
       </c>
       <c r="G85" t="n">
-        <v>168.9</v>
+        <v>164.5</v>
       </c>
       <c r="H85" t="n">
-        <v>95.90000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.83</v>
+        <v>172.64</v>
       </c>
       <c r="K85" t="n">
-        <v>162.25</v>
+        <v>-41.9</v>
       </c>
       <c r="L85" t="n">
-        <v>162.32</v>
+        <v>177.65</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:22:54</t>
+          <t>10:14:21</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.12</v>
+        <v>3.66</v>
       </c>
       <c r="F86" t="n">
-        <v>9.4</v>
+        <v>10.58</v>
       </c>
       <c r="G86" t="n">
-        <v>177.9</v>
+        <v>166.7</v>
       </c>
       <c r="H86" t="n">
-        <v>93.40000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-72.01000000000001</v>
+        <v>-238.07</v>
       </c>
       <c r="K86" t="n">
-        <v>-200.88</v>
+        <v>58.03</v>
       </c>
       <c r="L86" t="n">
-        <v>213.4</v>
+        <v>245.04</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:25:15</t>
+          <t>10:15:03</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.84</v>
+        <v>4.59</v>
       </c>
       <c r="F87" t="n">
-        <v>9.41</v>
+        <v>10.58</v>
       </c>
       <c r="G87" t="n">
-        <v>161.6</v>
+        <v>167.4</v>
       </c>
       <c r="H87" t="n">
-        <v>94.90000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-306.27</v>
+        <v>373.23</v>
       </c>
       <c r="K87" t="n">
-        <v>25.79</v>
+        <v>-58.51</v>
       </c>
       <c r="L87" t="n">
-        <v>307.36</v>
+        <v>377.79</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:26:33</t>
+          <t>10:17:31</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.53</v>
+        <v>4.07</v>
       </c>
       <c r="F88" t="n">
-        <v>9.67</v>
+        <v>10.58</v>
       </c>
       <c r="G88" t="n">
-        <v>173.1</v>
+        <v>175.6</v>
       </c>
       <c r="H88" t="n">
-        <v>94.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>152.85</v>
+        <v>-280.4</v>
       </c>
       <c r="K88" t="n">
-        <v>-333.67</v>
+        <v>-88.63</v>
       </c>
       <c r="L88" t="n">
-        <v>367.01</v>
+        <v>294.07</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-02.xlsx
+++ b/output/2024-04-02.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>70.39</v>
+        <v>74.37</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.74</v>
+        <v>-3.96</v>
       </c>
       <c r="L14" t="n">
-        <v>70.48999999999999</v>
+        <v>74.48</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-26.67</v>
+        <v>-28.64</v>
       </c>
       <c r="K15" t="n">
-        <v>-93.05</v>
+        <v>-99.94</v>
       </c>
       <c r="L15" t="n">
-        <v>96.8</v>
+        <v>103.97</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>47.04</v>
+        <v>51.31</v>
       </c>
       <c r="K16" t="n">
-        <v>37.98</v>
+        <v>41.43</v>
       </c>
       <c r="L16" t="n">
-        <v>60.45</v>
+        <v>65.95</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>67.90000000000001</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>70.91</v>
+        <v>76.16</v>
       </c>
       <c r="L17" t="n">
-        <v>98.18000000000001</v>
+        <v>105.45</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-53.81</v>
+        <v>-56.85</v>
       </c>
       <c r="K18" t="n">
-        <v>72.68000000000001</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>90.43000000000001</v>
+        <v>95.54000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>-67.12</v>
+        <v>-73.22</v>
       </c>
       <c r="K19" t="n">
-        <v>61.14</v>
+        <v>66.69</v>
       </c>
       <c r="L19" t="n">
-        <v>90.79000000000001</v>
+        <v>99.04000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-111.49</v>
+        <v>-123.43</v>
       </c>
       <c r="K20" t="n">
-        <v>108.32</v>
+        <v>119.92</v>
       </c>
       <c r="L20" t="n">
-        <v>155.44</v>
+        <v>172.1</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>123.31</v>
+        <v>136.52</v>
       </c>
       <c r="K21" t="n">
-        <v>-90.84</v>
+        <v>-100.57</v>
       </c>
       <c r="L21" t="n">
-        <v>153.16</v>
+        <v>169.57</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-132.31</v>
+        <v>-144.34</v>
       </c>
       <c r="K22" t="n">
-        <v>-51.21</v>
+        <v>-55.87</v>
       </c>
       <c r="L22" t="n">
-        <v>141.87</v>
+        <v>154.77</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>97.44</v>
+        <v>110.88</v>
       </c>
       <c r="K23" t="n">
-        <v>-123.38</v>
+        <v>-140.4</v>
       </c>
       <c r="L23" t="n">
-        <v>157.22</v>
+        <v>178.9</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>157.36</v>
+        <v>176.69</v>
       </c>
       <c r="K24" t="n">
-        <v>-116.49</v>
+        <v>-130.79</v>
       </c>
       <c r="L24" t="n">
-        <v>195.79</v>
+        <v>219.83</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>106.31</v>
+        <v>114.19</v>
       </c>
       <c r="K25" t="n">
-        <v>138.26</v>
+        <v>148.5</v>
       </c>
       <c r="L25" t="n">
-        <v>174.41</v>
+        <v>187.32</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>140.74</v>
+        <v>153.89</v>
       </c>
       <c r="K26" t="n">
-        <v>-323.47</v>
+        <v>-353.69</v>
       </c>
       <c r="L26" t="n">
-        <v>352.76</v>
+        <v>385.72</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>141.39</v>
+        <v>160.89</v>
       </c>
       <c r="K27" t="n">
-        <v>-162.72</v>
+        <v>-185.17</v>
       </c>
       <c r="L27" t="n">
-        <v>215.57</v>
+        <v>245.3</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-211.85</v>
+        <v>-228.05</v>
       </c>
       <c r="K28" t="n">
-        <v>-195.13</v>
+        <v>-210.05</v>
       </c>
       <c r="L28" t="n">
-        <v>288.02</v>
+        <v>310.04</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>-26.28</v>
+        <v>-29.51</v>
       </c>
       <c r="K29" t="n">
-        <v>-78.04000000000001</v>
+        <v>-87.62</v>
       </c>
       <c r="L29" t="n">
-        <v>82.34999999999999</v>
+        <v>92.45999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>0.93</v>
+        <v>1.05</v>
       </c>
       <c r="K30" t="n">
-        <v>110.43</v>
+        <v>125.43</v>
       </c>
       <c r="L30" t="n">
-        <v>110.44</v>
+        <v>125.44</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>55.06</v>
+        <v>60.06</v>
       </c>
       <c r="K31" t="n">
-        <v>53.64</v>
+        <v>58.52</v>
       </c>
       <c r="L31" t="n">
-        <v>76.87</v>
+        <v>83.86</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="K32" t="n">
-        <v>107.53</v>
+        <v>115.47</v>
       </c>
       <c r="L32" t="n">
-        <v>107.53</v>
+        <v>115.48</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>-40.73</v>
+        <v>-45.1</v>
       </c>
       <c r="K33" t="n">
-        <v>117.21</v>
+        <v>129.77</v>
       </c>
       <c r="L33" t="n">
-        <v>124.09</v>
+        <v>137.38</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-4.21</v>
+        <v>-4.57</v>
       </c>
       <c r="K34" t="n">
-        <v>-118.97</v>
+        <v>-129.24</v>
       </c>
       <c r="L34" t="n">
-        <v>119.04</v>
+        <v>129.32</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>120.11</v>
+        <v>136.68</v>
       </c>
       <c r="K35" t="n">
-        <v>-36.27</v>
+        <v>-41.27</v>
       </c>
       <c r="L35" t="n">
-        <v>125.47</v>
+        <v>142.77</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>129.37</v>
+        <v>143.23</v>
       </c>
       <c r="K36" t="n">
-        <v>-52.7</v>
+        <v>-58.35</v>
       </c>
       <c r="L36" t="n">
-        <v>139.69</v>
+        <v>154.66</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>-148.8</v>
+        <v>-164.67</v>
       </c>
       <c r="K37" t="n">
-        <v>-79.18000000000001</v>
+        <v>-87.62</v>
       </c>
       <c r="L37" t="n">
-        <v>168.55</v>
+        <v>186.53</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>282.64</v>
+        <v>321.69</v>
       </c>
       <c r="K38" t="n">
-        <v>-4.74</v>
+        <v>-5.4</v>
       </c>
       <c r="L38" t="n">
-        <v>282.68</v>
+        <v>321.74</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-243.66</v>
+        <v>-277.37</v>
       </c>
       <c r="K39" t="n">
-        <v>-178.13</v>
+        <v>-202.78</v>
       </c>
       <c r="L39" t="n">
-        <v>301.83</v>
+        <v>343.59</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>146.65</v>
+        <v>155.03</v>
       </c>
       <c r="K40" t="n">
-        <v>89.09</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>171.59</v>
+        <v>181.4</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-329.91</v>
+        <v>-348.58</v>
       </c>
       <c r="K41" t="n">
-        <v>-43.8</v>
+        <v>-46.28</v>
       </c>
       <c r="L41" t="n">
-        <v>332.8</v>
+        <v>351.64</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>246.73</v>
+        <v>281.2</v>
       </c>
       <c r="K42" t="n">
-        <v>-258.56</v>
+        <v>-294.69</v>
       </c>
       <c r="L42" t="n">
-        <v>357.39</v>
+        <v>407.32</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>-297.22</v>
+        <v>-320.73</v>
       </c>
       <c r="K43" t="n">
-        <v>132.43</v>
+        <v>142.9</v>
       </c>
       <c r="L43" t="n">
-        <v>325.39</v>
+        <v>351.12</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.4</v>
+        <v>-1.52</v>
       </c>
       <c r="K44" t="n">
-        <v>101.6</v>
+        <v>110.53</v>
       </c>
       <c r="L44" t="n">
-        <v>101.61</v>
+        <v>110.54</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>-63.04</v>
+        <v>-66.61</v>
       </c>
       <c r="K45" t="n">
-        <v>47.41</v>
+        <v>50.1</v>
       </c>
       <c r="L45" t="n">
-        <v>78.88</v>
+        <v>83.34999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-78.09999999999999</v>
+        <v>-88.73</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.66</v>
+        <v>-3.02</v>
       </c>
       <c r="L46" t="n">
-        <v>78.14</v>
+        <v>88.78</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>96.09</v>
+        <v>109.35</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.03</v>
+        <v>-1.17</v>
       </c>
       <c r="L47" t="n">
-        <v>96.09999999999999</v>
+        <v>109.35</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-60.1</v>
+        <v>-68.31</v>
       </c>
       <c r="K48" t="n">
-        <v>-67.33</v>
+        <v>-76.52</v>
       </c>
       <c r="L48" t="n">
-        <v>90.25</v>
+        <v>102.58</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>4.96</v>
+        <v>5.65</v>
       </c>
       <c r="K49" t="n">
-        <v>-133.56</v>
+        <v>-151.98</v>
       </c>
       <c r="L49" t="n">
-        <v>133.65</v>
+        <v>152.09</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-199.83</v>
+        <v>-211.01</v>
       </c>
       <c r="K50" t="n">
-        <v>-41.1</v>
+        <v>-43.39</v>
       </c>
       <c r="L50" t="n">
-        <v>204.01</v>
+        <v>215.42</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>35.02</v>
+        <v>39.85</v>
       </c>
       <c r="K51" t="n">
-        <v>-158.29</v>
+        <v>-180.12</v>
       </c>
       <c r="L51" t="n">
-        <v>162.12</v>
+        <v>184.48</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>150.41</v>
+        <v>170.99</v>
       </c>
       <c r="K52" t="n">
-        <v>11.61</v>
+        <v>13.2</v>
       </c>
       <c r="L52" t="n">
-        <v>150.86</v>
+        <v>171.5</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>61.47</v>
+        <v>68.06</v>
       </c>
       <c r="K53" t="n">
-        <v>214.27</v>
+        <v>237.23</v>
       </c>
       <c r="L53" t="n">
-        <v>222.91</v>
+        <v>246.8</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>109.48</v>
+        <v>122.98</v>
       </c>
       <c r="K54" t="n">
-        <v>-170.98</v>
+        <v>-192.05</v>
       </c>
       <c r="L54" t="n">
-        <v>203.03</v>
+        <v>228.05</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>89.7</v>
+        <v>102.08</v>
       </c>
       <c r="K55" t="n">
-        <v>-225.39</v>
+        <v>-256.48</v>
       </c>
       <c r="L55" t="n">
-        <v>242.59</v>
+        <v>276.05</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>-43.8</v>
+        <v>-47.91</v>
       </c>
       <c r="K56" t="n">
-        <v>-244.18</v>
+        <v>-267.11</v>
       </c>
       <c r="L56" t="n">
-        <v>248.07</v>
+        <v>271.38</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>290.21</v>
+        <v>312.97</v>
       </c>
       <c r="K57" t="n">
-        <v>122.43</v>
+        <v>132.04</v>
       </c>
       <c r="L57" t="n">
-        <v>314.98</v>
+        <v>339.69</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>219.55</v>
+        <v>249.84</v>
       </c>
       <c r="K58" t="n">
-        <v>-71.95</v>
+        <v>-81.88</v>
       </c>
       <c r="L58" t="n">
-        <v>231.04</v>
+        <v>262.91</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>7.74</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>88.19</v>
+        <v>94.55</v>
       </c>
       <c r="L59" t="n">
-        <v>88.52</v>
+        <v>94.92</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>24.45</v>
+        <v>27.07</v>
       </c>
       <c r="K60" t="n">
-        <v>-100.96</v>
+        <v>-111.78</v>
       </c>
       <c r="L60" t="n">
-        <v>103.88</v>
+        <v>115.01</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-24.99</v>
+        <v>-27.15</v>
       </c>
       <c r="K61" t="n">
-        <v>-67.68000000000001</v>
+        <v>-73.54000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>72.15000000000001</v>
+        <v>78.39</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-23.85</v>
+        <v>-25.18</v>
       </c>
       <c r="K62" t="n">
-        <v>128.13</v>
+        <v>135.3</v>
       </c>
       <c r="L62" t="n">
-        <v>130.34</v>
+        <v>137.62</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>9.58</v>
+        <v>10.9</v>
       </c>
       <c r="K63" t="n">
-        <v>-81.06</v>
+        <v>-92.23999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>81.63</v>
+        <v>92.88</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>93.09999999999999</v>
+        <v>105.81</v>
       </c>
       <c r="K64" t="n">
-        <v>56.05</v>
+        <v>63.71</v>
       </c>
       <c r="L64" t="n">
-        <v>108.67</v>
+        <v>123.51</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>-28.61</v>
+        <v>-30.7</v>
       </c>
       <c r="K65" t="n">
-        <v>-230.63</v>
+        <v>-247.48</v>
       </c>
       <c r="L65" t="n">
-        <v>232.4</v>
+        <v>249.37</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-16.21</v>
+        <v>-18.45</v>
       </c>
       <c r="K66" t="n">
-        <v>28.08</v>
+        <v>31.95</v>
       </c>
       <c r="L66" t="n">
-        <v>32.42</v>
+        <v>36.89</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-48.47</v>
+        <v>-55.06</v>
       </c>
       <c r="K67" t="n">
-        <v>165.1</v>
+        <v>187.57</v>
       </c>
       <c r="L67" t="n">
-        <v>172.07</v>
+        <v>195.48</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>18</v>
       </c>
       <c r="J68" t="n">
-        <v>-106.04</v>
+        <v>-117.45</v>
       </c>
       <c r="K68" t="n">
-        <v>-196.01</v>
+        <v>-217.1</v>
       </c>
       <c r="L68" t="n">
-        <v>222.86</v>
+        <v>246.83</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>63.69</v>
+        <v>72.52</v>
       </c>
       <c r="K69" t="n">
-        <v>181.77</v>
+        <v>206.96</v>
       </c>
       <c r="L69" t="n">
-        <v>192.61</v>
+        <v>219.3</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-63.18</v>
+        <v>-67.89</v>
       </c>
       <c r="K70" t="n">
-        <v>202.43</v>
+        <v>217.51</v>
       </c>
       <c r="L70" t="n">
-        <v>212.06</v>
+        <v>227.86</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>-294.31</v>
+        <v>-317.4</v>
       </c>
       <c r="K71" t="n">
-        <v>-11.56</v>
+        <v>-12.47</v>
       </c>
       <c r="L71" t="n">
-        <v>294.54</v>
+        <v>317.64</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-263.98</v>
+        <v>-284.55</v>
       </c>
       <c r="K72" t="n">
-        <v>-13.55</v>
+        <v>-14.61</v>
       </c>
       <c r="L72" t="n">
-        <v>264.33</v>
+        <v>284.92</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>-116.66</v>
+        <v>-129.21</v>
       </c>
       <c r="K73" t="n">
-        <v>59.28</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="L73" t="n">
-        <v>130.86</v>
+        <v>144.93</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>46.46</v>
+        <v>49.9</v>
       </c>
       <c r="K74" t="n">
-        <v>-104.61</v>
+        <v>-112.36</v>
       </c>
       <c r="L74" t="n">
-        <v>114.46</v>
+        <v>122.94</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>17</v>
       </c>
       <c r="J75" t="n">
-        <v>-126.81</v>
+        <v>-142.39</v>
       </c>
       <c r="K75" t="n">
-        <v>-12.53</v>
+        <v>-14.07</v>
       </c>
       <c r="L75" t="n">
-        <v>127.43</v>
+        <v>143.08</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>63.78</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>51.78</v>
+        <v>57.23</v>
       </c>
       <c r="L76" t="n">
-        <v>82.15000000000001</v>
+        <v>90.8</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>-61.21</v>
+        <v>-64.51000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>94.8</v>
+        <v>99.92</v>
       </c>
       <c r="L77" t="n">
-        <v>112.84</v>
+        <v>118.93</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-124.18</v>
+        <v>-141.06</v>
       </c>
       <c r="K78" t="n">
-        <v>-62.4</v>
+        <v>-70.88</v>
       </c>
       <c r="L78" t="n">
-        <v>138.98</v>
+        <v>157.87</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>-55.6</v>
+        <v>-59.54</v>
       </c>
       <c r="K79" t="n">
-        <v>-75.8</v>
+        <v>-81.18000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>94</v>
+        <v>100.68</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-126.42</v>
+        <v>-143.69</v>
       </c>
       <c r="K80" t="n">
-        <v>-135.45</v>
+        <v>-153.96</v>
       </c>
       <c r="L80" t="n">
-        <v>185.28</v>
+        <v>210.59</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>105.81</v>
+        <v>120.35</v>
       </c>
       <c r="K81" t="n">
-        <v>-60.62</v>
+        <v>-68.94</v>
       </c>
       <c r="L81" t="n">
-        <v>121.94</v>
+        <v>138.7</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>148.86</v>
+        <v>164.8</v>
       </c>
       <c r="K82" t="n">
-        <v>-37.56</v>
+        <v>-41.58</v>
       </c>
       <c r="L82" t="n">
-        <v>153.52</v>
+        <v>169.97</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>17</v>
       </c>
       <c r="J83" t="n">
-        <v>-58.18</v>
+        <v>-65.37</v>
       </c>
       <c r="K83" t="n">
-        <v>-248.87</v>
+        <v>-279.64</v>
       </c>
       <c r="L83" t="n">
-        <v>255.58</v>
+        <v>287.18</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>45.9</v>
+        <v>49.31</v>
       </c>
       <c r="K84" t="n">
-        <v>192.83</v>
+        <v>207.13</v>
       </c>
       <c r="L84" t="n">
-        <v>198.22</v>
+        <v>212.91</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>172.64</v>
+        <v>193.87</v>
       </c>
       <c r="K85" t="n">
-        <v>-41.9</v>
+        <v>-47.05</v>
       </c>
       <c r="L85" t="n">
-        <v>177.65</v>
+        <v>199.5</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-238.07</v>
+        <v>-264.48</v>
       </c>
       <c r="K86" t="n">
-        <v>58.03</v>
+        <v>64.47</v>
       </c>
       <c r="L86" t="n">
-        <v>245.04</v>
+        <v>272.22</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>373.23</v>
+        <v>431.38</v>
       </c>
       <c r="K87" t="n">
-        <v>-58.51</v>
+        <v>-67.62</v>
       </c>
       <c r="L87" t="n">
-        <v>377.79</v>
+        <v>436.65</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-280.4</v>
+        <v>-321.08</v>
       </c>
       <c r="K88" t="n">
-        <v>-88.63</v>
+        <v>-101.49</v>
       </c>
       <c r="L88" t="n">
-        <v>294.07</v>
+        <v>336.74</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-02.xlsx
+++ b/output/2024-04-02.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.07</v>
+        <v>3.41</v>
       </c>
       <c r="F14" t="n">
-        <v>9.130000000000001</v>
+        <v>10.58</v>
       </c>
       <c r="G14" t="n">
-        <v>161.2</v>
+        <v>175.4</v>
       </c>
       <c r="H14" t="n">
-        <v>94.40000000000001</v>
+        <v>50.5</v>
       </c>
       <c r="I14" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>74.37</v>
+        <v>32.9</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.96</v>
+        <v>-25.02</v>
       </c>
       <c r="L14" t="n">
-        <v>74.48</v>
+        <v>41.33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:42:23</t>
+          <t>06:42:19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.14</v>
+        <v>3.48</v>
       </c>
       <c r="F15" t="n">
-        <v>7.36</v>
+        <v>9.33</v>
       </c>
       <c r="G15" t="n">
-        <v>157.1</v>
+        <v>173.2</v>
       </c>
       <c r="H15" t="n">
-        <v>96.09999999999999</v>
+        <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-28.64</v>
+        <v>49.29</v>
       </c>
       <c r="K15" t="n">
-        <v>-99.94</v>
+        <v>21.75</v>
       </c>
       <c r="L15" t="n">
-        <v>103.97</v>
+        <v>53.87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:43:36</t>
+          <t>06:43:26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.74</v>
+        <v>2.91</v>
       </c>
       <c r="F16" t="n">
-        <v>7.05</v>
+        <v>7.2</v>
       </c>
       <c r="G16" t="n">
-        <v>164.3</v>
+        <v>172.3</v>
       </c>
       <c r="H16" t="n">
-        <v>93.5</v>
+        <v>44.4</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>51.31</v>
+        <v>-21.73</v>
       </c>
       <c r="K16" t="n">
-        <v>41.43</v>
+        <v>52.92</v>
       </c>
       <c r="L16" t="n">
-        <v>65.95</v>
+        <v>57.21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:47:05</t>
+          <t>06:48:03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="F17" t="n">
-        <v>4.66</v>
+        <v>10.58</v>
       </c>
       <c r="G17" t="n">
-        <v>167.3</v>
+        <v>176.5</v>
       </c>
       <c r="H17" t="n">
-        <v>85.90000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J17" t="n">
-        <v>72.93000000000001</v>
+        <v>6.23</v>
       </c>
       <c r="K17" t="n">
-        <v>76.16</v>
+        <v>-86.09</v>
       </c>
       <c r="L17" t="n">
-        <v>105.45</v>
+        <v>86.31999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:49:07</t>
+          <t>06:50:34</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="F18" t="n">
-        <v>8.76</v>
+        <v>9.17</v>
       </c>
       <c r="G18" t="n">
-        <v>167</v>
+        <v>163.5</v>
       </c>
       <c r="H18" t="n">
-        <v>92.5</v>
+        <v>64.5</v>
       </c>
       <c r="I18" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>-56.85</v>
+        <v>-63.09</v>
       </c>
       <c r="K18" t="n">
-        <v>76.79000000000001</v>
+        <v>43.87</v>
       </c>
       <c r="L18" t="n">
-        <v>95.54000000000001</v>
+        <v>76.84</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:50:59</t>
+          <t>06:51:15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.27</v>
+        <v>3.09</v>
       </c>
       <c r="F19" t="n">
-        <v>9.949999999999999</v>
+        <v>3.74</v>
       </c>
       <c r="G19" t="n">
-        <v>160.9</v>
+        <v>165</v>
       </c>
       <c r="H19" t="n">
-        <v>95</v>
+        <v>76.2</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-73.22</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>66.69</v>
+        <v>-42.1</v>
       </c>
       <c r="L19" t="n">
-        <v>99.04000000000001</v>
+        <v>88.41</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:55:56</t>
+          <t>06:56:39</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.81</v>
+        <v>3.33</v>
       </c>
       <c r="F20" t="n">
-        <v>5.19</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>167.9</v>
+        <v>181.7</v>
       </c>
       <c r="H20" t="n">
-        <v>93.8</v>
+        <v>72.5</v>
       </c>
       <c r="I20" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J20" t="n">
-        <v>-123.43</v>
+        <v>-83.73999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>119.92</v>
+        <v>18.34</v>
       </c>
       <c r="L20" t="n">
-        <v>172.1</v>
+        <v>85.73</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:58:07</t>
+          <t>06:57:41</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.14</v>
+        <v>3.09</v>
       </c>
       <c r="F21" t="n">
-        <v>8.27</v>
+        <v>8.32</v>
       </c>
       <c r="G21" t="n">
-        <v>178.6</v>
+        <v>154.3</v>
       </c>
       <c r="H21" t="n">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>136.52</v>
+        <v>45.06</v>
       </c>
       <c r="K21" t="n">
-        <v>-100.57</v>
+        <v>-59.44</v>
       </c>
       <c r="L21" t="n">
-        <v>169.57</v>
+        <v>74.59</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:00:10</t>
+          <t>06:58:31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.09</v>
+        <v>3.22</v>
       </c>
       <c r="F22" t="n">
-        <v>8.699999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>166.4</v>
+        <v>188.7</v>
       </c>
       <c r="H22" t="n">
-        <v>100</v>
+        <v>74.3</v>
       </c>
       <c r="I22" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>-144.34</v>
+        <v>-25.27</v>
       </c>
       <c r="K22" t="n">
-        <v>-55.87</v>
+        <v>-110.54</v>
       </c>
       <c r="L22" t="n">
-        <v>154.77</v>
+        <v>113.39</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:05:08</t>
+          <t>07:03:17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.66</v>
+        <v>3.8</v>
       </c>
       <c r="F23" t="n">
-        <v>7.25</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>162.3</v>
+        <v>165</v>
       </c>
       <c r="H23" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>110.88</v>
+        <v>-186.37</v>
       </c>
       <c r="K23" t="n">
-        <v>-140.4</v>
+        <v>98.17</v>
       </c>
       <c r="L23" t="n">
-        <v>178.9</v>
+        <v>210.65</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:06:55</t>
+          <t>07:05:03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.26</v>
+        <v>2.98</v>
       </c>
       <c r="F24" t="n">
-        <v>8.619999999999999</v>
+        <v>7.29</v>
       </c>
       <c r="G24" t="n">
-        <v>155.8</v>
+        <v>174.3</v>
       </c>
       <c r="H24" t="n">
-        <v>93</v>
+        <v>53.6</v>
       </c>
       <c r="I24" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>176.69</v>
+        <v>92.8</v>
       </c>
       <c r="K24" t="n">
-        <v>-130.79</v>
+        <v>-106.13</v>
       </c>
       <c r="L24" t="n">
-        <v>219.83</v>
+        <v>140.98</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:08:25</t>
+          <t>07:07:38</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="F25" t="n">
-        <v>8.970000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="G25" t="n">
-        <v>176.8</v>
+        <v>154.2</v>
       </c>
       <c r="H25" t="n">
-        <v>92</v>
+        <v>69.2</v>
       </c>
       <c r="I25" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>114.19</v>
+        <v>-138.3</v>
       </c>
       <c r="K25" t="n">
-        <v>148.5</v>
+        <v>-135.38</v>
       </c>
       <c r="L25" t="n">
-        <v>187.32</v>
+        <v>193.53</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:13:03</t>
+          <t>07:10:45</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="F26" t="n">
-        <v>10.16</v>
+        <v>8.6</v>
       </c>
       <c r="G26" t="n">
-        <v>171.2</v>
+        <v>153</v>
       </c>
       <c r="H26" t="n">
-        <v>97</v>
+        <v>57.9</v>
       </c>
       <c r="I26" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J26" t="n">
-        <v>153.89</v>
+        <v>-190.77</v>
       </c>
       <c r="K26" t="n">
-        <v>-353.69</v>
+        <v>10.53</v>
       </c>
       <c r="L26" t="n">
-        <v>385.72</v>
+        <v>191.06</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:15:21</t>
+          <t>07:12:05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.93</v>
+        <v>4.01</v>
       </c>
       <c r="F27" t="n">
-        <v>9.01</v>
+        <v>7.37</v>
       </c>
       <c r="G27" t="n">
-        <v>157.8</v>
+        <v>165.5</v>
       </c>
       <c r="H27" t="n">
-        <v>93.5</v>
+        <v>73.2</v>
       </c>
       <c r="I27" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>160.89</v>
+        <v>108.96</v>
       </c>
       <c r="K27" t="n">
-        <v>-185.17</v>
+        <v>-303.15</v>
       </c>
       <c r="L27" t="n">
-        <v>245.3</v>
+        <v>322.14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:16:33</t>
+          <t>07:13:38</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.51</v>
+        <v>2.99</v>
       </c>
       <c r="F28" t="n">
-        <v>9.74</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>170.6</v>
+        <v>166.9</v>
       </c>
       <c r="H28" t="n">
-        <v>90.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J28" t="n">
-        <v>-228.05</v>
+        <v>216.83</v>
       </c>
       <c r="K28" t="n">
-        <v>-210.05</v>
+        <v>-140.85</v>
       </c>
       <c r="L28" t="n">
-        <v>310.04</v>
+        <v>258.56</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:26:57</t>
+          <t>07:23:45</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.16</v>
+        <v>3.49</v>
       </c>
       <c r="F29" t="n">
-        <v>10.58</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>150.2</v>
+        <v>170.1</v>
       </c>
       <c r="H29" t="n">
-        <v>93.59999999999999</v>
+        <v>57</v>
       </c>
       <c r="I29" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>-29.51</v>
+        <v>-36.23</v>
       </c>
       <c r="K29" t="n">
-        <v>-87.62</v>
+        <v>-37.29</v>
       </c>
       <c r="L29" t="n">
-        <v>92.45999999999999</v>
+        <v>51.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:29:16</t>
+          <t>07:25:29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.63</v>
+        <v>3.43</v>
       </c>
       <c r="F30" t="n">
-        <v>10.58</v>
+        <v>7.5</v>
       </c>
       <c r="G30" t="n">
-        <v>167.3</v>
+        <v>153.9</v>
       </c>
       <c r="H30" t="n">
-        <v>94.8</v>
+        <v>43.8</v>
       </c>
       <c r="I30" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J30" t="n">
-        <v>1.05</v>
+        <v>-22.97</v>
       </c>
       <c r="K30" t="n">
-        <v>125.43</v>
+        <v>50.11</v>
       </c>
       <c r="L30" t="n">
-        <v>125.44</v>
+        <v>55.12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:30:23</t>
+          <t>07:27:33</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.54</v>
+        <v>3.02</v>
       </c>
       <c r="F31" t="n">
-        <v>5.81</v>
+        <v>5.68</v>
       </c>
       <c r="G31" t="n">
-        <v>170.8</v>
+        <v>169.3</v>
       </c>
       <c r="H31" t="n">
-        <v>97.40000000000001</v>
+        <v>58.3</v>
       </c>
       <c r="I31" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>60.06</v>
+        <v>-38</v>
       </c>
       <c r="K31" t="n">
-        <v>58.52</v>
+        <v>-29.5</v>
       </c>
       <c r="L31" t="n">
-        <v>83.86</v>
+        <v>48.11</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:34:02</t>
+          <t>07:32:38</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="F32" t="n">
-        <v>9.15</v>
+        <v>10.58</v>
       </c>
       <c r="G32" t="n">
-        <v>172.6</v>
+        <v>185.4</v>
       </c>
       <c r="H32" t="n">
-        <v>92.40000000000001</v>
+        <v>58.9</v>
       </c>
       <c r="I32" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>0.99</v>
+        <v>83.69</v>
       </c>
       <c r="K32" t="n">
-        <v>115.47</v>
+        <v>3.21</v>
       </c>
       <c r="L32" t="n">
-        <v>115.48</v>
+        <v>83.75</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:36:06</t>
+          <t>07:35:07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.52</v>
+        <v>3.38</v>
       </c>
       <c r="F33" t="n">
-        <v>4.74</v>
+        <v>9.02</v>
       </c>
       <c r="G33" t="n">
-        <v>154.9</v>
+        <v>155.6</v>
       </c>
       <c r="H33" t="n">
-        <v>93.59999999999999</v>
+        <v>33.9</v>
       </c>
       <c r="I33" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-45.1</v>
+        <v>-86.63</v>
       </c>
       <c r="K33" t="n">
-        <v>129.77</v>
+        <v>-44.13</v>
       </c>
       <c r="L33" t="n">
-        <v>137.38</v>
+        <v>97.23</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:38:28</t>
+          <t>07:36:14</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.12</v>
+        <v>3.2</v>
       </c>
       <c r="F34" t="n">
-        <v>9.06</v>
+        <v>6.1</v>
       </c>
       <c r="G34" t="n">
-        <v>166.1</v>
+        <v>180.6</v>
       </c>
       <c r="H34" t="n">
-        <v>87</v>
+        <v>53.3</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J34" t="n">
-        <v>-4.57</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>-129.24</v>
+        <v>36.22</v>
       </c>
       <c r="L34" t="n">
-        <v>129.32</v>
+        <v>80.86</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:43:18</t>
+          <t>07:39:59</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.05</v>
+        <v>3.52</v>
       </c>
       <c r="F35" t="n">
-        <v>8.720000000000001</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>173.8</v>
+        <v>166.8</v>
       </c>
       <c r="H35" t="n">
-        <v>89.3</v>
+        <v>48.8</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>136.68</v>
+        <v>-85.38</v>
       </c>
       <c r="K35" t="n">
-        <v>-41.27</v>
+        <v>-77.34999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>142.77</v>
+        <v>115.21</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:44:15</t>
+          <t>07:41:28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.87</v>
+        <v>3.48</v>
       </c>
       <c r="F36" t="n">
-        <v>8.25</v>
+        <v>8.33</v>
       </c>
       <c r="G36" t="n">
-        <v>165.9</v>
+        <v>177.6</v>
       </c>
       <c r="H36" t="n">
-        <v>97.09999999999999</v>
+        <v>48.7</v>
       </c>
       <c r="I36" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>143.23</v>
+        <v>65.37</v>
       </c>
       <c r="K36" t="n">
-        <v>-58.35</v>
+        <v>-111.25</v>
       </c>
       <c r="L36" t="n">
-        <v>154.66</v>
+        <v>129.03</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:45:33</t>
+          <t>07:43:42</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.5</v>
+        <v>3.31</v>
       </c>
       <c r="F37" t="n">
-        <v>10.58</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>178.9</v>
+        <v>153.5</v>
       </c>
       <c r="H37" t="n">
-        <v>90.90000000000001</v>
+        <v>21.2</v>
       </c>
       <c r="I37" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J37" t="n">
-        <v>-164.67</v>
+        <v>-122.31</v>
       </c>
       <c r="K37" t="n">
-        <v>-87.62</v>
+        <v>-58.26</v>
       </c>
       <c r="L37" t="n">
-        <v>186.53</v>
+        <v>135.48</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:49:27</t>
+          <t>07:47:50</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.42</v>
+        <v>2.48</v>
       </c>
       <c r="F38" t="n">
-        <v>8.09</v>
+        <v>6.32</v>
       </c>
       <c r="G38" t="n">
-        <v>161.3</v>
+        <v>175.6</v>
       </c>
       <c r="H38" t="n">
-        <v>91.90000000000001</v>
+        <v>52.7</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>321.69</v>
+        <v>-225.58</v>
       </c>
       <c r="K38" t="n">
-        <v>-5.4</v>
+        <v>25.38</v>
       </c>
       <c r="L38" t="n">
-        <v>321.74</v>
+        <v>227</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:51:33</t>
+          <t>07:49:52</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.56</v>
+        <v>3.46</v>
       </c>
       <c r="F39" t="n">
-        <v>9.24</v>
+        <v>10.58</v>
       </c>
       <c r="G39" t="n">
-        <v>156</v>
+        <v>159.3</v>
       </c>
       <c r="H39" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J39" t="n">
-        <v>-277.37</v>
+        <v>132.76</v>
       </c>
       <c r="K39" t="n">
-        <v>-202.78</v>
+        <v>-82.56</v>
       </c>
       <c r="L39" t="n">
-        <v>343.59</v>
+        <v>156.33</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:53:14</t>
+          <t>07:52:01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="F40" t="n">
-        <v>10.58</v>
+        <v>7.04</v>
       </c>
       <c r="G40" t="n">
-        <v>173.3</v>
+        <v>171.4</v>
       </c>
       <c r="H40" t="n">
-        <v>96.2</v>
+        <v>45.1</v>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J40" t="n">
-        <v>155.03</v>
+        <v>-70.94</v>
       </c>
       <c r="K40" t="n">
-        <v>94.18000000000001</v>
+        <v>163.69</v>
       </c>
       <c r="L40" t="n">
-        <v>181.4</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:56:39</t>
+          <t>07:56:31</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="F41" t="n">
-        <v>9.4</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>157.5</v>
+        <v>163.9</v>
       </c>
       <c r="H41" t="n">
-        <v>90.09999999999999</v>
+        <v>58.2</v>
       </c>
       <c r="I41" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-348.58</v>
+        <v>-36.24</v>
       </c>
       <c r="K41" t="n">
-        <v>-46.28</v>
+        <v>-167.3</v>
       </c>
       <c r="L41" t="n">
-        <v>351.64</v>
+        <v>171.18</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:59:03</t>
+          <t>07:58:12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.43</v>
+        <v>3.37</v>
       </c>
       <c r="F42" t="n">
-        <v>9.289999999999999</v>
+        <v>6.48</v>
       </c>
       <c r="G42" t="n">
-        <v>171.9</v>
+        <v>165.2</v>
       </c>
       <c r="H42" t="n">
-        <v>96.90000000000001</v>
+        <v>61.7</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J42" t="n">
-        <v>281.2</v>
+        <v>-30.61</v>
       </c>
       <c r="K42" t="n">
-        <v>-294.69</v>
+        <v>-171.49</v>
       </c>
       <c r="L42" t="n">
-        <v>407.32</v>
+        <v>174.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:01:27</t>
+          <t>07:59:05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.83</v>
+        <v>3.14</v>
       </c>
       <c r="F43" t="n">
-        <v>10.58</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>152.5</v>
+        <v>166</v>
       </c>
       <c r="H43" t="n">
-        <v>93</v>
+        <v>47.1</v>
       </c>
       <c r="I43" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>-320.73</v>
+        <v>143.14</v>
       </c>
       <c r="K43" t="n">
-        <v>142.9</v>
+        <v>-187.61</v>
       </c>
       <c r="L43" t="n">
-        <v>351.12</v>
+        <v>235.98</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:11:04</t>
+          <t>08:08:01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.82</v>
+        <v>2.95</v>
       </c>
       <c r="F44" t="n">
-        <v>10.58</v>
+        <v>6.81</v>
       </c>
       <c r="G44" t="n">
-        <v>162</v>
+        <v>170.6</v>
       </c>
       <c r="H44" t="n">
-        <v>91.7</v>
+        <v>68.7</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.52</v>
+        <v>52.95</v>
       </c>
       <c r="K44" t="n">
-        <v>110.53</v>
+        <v>31.87</v>
       </c>
       <c r="L44" t="n">
-        <v>110.54</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:12:37</t>
+          <t>08:09:59</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.24</v>
+        <v>3.74</v>
       </c>
       <c r="F45" t="n">
-        <v>8.970000000000001</v>
+        <v>9.65</v>
       </c>
       <c r="G45" t="n">
-        <v>166.6</v>
+        <v>168.6</v>
       </c>
       <c r="H45" t="n">
-        <v>92.8</v>
+        <v>71.3</v>
       </c>
       <c r="I45" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>-66.61</v>
+        <v>47.23</v>
       </c>
       <c r="K45" t="n">
-        <v>50.1</v>
+        <v>-51.05</v>
       </c>
       <c r="L45" t="n">
-        <v>83.34999999999999</v>
+        <v>69.55</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:13:45</t>
+          <t>08:11:24</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.57</v>
+        <v>3.17</v>
       </c>
       <c r="F46" t="n">
         <v>10.58</v>
       </c>
       <c r="G46" t="n">
-        <v>164</v>
+        <v>169.6</v>
       </c>
       <c r="H46" t="n">
-        <v>100</v>
+        <v>25.6</v>
       </c>
       <c r="I46" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J46" t="n">
-        <v>-88.73</v>
+        <v>-51.09</v>
       </c>
       <c r="K46" t="n">
-        <v>-3.02</v>
+        <v>20.93</v>
       </c>
       <c r="L46" t="n">
-        <v>88.78</v>
+        <v>55.21</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:18:22</t>
+          <t>08:16:40</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.22</v>
+        <v>3.72</v>
       </c>
       <c r="F47" t="n">
-        <v>9.390000000000001</v>
+        <v>10.58</v>
       </c>
       <c r="G47" t="n">
-        <v>149.6</v>
+        <v>157.2</v>
       </c>
       <c r="H47" t="n">
-        <v>99.40000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="I47" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>109.35</v>
+        <v>-91.25</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.17</v>
+        <v>-9.52</v>
       </c>
       <c r="L47" t="n">
-        <v>109.35</v>
+        <v>91.75</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:19:37</t>
+          <t>08:17:26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.48</v>
+        <v>3.33</v>
       </c>
       <c r="F48" t="n">
-        <v>9.470000000000001</v>
+        <v>9.91</v>
       </c>
       <c r="G48" t="n">
-        <v>173.6</v>
+        <v>172.2</v>
       </c>
       <c r="H48" t="n">
-        <v>100</v>
+        <v>12.9</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-68.31</v>
+        <v>-78.22</v>
       </c>
       <c r="K48" t="n">
-        <v>-76.52</v>
+        <v>-26.08</v>
       </c>
       <c r="L48" t="n">
-        <v>102.58</v>
+        <v>82.45999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:22:05</t>
+          <t>08:19:26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="F49" t="n">
-        <v>8.99</v>
+        <v>9.76</v>
       </c>
       <c r="G49" t="n">
-        <v>157.7</v>
+        <v>154.5</v>
       </c>
       <c r="H49" t="n">
-        <v>92</v>
+        <v>56.4</v>
       </c>
       <c r="I49" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>5.65</v>
+        <v>85.41</v>
       </c>
       <c r="K49" t="n">
-        <v>-151.98</v>
+        <v>-33.08</v>
       </c>
       <c r="L49" t="n">
-        <v>152.09</v>
+        <v>91.59</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:26:37</t>
+          <t>08:24:47</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.61</v>
+        <v>3.77</v>
       </c>
       <c r="F50" t="n">
-        <v>9.5</v>
+        <v>10.58</v>
       </c>
       <c r="G50" t="n">
-        <v>159</v>
+        <v>169.3</v>
       </c>
       <c r="H50" t="n">
-        <v>84.7</v>
+        <v>61.2</v>
       </c>
       <c r="I50" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J50" t="n">
-        <v>-211.01</v>
+        <v>-71.68000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>-43.39</v>
+        <v>73.02</v>
       </c>
       <c r="L50" t="n">
-        <v>215.42</v>
+        <v>102.32</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:28:19</t>
+          <t>08:26:12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="F51" t="n">
-        <v>7.37</v>
+        <v>8.69</v>
       </c>
       <c r="G51" t="n">
-        <v>181.7</v>
+        <v>155</v>
       </c>
       <c r="H51" t="n">
-        <v>96.90000000000001</v>
+        <v>55.5</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J51" t="n">
-        <v>39.85</v>
+        <v>39.79</v>
       </c>
       <c r="K51" t="n">
-        <v>-180.12</v>
+        <v>-119.76</v>
       </c>
       <c r="L51" t="n">
-        <v>184.48</v>
+        <v>126.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:30:10</t>
+          <t>08:27:19</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.79</v>
+        <v>3.5</v>
       </c>
       <c r="F52" t="n">
-        <v>9.52</v>
+        <v>10.58</v>
       </c>
       <c r="G52" t="n">
-        <v>154.5</v>
+        <v>154.4</v>
       </c>
       <c r="H52" t="n">
-        <v>94.5</v>
+        <v>50.5</v>
       </c>
       <c r="I52" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J52" t="n">
-        <v>170.99</v>
+        <v>1.47</v>
       </c>
       <c r="K52" t="n">
-        <v>13.2</v>
+        <v>-126.76</v>
       </c>
       <c r="L52" t="n">
-        <v>171.5</v>
+        <v>126.77</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:35:09</t>
+          <t>08:31:34</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.99</v>
+        <v>4.14</v>
       </c>
       <c r="F53" t="n">
-        <v>9.470000000000001</v>
+        <v>10.58</v>
       </c>
       <c r="G53" t="n">
-        <v>174</v>
+        <v>168.1</v>
       </c>
       <c r="H53" t="n">
-        <v>90.3</v>
+        <v>51.3</v>
       </c>
       <c r="I53" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>68.06</v>
+        <v>274.43</v>
       </c>
       <c r="K53" t="n">
-        <v>237.23</v>
+        <v>-127.07</v>
       </c>
       <c r="L53" t="n">
-        <v>246.8</v>
+        <v>302.42</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:35:51</t>
+          <t>08:32:45</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.59</v>
+        <v>3.4</v>
       </c>
       <c r="F54" t="n">
-        <v>10.58</v>
+        <v>5.66</v>
       </c>
       <c r="G54" t="n">
-        <v>160.6</v>
+        <v>166.1</v>
       </c>
       <c r="H54" t="n">
-        <v>93.7</v>
+        <v>74</v>
       </c>
       <c r="I54" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="J54" t="n">
-        <v>122.98</v>
+        <v>133.52</v>
       </c>
       <c r="K54" t="n">
-        <v>-192.05</v>
+        <v>-97.33</v>
       </c>
       <c r="L54" t="n">
-        <v>228.05</v>
+        <v>165.23</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:38:03</t>
+          <t>08:35:04</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.16</v>
+        <v>3.76</v>
       </c>
       <c r="F55" t="n">
-        <v>9.279999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>166.1</v>
+        <v>167.8</v>
       </c>
       <c r="H55" t="n">
-        <v>98.3</v>
+        <v>83.7</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>102.08</v>
+        <v>-202.13</v>
       </c>
       <c r="K55" t="n">
-        <v>-256.48</v>
+        <v>-58.9</v>
       </c>
       <c r="L55" t="n">
-        <v>276.05</v>
+        <v>210.53</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:42:30</t>
+          <t>08:39:57</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.58</v>
+        <v>3.41</v>
       </c>
       <c r="F56" t="n">
-        <v>10.58</v>
+        <v>8.6</v>
       </c>
       <c r="G56" t="n">
-        <v>162.9</v>
+        <v>156.1</v>
       </c>
       <c r="H56" t="n">
-        <v>93.09999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J56" t="n">
-        <v>-47.91</v>
+        <v>25.46</v>
       </c>
       <c r="K56" t="n">
-        <v>-267.11</v>
+        <v>-233.91</v>
       </c>
       <c r="L56" t="n">
-        <v>271.38</v>
+        <v>235.29</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:44:49</t>
+          <t>08:41:24</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.75</v>
+        <v>3.09</v>
       </c>
       <c r="F57" t="n">
-        <v>10.58</v>
+        <v>7.3</v>
       </c>
       <c r="G57" t="n">
-        <v>158</v>
+        <v>163.1</v>
       </c>
       <c r="H57" t="n">
-        <v>96.09999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J57" t="n">
-        <v>312.97</v>
+        <v>151.72</v>
       </c>
       <c r="K57" t="n">
-        <v>132.04</v>
+        <v>-113.71</v>
       </c>
       <c r="L57" t="n">
-        <v>339.69</v>
+        <v>189.6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:46:51</t>
+          <t>08:43:59</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.05</v>
+        <v>3.67</v>
       </c>
       <c r="F58" t="n">
-        <v>9.15</v>
+        <v>10.58</v>
       </c>
       <c r="G58" t="n">
-        <v>166.8</v>
+        <v>167.6</v>
       </c>
       <c r="H58" t="n">
-        <v>88.2</v>
+        <v>40.5</v>
       </c>
       <c r="I58" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>249.84</v>
+        <v>81.81</v>
       </c>
       <c r="K58" t="n">
-        <v>-81.88</v>
+        <v>-217.27</v>
       </c>
       <c r="L58" t="n">
-        <v>262.91</v>
+        <v>232.16</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:55:27</t>
+          <t>08:52:52</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="F59" t="n">
-        <v>10.58</v>
+        <v>7.3</v>
       </c>
       <c r="G59" t="n">
-        <v>165.7</v>
+        <v>167.6</v>
       </c>
       <c r="H59" t="n">
-        <v>93.3</v>
+        <v>52.1</v>
       </c>
       <c r="I59" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J59" t="n">
-        <v>8.300000000000001</v>
+        <v>-33.92</v>
       </c>
       <c r="K59" t="n">
-        <v>94.55</v>
+        <v>53.84</v>
       </c>
       <c r="L59" t="n">
-        <v>94.92</v>
+        <v>63.63</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:58:13</t>
+          <t>08:54:13</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="F60" t="n">
-        <v>7.5</v>
+        <v>10.21</v>
       </c>
       <c r="G60" t="n">
-        <v>178.8</v>
+        <v>147.5</v>
       </c>
       <c r="H60" t="n">
-        <v>91.90000000000001</v>
+        <v>63.1</v>
       </c>
       <c r="I60" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J60" t="n">
-        <v>27.07</v>
+        <v>-24.44</v>
       </c>
       <c r="K60" t="n">
-        <v>-111.78</v>
+        <v>60.42</v>
       </c>
       <c r="L60" t="n">
-        <v>115.01</v>
+        <v>65.18000000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:00:10</t>
+          <t>08:55:54</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.08</v>
+        <v>3.82</v>
       </c>
       <c r="F61" t="n">
         <v>10.58</v>
       </c>
       <c r="G61" t="n">
-        <v>176.5</v>
+        <v>152.2</v>
       </c>
       <c r="H61" t="n">
-        <v>89</v>
+        <v>55.1</v>
       </c>
       <c r="I61" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>-27.15</v>
+        <v>-47.49</v>
       </c>
       <c r="K61" t="n">
-        <v>-73.54000000000001</v>
+        <v>47.15</v>
       </c>
       <c r="L61" t="n">
-        <v>78.39</v>
+        <v>66.92</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:04:53</t>
+          <t>09:01:16</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.38</v>
+        <v>3.67</v>
       </c>
       <c r="F62" t="n">
-        <v>9.92</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="G62" t="n">
-        <v>166.9</v>
+        <v>151.6</v>
       </c>
       <c r="H62" t="n">
-        <v>97.2</v>
+        <v>63</v>
       </c>
       <c r="I62" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-25.18</v>
+        <v>74.03</v>
       </c>
       <c r="K62" t="n">
-        <v>135.3</v>
+        <v>-54.05</v>
       </c>
       <c r="L62" t="n">
-        <v>137.62</v>
+        <v>91.66</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:06:14</t>
+          <t>09:02:29</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.09</v>
+        <v>3.59</v>
       </c>
       <c r="F63" t="n">
         <v>10.58</v>
       </c>
       <c r="G63" t="n">
-        <v>175</v>
+        <v>164.9</v>
       </c>
       <c r="H63" t="n">
-        <v>100</v>
+        <v>70.8</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>10.9</v>
+        <v>105.18</v>
       </c>
       <c r="K63" t="n">
-        <v>-92.23999999999999</v>
+        <v>-12.05</v>
       </c>
       <c r="L63" t="n">
-        <v>92.88</v>
+        <v>105.87</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:07:41</t>
+          <t>09:03:57</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.49</v>
+        <v>3.8</v>
       </c>
       <c r="F64" t="n">
-        <v>10.58</v>
+        <v>9.25</v>
       </c>
       <c r="G64" t="n">
-        <v>159.7</v>
+        <v>173</v>
       </c>
       <c r="H64" t="n">
-        <v>95.3</v>
+        <v>56.6</v>
       </c>
       <c r="I64" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J64" t="n">
-        <v>105.81</v>
+        <v>-90.83</v>
       </c>
       <c r="K64" t="n">
-        <v>63.71</v>
+        <v>-40.94</v>
       </c>
       <c r="L64" t="n">
-        <v>123.51</v>
+        <v>99.63</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:12:50</t>
+          <t>09:09:17</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.79</v>
+        <v>3.48</v>
       </c>
       <c r="F65" t="n">
-        <v>9.19</v>
+        <v>8.34</v>
       </c>
       <c r="G65" t="n">
-        <v>168.9</v>
+        <v>174</v>
       </c>
       <c r="H65" t="n">
-        <v>88.09999999999999</v>
+        <v>61.4</v>
       </c>
       <c r="I65" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>-30.7</v>
+        <v>72.83</v>
       </c>
       <c r="K65" t="n">
-        <v>-247.48</v>
+        <v>44.43</v>
       </c>
       <c r="L65" t="n">
-        <v>249.37</v>
+        <v>85.31</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:14:37</t>
+          <t>09:10:50</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.21</v>
+        <v>3.76</v>
       </c>
       <c r="F66" t="n">
-        <v>7.99</v>
+        <v>10.58</v>
       </c>
       <c r="G66" t="n">
-        <v>155.9</v>
+        <v>172.4</v>
       </c>
       <c r="H66" t="n">
-        <v>96</v>
+        <v>55.2</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>-18.45</v>
+        <v>-101.65</v>
       </c>
       <c r="K66" t="n">
-        <v>31.95</v>
+        <v>82.66</v>
       </c>
       <c r="L66" t="n">
-        <v>36.89</v>
+        <v>131.01</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:15:47</t>
+          <t>09:12:11</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.26</v>
+        <v>3.76</v>
       </c>
       <c r="F67" t="n">
         <v>10.58</v>
       </c>
       <c r="G67" t="n">
-        <v>171.1</v>
+        <v>168.3</v>
       </c>
       <c r="H67" t="n">
-        <v>93.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-55.06</v>
+        <v>-11</v>
       </c>
       <c r="K67" t="n">
-        <v>187.57</v>
+        <v>-126.46</v>
       </c>
       <c r="L67" t="n">
-        <v>195.48</v>
+        <v>126.94</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:20:48</t>
+          <t>09:16:45</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="F68" t="n">
-        <v>10.25</v>
+        <v>7.89</v>
       </c>
       <c r="G68" t="n">
-        <v>169.9</v>
+        <v>172.8</v>
       </c>
       <c r="H68" t="n">
-        <v>100</v>
+        <v>24.6</v>
       </c>
       <c r="I68" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J68" t="n">
-        <v>-117.45</v>
+        <v>4.68</v>
       </c>
       <c r="K68" t="n">
-        <v>-217.1</v>
+        <v>-137.09</v>
       </c>
       <c r="L68" t="n">
-        <v>246.83</v>
+        <v>137.17</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:22:43</t>
+          <t>09:17:21</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.73</v>
+        <v>3.61</v>
       </c>
       <c r="F69" t="n">
         <v>10.58</v>
       </c>
       <c r="G69" t="n">
-        <v>155.6</v>
+        <v>154.5</v>
       </c>
       <c r="H69" t="n">
-        <v>89.2</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>72.52</v>
+        <v>166.46</v>
       </c>
       <c r="K69" t="n">
-        <v>206.96</v>
+        <v>51.05</v>
       </c>
       <c r="L69" t="n">
-        <v>219.3</v>
+        <v>174.11</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:24:15</t>
+          <t>09:18:59</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="F70" t="n">
-        <v>9.92</v>
+        <v>10.43</v>
       </c>
       <c r="G70" t="n">
-        <v>183.8</v>
+        <v>158.4</v>
       </c>
       <c r="H70" t="n">
-        <v>93.90000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J70" t="n">
-        <v>-67.89</v>
+        <v>66.81</v>
       </c>
       <c r="K70" t="n">
-        <v>217.51</v>
+        <v>-187.95</v>
       </c>
       <c r="L70" t="n">
-        <v>227.86</v>
+        <v>199.47</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:29:31</t>
+          <t>09:23:14</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.75</v>
+        <v>3.61</v>
       </c>
       <c r="F71" t="n">
-        <v>10.58</v>
+        <v>9.49</v>
       </c>
       <c r="G71" t="n">
-        <v>160.5</v>
+        <v>171.1</v>
       </c>
       <c r="H71" t="n">
-        <v>97.7</v>
+        <v>45.5</v>
       </c>
       <c r="I71" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>-317.4</v>
+        <v>-285.57</v>
       </c>
       <c r="K71" t="n">
-        <v>-12.47</v>
+        <v>-77.61</v>
       </c>
       <c r="L71" t="n">
-        <v>317.64</v>
+        <v>295.93</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:31:25</t>
+          <t>09:24:39</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.68</v>
+        <v>3.51</v>
       </c>
       <c r="F72" t="n">
-        <v>10.46</v>
+        <v>8.19</v>
       </c>
       <c r="G72" t="n">
-        <v>158.4</v>
+        <v>151.6</v>
       </c>
       <c r="H72" t="n">
-        <v>92.09999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="I72" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J72" t="n">
-        <v>-284.55</v>
+        <v>-66.61</v>
       </c>
       <c r="K72" t="n">
-        <v>-14.61</v>
+        <v>186.77</v>
       </c>
       <c r="L72" t="n">
-        <v>284.92</v>
+        <v>198.29</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:32:43</t>
+          <t>09:26:50</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.29</v>
+        <v>3.83</v>
       </c>
       <c r="F73" t="n">
-        <v>7.46</v>
+        <v>10.24</v>
       </c>
       <c r="G73" t="n">
-        <v>177.6</v>
+        <v>156.2</v>
       </c>
       <c r="H73" t="n">
-        <v>92.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="I73" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J73" t="n">
-        <v>-129.21</v>
+        <v>-13.26</v>
       </c>
       <c r="K73" t="n">
-        <v>65.65000000000001</v>
+        <v>-224.42</v>
       </c>
       <c r="L73" t="n">
-        <v>144.93</v>
+        <v>224.81</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:41:06</t>
+          <t>09:35:45</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.03</v>
+        <v>3.66</v>
       </c>
       <c r="F74" t="n">
-        <v>10.58</v>
+        <v>6.9</v>
       </c>
       <c r="G74" t="n">
-        <v>167.5</v>
+        <v>152.6</v>
       </c>
       <c r="H74" t="n">
-        <v>95.09999999999999</v>
+        <v>53.6</v>
       </c>
       <c r="I74" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J74" t="n">
-        <v>49.9</v>
+        <v>58.59</v>
       </c>
       <c r="K74" t="n">
-        <v>-112.36</v>
+        <v>-3.28</v>
       </c>
       <c r="L74" t="n">
-        <v>122.94</v>
+        <v>58.68</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:42:57</t>
+          <t>09:36:39</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="F75" t="n">
-        <v>7.9</v>
+        <v>9.25</v>
       </c>
       <c r="G75" t="n">
-        <v>151.5</v>
+        <v>157.4</v>
       </c>
       <c r="H75" t="n">
-        <v>93.3</v>
+        <v>79.3</v>
       </c>
       <c r="I75" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J75" t="n">
-        <v>-142.39</v>
+        <v>56.84</v>
       </c>
       <c r="K75" t="n">
-        <v>-14.07</v>
+        <v>-2.8</v>
       </c>
       <c r="L75" t="n">
-        <v>143.08</v>
+        <v>56.91</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:44:50</t>
+          <t>09:37:59</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="F76" t="n">
-        <v>10.58</v>
+        <v>10.18</v>
       </c>
       <c r="G76" t="n">
-        <v>165.6</v>
+        <v>163.6</v>
       </c>
       <c r="H76" t="n">
-        <v>99.40000000000001</v>
+        <v>59.4</v>
       </c>
       <c r="I76" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J76" t="n">
-        <v>70.48999999999999</v>
+        <v>20.4</v>
       </c>
       <c r="K76" t="n">
-        <v>57.23</v>
+        <v>-55.9</v>
       </c>
       <c r="L76" t="n">
-        <v>90.8</v>
+        <v>59.51</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:50:18</t>
+          <t>09:41:36</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.76</v>
+        <v>3.88</v>
       </c>
       <c r="F77" t="n">
-        <v>8.92</v>
+        <v>10.58</v>
       </c>
       <c r="G77" t="n">
-        <v>173</v>
+        <v>168.4</v>
       </c>
       <c r="H77" t="n">
-        <v>90.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I77" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>-64.51000000000001</v>
+        <v>-87.31999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>99.92</v>
+        <v>-37.84</v>
       </c>
       <c r="L77" t="n">
-        <v>118.93</v>
+        <v>95.17</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:51:18</t>
+          <t>09:42:43</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.6</v>
+        <v>3.43</v>
       </c>
       <c r="F78" t="n">
-        <v>10.58</v>
+        <v>7.62</v>
       </c>
       <c r="G78" t="n">
-        <v>177.9</v>
+        <v>171.4</v>
       </c>
       <c r="H78" t="n">
-        <v>94.2</v>
+        <v>69</v>
       </c>
       <c r="I78" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-141.06</v>
+        <v>-38.38</v>
       </c>
       <c r="K78" t="n">
-        <v>-70.88</v>
+        <v>-81.93000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>157.87</v>
+        <v>90.47</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:52:09</t>
+          <t>09:43:39</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="F79" t="n">
-        <v>8.5</v>
+        <v>9.31</v>
       </c>
       <c r="G79" t="n">
-        <v>164.1</v>
+        <v>169</v>
       </c>
       <c r="H79" t="n">
-        <v>92.3</v>
+        <v>69.8</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-59.54</v>
+        <v>82.81</v>
       </c>
       <c r="K79" t="n">
-        <v>-81.18000000000001</v>
+        <v>-33.97</v>
       </c>
       <c r="L79" t="n">
-        <v>100.68</v>
+        <v>89.51000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:56:03</t>
+          <t>09:48:04</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.91</v>
+        <v>3.29</v>
       </c>
       <c r="F80" t="n">
-        <v>10.58</v>
+        <v>10.54</v>
       </c>
       <c r="G80" t="n">
-        <v>168.1</v>
+        <v>179.7</v>
       </c>
       <c r="H80" t="n">
-        <v>93</v>
+        <v>60.9</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-143.69</v>
+        <v>-85.89</v>
       </c>
       <c r="K80" t="n">
-        <v>-153.96</v>
+        <v>-64.48</v>
       </c>
       <c r="L80" t="n">
-        <v>210.59</v>
+        <v>107.4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:58:03</t>
+          <t>09:50:44</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="F81" t="n">
-        <v>10.37</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="G81" t="n">
-        <v>167.2</v>
+        <v>171.5</v>
       </c>
       <c r="H81" t="n">
-        <v>88.3</v>
+        <v>31.7</v>
       </c>
       <c r="I81" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J81" t="n">
-        <v>120.35</v>
+        <v>-3.67</v>
       </c>
       <c r="K81" t="n">
-        <v>-68.94</v>
+        <v>116.55</v>
       </c>
       <c r="L81" t="n">
-        <v>138.7</v>
+        <v>116.6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:00:23</t>
+          <t>09:51:20</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.27</v>
+        <v>3.56</v>
       </c>
       <c r="F82" t="n">
-        <v>9.5</v>
+        <v>10.58</v>
       </c>
       <c r="G82" t="n">
-        <v>149.3</v>
+        <v>175</v>
       </c>
       <c r="H82" t="n">
-        <v>98.7</v>
+        <v>51.9</v>
       </c>
       <c r="I82" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J82" t="n">
-        <v>164.8</v>
+        <v>108.18</v>
       </c>
       <c r="K82" t="n">
-        <v>-41.58</v>
+        <v>-102.22</v>
       </c>
       <c r="L82" t="n">
-        <v>169.97</v>
+        <v>148.83</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:05:31</t>
+          <t>09:55:36</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.87</v>
+        <v>3.28</v>
       </c>
       <c r="F83" t="n">
-        <v>10.58</v>
+        <v>10.54</v>
       </c>
       <c r="G83" t="n">
-        <v>174.5</v>
+        <v>158</v>
       </c>
       <c r="H83" t="n">
-        <v>85.2</v>
+        <v>63.2</v>
       </c>
       <c r="I83" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>-65.37</v>
+        <v>161.32</v>
       </c>
       <c r="K83" t="n">
-        <v>-279.64</v>
+        <v>-133.88</v>
       </c>
       <c r="L83" t="n">
-        <v>287.18</v>
+        <v>209.64</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:07:16</t>
+          <t>09:58:10</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.3</v>
+        <v>3.86</v>
       </c>
       <c r="F84" t="n">
-        <v>8.380000000000001</v>
+        <v>8.19</v>
       </c>
       <c r="G84" t="n">
-        <v>170.6</v>
+        <v>158.3</v>
       </c>
       <c r="H84" t="n">
-        <v>96.09999999999999</v>
+        <v>49.1</v>
       </c>
       <c r="I84" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>49.31</v>
+        <v>232.89</v>
       </c>
       <c r="K84" t="n">
-        <v>207.13</v>
+        <v>-11.92</v>
       </c>
       <c r="L84" t="n">
-        <v>212.91</v>
+        <v>233.19</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:09:37</t>
+          <t>10:00:15</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.4</v>
+        <v>5.01</v>
       </c>
       <c r="F85" t="n">
         <v>10.58</v>
       </c>
       <c r="G85" t="n">
-        <v>164.5</v>
+        <v>151.2</v>
       </c>
       <c r="H85" t="n">
-        <v>88.90000000000001</v>
+        <v>33</v>
       </c>
       <c r="I85" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>193.87</v>
+        <v>-48.72</v>
       </c>
       <c r="K85" t="n">
-        <v>-47.05</v>
+        <v>-472.3</v>
       </c>
       <c r="L85" t="n">
-        <v>199.5</v>
+        <v>474.81</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:14:21</t>
+          <t>10:04:47</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="F86" t="n">
-        <v>10.58</v>
+        <v>7.2</v>
       </c>
       <c r="G86" t="n">
-        <v>166.7</v>
+        <v>170.3</v>
       </c>
       <c r="H86" t="n">
-        <v>93.59999999999999</v>
+        <v>42.8</v>
       </c>
       <c r="I86" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-264.48</v>
+        <v>264.17</v>
       </c>
       <c r="K86" t="n">
-        <v>64.47</v>
+        <v>-78.41</v>
       </c>
       <c r="L86" t="n">
-        <v>272.22</v>
+        <v>275.57</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:15:03</t>
+          <t>10:06:25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.59</v>
+        <v>3.85</v>
       </c>
       <c r="F87" t="n">
         <v>10.58</v>
       </c>
       <c r="G87" t="n">
-        <v>167.4</v>
+        <v>167.8</v>
       </c>
       <c r="H87" t="n">
-        <v>96.90000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>431.38</v>
+        <v>-242.6</v>
       </c>
       <c r="K87" t="n">
-        <v>-67.62</v>
+        <v>59.68</v>
       </c>
       <c r="L87" t="n">
-        <v>436.65</v>
+        <v>249.84</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:17:31</t>
+          <t>10:08:09</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.07</v>
+        <v>3.94</v>
       </c>
       <c r="F88" t="n">
         <v>10.58</v>
       </c>
       <c r="G88" t="n">
-        <v>175.6</v>
+        <v>158.6</v>
       </c>
       <c r="H88" t="n">
-        <v>96.09999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="I88" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J88" t="n">
-        <v>-321.08</v>
+        <v>135.94</v>
       </c>
       <c r="K88" t="n">
-        <v>-101.49</v>
+        <v>-278.9</v>
       </c>
       <c r="L88" t="n">
-        <v>336.74</v>
+        <v>310.26</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-02.xlsx
+++ b/output/2024-04-02.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.41</v>
+        <v>2.77</v>
       </c>
       <c r="F14" t="n">
-        <v>10.58</v>
+        <v>7.51</v>
       </c>
       <c r="G14" t="n">
-        <v>175.4</v>
+        <v>163.1</v>
       </c>
       <c r="H14" t="n">
-        <v>50.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>32.9</v>
+        <v>0.22</v>
       </c>
       <c r="K14" t="n">
-        <v>-25.02</v>
+        <v>-25.56</v>
       </c>
       <c r="L14" t="n">
-        <v>41.33</v>
+        <v>25.56</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:42:19</t>
+          <t>06:41:59</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.48</v>
+        <v>2.68</v>
       </c>
       <c r="F15" t="n">
-        <v>9.33</v>
+        <v>6.73</v>
       </c>
       <c r="G15" t="n">
-        <v>173.2</v>
+        <v>173.3</v>
       </c>
       <c r="H15" t="n">
-        <v>48.6</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>49.29</v>
+        <v>-13.69</v>
       </c>
       <c r="K15" t="n">
-        <v>21.75</v>
+        <v>43.27</v>
       </c>
       <c r="L15" t="n">
-        <v>53.87</v>
+        <v>45.39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:43:26</t>
+          <t>06:44:11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="F16" t="n">
-        <v>7.2</v>
+        <v>5.39</v>
       </c>
       <c r="G16" t="n">
-        <v>172.3</v>
+        <v>169.6</v>
       </c>
       <c r="H16" t="n">
-        <v>44.4</v>
+        <v>62.9</v>
       </c>
       <c r="I16" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-21.73</v>
+        <v>-15.6</v>
       </c>
       <c r="K16" t="n">
-        <v>52.92</v>
+        <v>-45.05</v>
       </c>
       <c r="L16" t="n">
-        <v>57.21</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:48:03</t>
+          <t>06:48:23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.21</v>
+        <v>2.77</v>
       </c>
       <c r="F17" t="n">
-        <v>10.58</v>
+        <v>6.2</v>
       </c>
       <c r="G17" t="n">
-        <v>176.5</v>
+        <v>163.7</v>
       </c>
       <c r="H17" t="n">
-        <v>56.8</v>
+        <v>62.5</v>
       </c>
       <c r="I17" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>6.23</v>
+        <v>50.55</v>
       </c>
       <c r="K17" t="n">
-        <v>-86.09</v>
+        <v>-1.61</v>
       </c>
       <c r="L17" t="n">
-        <v>86.31999999999999</v>
+        <v>50.57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:50:34</t>
+          <t>06:49:56</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.06</v>
+        <v>3.16</v>
       </c>
       <c r="F18" t="n">
-        <v>9.17</v>
+        <v>7.05</v>
       </c>
       <c r="G18" t="n">
-        <v>163.5</v>
+        <v>166.7</v>
       </c>
       <c r="H18" t="n">
-        <v>64.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>-63.09</v>
+        <v>-62.18</v>
       </c>
       <c r="K18" t="n">
-        <v>43.87</v>
+        <v>-58.22</v>
       </c>
       <c r="L18" t="n">
-        <v>76.84</v>
+        <v>85.18000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:51:15</t>
+          <t>06:51:17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="F19" t="n">
-        <v>3.74</v>
+        <v>6.46</v>
       </c>
       <c r="G19" t="n">
-        <v>165</v>
+        <v>171.7</v>
       </c>
       <c r="H19" t="n">
-        <v>76.2</v>
+        <v>74.2</v>
       </c>
       <c r="I19" t="n">
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>77.73999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-42.1</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>88.41</v>
+        <v>66.97</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:56:39</t>
+          <t>06:55:03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.33</v>
+        <v>2.91</v>
       </c>
       <c r="F20" t="n">
-        <v>9.210000000000001</v>
+        <v>8.06</v>
       </c>
       <c r="G20" t="n">
-        <v>181.7</v>
+        <v>176.5</v>
       </c>
       <c r="H20" t="n">
-        <v>72.5</v>
+        <v>56.8</v>
       </c>
       <c r="I20" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>-83.73999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="K20" t="n">
-        <v>18.34</v>
+        <v>-106.86</v>
       </c>
       <c r="L20" t="n">
-        <v>85.73</v>
+        <v>107.17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:57:41</t>
+          <t>06:56:41</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -922,31 +922,31 @@
         <v>3.09</v>
       </c>
       <c r="F21" t="n">
-        <v>8.32</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>154.3</v>
+        <v>163.8</v>
       </c>
       <c r="H21" t="n">
-        <v>67</v>
+        <v>52.4</v>
       </c>
       <c r="I21" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>45.06</v>
+        <v>-16.55</v>
       </c>
       <c r="K21" t="n">
-        <v>-59.44</v>
+        <v>113.34</v>
       </c>
       <c r="L21" t="n">
-        <v>74.59</v>
+        <v>114.55</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:58:31</t>
+          <t>06:59:17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.22</v>
+        <v>2.82</v>
       </c>
       <c r="F22" t="n">
-        <v>9.050000000000001</v>
+        <v>3.85</v>
       </c>
       <c r="G22" t="n">
-        <v>188.7</v>
+        <v>173</v>
       </c>
       <c r="H22" t="n">
-        <v>74.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J22" t="n">
-        <v>-25.27</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-110.54</v>
+        <v>-22.21</v>
       </c>
       <c r="L22" t="n">
-        <v>113.39</v>
+        <v>81.78</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:03:17</t>
+          <t>07:03:33</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.8</v>
+        <v>2.77</v>
       </c>
       <c r="F23" t="n">
-        <v>8.619999999999999</v>
+        <v>6.05</v>
       </c>
       <c r="G23" t="n">
-        <v>165</v>
+        <v>181.7</v>
       </c>
       <c r="H23" t="n">
-        <v>59</v>
+        <v>72.5</v>
       </c>
       <c r="I23" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-186.37</v>
+        <v>-102.76</v>
       </c>
       <c r="K23" t="n">
-        <v>98.17</v>
+        <v>53.81</v>
       </c>
       <c r="L23" t="n">
-        <v>210.65</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:05:03</t>
+          <t>07:05:22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.98</v>
+        <v>3.12</v>
       </c>
       <c r="F24" t="n">
-        <v>7.29</v>
+        <v>8.44</v>
       </c>
       <c r="G24" t="n">
-        <v>174.3</v>
+        <v>169.3</v>
       </c>
       <c r="H24" t="n">
-        <v>53.6</v>
+        <v>80.5</v>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>92.8</v>
+        <v>-123.71</v>
       </c>
       <c r="K24" t="n">
-        <v>-106.13</v>
+        <v>-136.4</v>
       </c>
       <c r="L24" t="n">
-        <v>140.98</v>
+        <v>184.14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:07:38</t>
+          <t>07:06:54</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.5</v>
+        <v>3.21</v>
       </c>
       <c r="F25" t="n">
-        <v>6.6</v>
+        <v>10.58</v>
       </c>
       <c r="G25" t="n">
-        <v>154.2</v>
+        <v>188.7</v>
       </c>
       <c r="H25" t="n">
-        <v>69.2</v>
+        <v>74.3</v>
       </c>
       <c r="I25" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J25" t="n">
-        <v>-138.3</v>
+        <v>-43.82</v>
       </c>
       <c r="K25" t="n">
-        <v>-135.38</v>
+        <v>-175.35</v>
       </c>
       <c r="L25" t="n">
-        <v>193.53</v>
+        <v>180.74</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:10:45</t>
+          <t>07:12:59</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.51</v>
+        <v>3.84</v>
       </c>
       <c r="F26" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>153</v>
+        <v>166.1</v>
       </c>
       <c r="H26" t="n">
-        <v>57.9</v>
+        <v>79.5</v>
       </c>
       <c r="I26" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>-190.77</v>
+        <v>-11.13</v>
       </c>
       <c r="K26" t="n">
-        <v>10.53</v>
+        <v>-212.09</v>
       </c>
       <c r="L26" t="n">
-        <v>191.06</v>
+        <v>212.38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:12:05</t>
+          <t>07:14:57</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.01</v>
+        <v>3.3</v>
       </c>
       <c r="F27" t="n">
-        <v>7.37</v>
+        <v>7.77</v>
       </c>
       <c r="G27" t="n">
-        <v>165.5</v>
+        <v>164</v>
       </c>
       <c r="H27" t="n">
-        <v>73.2</v>
+        <v>56.1</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>108.96</v>
+        <v>-50.11</v>
       </c>
       <c r="K27" t="n">
-        <v>-303.15</v>
+        <v>-231.09</v>
       </c>
       <c r="L27" t="n">
-        <v>322.14</v>
+        <v>236.47</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:13:38</t>
+          <t>07:16:55</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.99</v>
+        <v>3.56</v>
       </c>
       <c r="F28" t="n">
-        <v>8.199999999999999</v>
+        <v>10.58</v>
       </c>
       <c r="G28" t="n">
-        <v>166.9</v>
+        <v>173.6</v>
       </c>
       <c r="H28" t="n">
-        <v>74.2</v>
+        <v>30.9</v>
       </c>
       <c r="I28" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>216.83</v>
+        <v>-180.79</v>
       </c>
       <c r="K28" t="n">
-        <v>-140.85</v>
+        <v>145.98</v>
       </c>
       <c r="L28" t="n">
-        <v>258.56</v>
+        <v>232.37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:23:45</t>
+          <t>07:27:14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.49</v>
+        <v>3.3</v>
       </c>
       <c r="F29" t="n">
-        <v>9.210000000000001</v>
+        <v>10.58</v>
       </c>
       <c r="G29" t="n">
-        <v>170.1</v>
+        <v>165.7</v>
       </c>
       <c r="H29" t="n">
-        <v>57</v>
+        <v>54.8</v>
       </c>
       <c r="I29" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-36.23</v>
+        <v>26.39</v>
       </c>
       <c r="K29" t="n">
-        <v>-37.29</v>
+        <v>-54.7</v>
       </c>
       <c r="L29" t="n">
-        <v>51.99</v>
+        <v>60.74</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:25:29</t>
+          <t>07:28:39</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.43</v>
+        <v>3.02</v>
       </c>
       <c r="F30" t="n">
-        <v>7.5</v>
+        <v>7.07</v>
       </c>
       <c r="G30" t="n">
-        <v>153.9</v>
+        <v>152</v>
       </c>
       <c r="H30" t="n">
-        <v>43.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-22.97</v>
+        <v>-11.07</v>
       </c>
       <c r="K30" t="n">
-        <v>50.11</v>
+        <v>43.61</v>
       </c>
       <c r="L30" t="n">
-        <v>55.12</v>
+        <v>44.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:27:33</t>
+          <t>07:29:59</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.02</v>
+        <v>3.13</v>
       </c>
       <c r="F31" t="n">
-        <v>5.68</v>
+        <v>7.45</v>
       </c>
       <c r="G31" t="n">
-        <v>169.3</v>
+        <v>169</v>
       </c>
       <c r="H31" t="n">
-        <v>58.3</v>
+        <v>75</v>
       </c>
       <c r="I31" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-38</v>
+        <v>-42.57</v>
       </c>
       <c r="K31" t="n">
-        <v>-29.5</v>
+        <v>31.26</v>
       </c>
       <c r="L31" t="n">
-        <v>48.11</v>
+        <v>52.82</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:32:38</t>
+          <t>07:35:52</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.2</v>
+        <v>3.62</v>
       </c>
       <c r="F32" t="n">
-        <v>10.58</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>185.4</v>
+        <v>175</v>
       </c>
       <c r="H32" t="n">
-        <v>58.9</v>
+        <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>83.69</v>
+        <v>79.38</v>
       </c>
       <c r="K32" t="n">
-        <v>3.21</v>
+        <v>-0.09</v>
       </c>
       <c r="L32" t="n">
-        <v>83.75</v>
+        <v>79.38</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:35:07</t>
+          <t>07:36:48</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="F33" t="n">
-        <v>9.02</v>
+        <v>10.1</v>
       </c>
       <c r="G33" t="n">
-        <v>155.6</v>
+        <v>173</v>
       </c>
       <c r="H33" t="n">
-        <v>33.9</v>
+        <v>74.2</v>
       </c>
       <c r="I33" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-86.63</v>
+        <v>-60.96</v>
       </c>
       <c r="K33" t="n">
-        <v>-44.13</v>
+        <v>-20.61</v>
       </c>
       <c r="L33" t="n">
-        <v>97.23</v>
+        <v>64.34999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:36:14</t>
+          <t>07:39:13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="F34" t="n">
-        <v>6.1</v>
+        <v>6.28</v>
       </c>
       <c r="G34" t="n">
-        <v>180.6</v>
+        <v>161.7</v>
       </c>
       <c r="H34" t="n">
-        <v>53.3</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>72.29000000000001</v>
+        <v>-87.98999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>36.22</v>
+        <v>-5.63</v>
       </c>
       <c r="L34" t="n">
-        <v>80.86</v>
+        <v>88.17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:39:59</t>
+          <t>07:43:28</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.52</v>
+        <v>3.72</v>
       </c>
       <c r="F35" t="n">
-        <v>9.890000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="G35" t="n">
-        <v>166.8</v>
+        <v>166.2</v>
       </c>
       <c r="H35" t="n">
-        <v>48.8</v>
+        <v>71.3</v>
       </c>
       <c r="I35" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-85.38</v>
+        <v>36.21</v>
       </c>
       <c r="K35" t="n">
-        <v>-77.34999999999999</v>
+        <v>110.13</v>
       </c>
       <c r="L35" t="n">
-        <v>115.21</v>
+        <v>115.92</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:41:28</t>
+          <t>07:45:24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.48</v>
+        <v>3.39</v>
       </c>
       <c r="F36" t="n">
-        <v>8.33</v>
+        <v>7.86</v>
       </c>
       <c r="G36" t="n">
-        <v>177.6</v>
+        <v>170.7</v>
       </c>
       <c r="H36" t="n">
-        <v>48.7</v>
+        <v>44.1</v>
       </c>
       <c r="I36" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>65.37</v>
+        <v>-76.79000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>-111.25</v>
+        <v>-40.61</v>
       </c>
       <c r="L36" t="n">
-        <v>129.03</v>
+        <v>86.87</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:43:42</t>
+          <t>07:46:08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1594,31 +1594,31 @@
         <v>3.31</v>
       </c>
       <c r="F37" t="n">
-        <v>9.720000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="G37" t="n">
-        <v>153.5</v>
+        <v>165.7</v>
       </c>
       <c r="H37" t="n">
-        <v>21.2</v>
+        <v>57.3</v>
       </c>
       <c r="I37" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-122.31</v>
+        <v>-25.85</v>
       </c>
       <c r="K37" t="n">
-        <v>-58.26</v>
+        <v>-95.27</v>
       </c>
       <c r="L37" t="n">
-        <v>135.48</v>
+        <v>98.72</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:47:50</t>
+          <t>07:51:18</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.48</v>
+        <v>3.34</v>
       </c>
       <c r="F38" t="n">
-        <v>6.32</v>
+        <v>10.22</v>
       </c>
       <c r="G38" t="n">
-        <v>175.6</v>
+        <v>174</v>
       </c>
       <c r="H38" t="n">
-        <v>52.7</v>
+        <v>45</v>
       </c>
       <c r="I38" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-225.58</v>
+        <v>-114.11</v>
       </c>
       <c r="K38" t="n">
-        <v>25.38</v>
+        <v>-133.12</v>
       </c>
       <c r="L38" t="n">
-        <v>227</v>
+        <v>175.33</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:49:52</t>
+          <t>07:53:20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.46</v>
+        <v>2.99</v>
       </c>
       <c r="F39" t="n">
-        <v>10.58</v>
+        <v>6.22</v>
       </c>
       <c r="G39" t="n">
-        <v>159.3</v>
+        <v>172.7</v>
       </c>
       <c r="H39" t="n">
-        <v>100</v>
+        <v>38.1</v>
       </c>
       <c r="I39" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>132.76</v>
+        <v>125.4</v>
       </c>
       <c r="K39" t="n">
-        <v>-82.56</v>
+        <v>-63.12</v>
       </c>
       <c r="L39" t="n">
-        <v>156.33</v>
+        <v>140.39</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:52:01</t>
+          <t>07:54:45</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.71</v>
+        <v>3.46</v>
       </c>
       <c r="F40" t="n">
-        <v>7.04</v>
+        <v>9.23</v>
       </c>
       <c r="G40" t="n">
-        <v>171.4</v>
+        <v>168.1</v>
       </c>
       <c r="H40" t="n">
-        <v>45.1</v>
+        <v>100</v>
       </c>
       <c r="I40" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>-70.94</v>
+        <v>-142.68</v>
       </c>
       <c r="K40" t="n">
-        <v>163.69</v>
+        <v>-146.76</v>
       </c>
       <c r="L40" t="n">
-        <v>178.4</v>
+        <v>204.68</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:56:31</t>
+          <t>07:59:45</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="F41" t="n">
-        <v>9.710000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="G41" t="n">
-        <v>163.9</v>
+        <v>145</v>
       </c>
       <c r="H41" t="n">
-        <v>58.2</v>
+        <v>35.8</v>
       </c>
       <c r="I41" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-36.24</v>
+        <v>178.09</v>
       </c>
       <c r="K41" t="n">
-        <v>-167.3</v>
+        <v>56.09</v>
       </c>
       <c r="L41" t="n">
-        <v>171.18</v>
+        <v>186.72</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:58:12</t>
+          <t>08:00:51</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.37</v>
+        <v>2.71</v>
       </c>
       <c r="F42" t="n">
-        <v>6.48</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>165.2</v>
+        <v>174.9</v>
       </c>
       <c r="H42" t="n">
-        <v>61.7</v>
+        <v>67.3</v>
       </c>
       <c r="I42" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>-30.61</v>
+        <v>-115.02</v>
       </c>
       <c r="K42" t="n">
-        <v>-171.49</v>
+        <v>102.06</v>
       </c>
       <c r="L42" t="n">
-        <v>174.2</v>
+        <v>153.77</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:59:05</t>
+          <t>08:01:46</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.14</v>
+        <v>3.79</v>
       </c>
       <c r="F43" t="n">
-        <v>8.210000000000001</v>
+        <v>10.58</v>
       </c>
       <c r="G43" t="n">
-        <v>166</v>
+        <v>177.9</v>
       </c>
       <c r="H43" t="n">
-        <v>47.1</v>
+        <v>59.1</v>
       </c>
       <c r="I43" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>143.14</v>
+        <v>159.07</v>
       </c>
       <c r="K43" t="n">
-        <v>-187.61</v>
+        <v>-154.77</v>
       </c>
       <c r="L43" t="n">
-        <v>235.98</v>
+        <v>221.94</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:08:01</t>
+          <t>08:13:11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.95</v>
+        <v>3.17</v>
       </c>
       <c r="F44" t="n">
-        <v>6.81</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>170.6</v>
+        <v>162</v>
       </c>
       <c r="H44" t="n">
-        <v>68.7</v>
+        <v>33.6</v>
       </c>
       <c r="I44" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>52.95</v>
+        <v>45.61</v>
       </c>
       <c r="K44" t="n">
-        <v>31.87</v>
+        <v>-28.39</v>
       </c>
       <c r="L44" t="n">
-        <v>61.8</v>
+        <v>53.73</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:09:59</t>
+          <t>08:15:50</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.74</v>
+        <v>3.15</v>
       </c>
       <c r="F45" t="n">
-        <v>9.65</v>
+        <v>7.05</v>
       </c>
       <c r="G45" t="n">
-        <v>168.6</v>
+        <v>168.3</v>
       </c>
       <c r="H45" t="n">
-        <v>71.3</v>
+        <v>37.9</v>
       </c>
       <c r="I45" t="n">
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>47.23</v>
+        <v>27.77</v>
       </c>
       <c r="K45" t="n">
-        <v>-51.05</v>
+        <v>37.96</v>
       </c>
       <c r="L45" t="n">
-        <v>69.55</v>
+        <v>47.03</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:11:24</t>
+          <t>08:17:05</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.17</v>
+        <v>2.97</v>
       </c>
       <c r="F46" t="n">
-        <v>10.58</v>
+        <v>8.15</v>
       </c>
       <c r="G46" t="n">
-        <v>169.6</v>
+        <v>149.3</v>
       </c>
       <c r="H46" t="n">
-        <v>25.6</v>
+        <v>81.7</v>
       </c>
       <c r="I46" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-51.09</v>
+        <v>7.36</v>
       </c>
       <c r="K46" t="n">
-        <v>20.93</v>
+        <v>42.99</v>
       </c>
       <c r="L46" t="n">
-        <v>55.21</v>
+        <v>43.61</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:16:40</t>
+          <t>08:23:11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.72</v>
+        <v>2.94</v>
       </c>
       <c r="F47" t="n">
-        <v>10.58</v>
+        <v>9.6</v>
       </c>
       <c r="G47" t="n">
-        <v>157.2</v>
+        <v>155.9</v>
       </c>
       <c r="H47" t="n">
-        <v>82.7</v>
+        <v>52</v>
       </c>
       <c r="I47" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-91.25</v>
+        <v>-20.76</v>
       </c>
       <c r="K47" t="n">
-        <v>-9.52</v>
+        <v>55.68</v>
       </c>
       <c r="L47" t="n">
-        <v>91.75</v>
+        <v>59.42</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:17:26</t>
+          <t>08:24:51</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.33</v>
+        <v>3.49</v>
       </c>
       <c r="F48" t="n">
-        <v>9.91</v>
+        <v>7.83</v>
       </c>
       <c r="G48" t="n">
-        <v>172.2</v>
+        <v>176.1</v>
       </c>
       <c r="H48" t="n">
-        <v>12.9</v>
+        <v>60.1</v>
       </c>
       <c r="I48" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-78.22</v>
+        <v>-68.22</v>
       </c>
       <c r="K48" t="n">
-        <v>-26.08</v>
+        <v>-27.66</v>
       </c>
       <c r="L48" t="n">
-        <v>82.45999999999999</v>
+        <v>73.61</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:19:26</t>
+          <t>08:25:53</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="F49" t="n">
-        <v>9.76</v>
+        <v>9.69</v>
       </c>
       <c r="G49" t="n">
-        <v>154.5</v>
+        <v>167.6</v>
       </c>
       <c r="H49" t="n">
-        <v>56.4</v>
+        <v>60.3</v>
       </c>
       <c r="I49" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>85.41</v>
+        <v>38.06</v>
       </c>
       <c r="K49" t="n">
-        <v>-33.08</v>
+        <v>98.94</v>
       </c>
       <c r="L49" t="n">
-        <v>91.59</v>
+        <v>106.01</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:24:47</t>
+          <t>08:30:58</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.77</v>
+        <v>3.61</v>
       </c>
       <c r="F50" t="n">
         <v>10.58</v>
       </c>
       <c r="G50" t="n">
-        <v>169.3</v>
+        <v>168.5</v>
       </c>
       <c r="H50" t="n">
-        <v>61.2</v>
+        <v>84.7</v>
       </c>
       <c r="I50" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>-71.68000000000001</v>
+        <v>45.34</v>
       </c>
       <c r="K50" t="n">
-        <v>73.02</v>
+        <v>-132.9</v>
       </c>
       <c r="L50" t="n">
-        <v>102.32</v>
+        <v>140.42</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:26:12</t>
+          <t>08:32:57</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="F51" t="n">
-        <v>8.69</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>155</v>
+        <v>152.9</v>
       </c>
       <c r="H51" t="n">
-        <v>55.5</v>
+        <v>82.8</v>
       </c>
       <c r="I51" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>39.79</v>
+        <v>-95.43000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>-119.76</v>
+        <v>14.3</v>
       </c>
       <c r="L51" t="n">
-        <v>126.2</v>
+        <v>96.48999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:27:19</t>
+          <t>08:34:30</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="F52" t="n">
-        <v>10.58</v>
+        <v>6.73</v>
       </c>
       <c r="G52" t="n">
-        <v>154.4</v>
+        <v>166</v>
       </c>
       <c r="H52" t="n">
-        <v>50.5</v>
+        <v>62.2</v>
       </c>
       <c r="I52" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>1.47</v>
+        <v>-48.99</v>
       </c>
       <c r="K52" t="n">
-        <v>-126.76</v>
+        <v>75.38</v>
       </c>
       <c r="L52" t="n">
-        <v>126.77</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:31:34</t>
+          <t>08:39:43</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.14</v>
+        <v>3.36</v>
       </c>
       <c r="F53" t="n">
-        <v>10.58</v>
+        <v>6.75</v>
       </c>
       <c r="G53" t="n">
-        <v>168.1</v>
+        <v>173</v>
       </c>
       <c r="H53" t="n">
-        <v>51.3</v>
+        <v>26</v>
       </c>
       <c r="I53" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>274.43</v>
+        <v>-140.93</v>
       </c>
       <c r="K53" t="n">
-        <v>-127.07</v>
+        <v>17.37</v>
       </c>
       <c r="L53" t="n">
-        <v>302.42</v>
+        <v>142</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:32:45</t>
+          <t>08:40:47</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="F54" t="n">
-        <v>5.66</v>
+        <v>9.07</v>
       </c>
       <c r="G54" t="n">
-        <v>166.1</v>
+        <v>161.4</v>
       </c>
       <c r="H54" t="n">
-        <v>74</v>
+        <v>66.8</v>
       </c>
       <c r="I54" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>133.52</v>
+        <v>148.57</v>
       </c>
       <c r="K54" t="n">
-        <v>-97.33</v>
+        <v>-71.65000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>165.23</v>
+        <v>164.94</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:35:04</t>
+          <t>08:41:25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="F55" t="n">
-        <v>9.300000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="G55" t="n">
-        <v>167.8</v>
+        <v>158.8</v>
       </c>
       <c r="H55" t="n">
-        <v>83.7</v>
+        <v>31.1</v>
       </c>
       <c r="I55" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-202.13</v>
+        <v>169.74</v>
       </c>
       <c r="K55" t="n">
-        <v>-58.9</v>
+        <v>-51.57</v>
       </c>
       <c r="L55" t="n">
-        <v>210.53</v>
+        <v>177.41</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:39:57</t>
+          <t>08:45:13</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.41</v>
+        <v>3.44</v>
       </c>
       <c r="F56" t="n">
-        <v>8.6</v>
+        <v>8.69</v>
       </c>
       <c r="G56" t="n">
-        <v>156.1</v>
+        <v>155.9</v>
       </c>
       <c r="H56" t="n">
-        <v>79.40000000000001</v>
+        <v>29.7</v>
       </c>
       <c r="I56" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>25.46</v>
+        <v>166.61</v>
       </c>
       <c r="K56" t="n">
-        <v>-233.91</v>
+        <v>54.01</v>
       </c>
       <c r="L56" t="n">
-        <v>235.29</v>
+        <v>175.14</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:41:24</t>
+          <t>08:46:15</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.09</v>
+        <v>4.03</v>
       </c>
       <c r="F57" t="n">
-        <v>7.3</v>
+        <v>10.4</v>
       </c>
       <c r="G57" t="n">
-        <v>163.1</v>
+        <v>168.9</v>
       </c>
       <c r="H57" t="n">
-        <v>67.40000000000001</v>
+        <v>14.6</v>
       </c>
       <c r="I57" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>151.72</v>
+        <v>-84.12</v>
       </c>
       <c r="K57" t="n">
-        <v>-113.71</v>
+        <v>-261.49</v>
       </c>
       <c r="L57" t="n">
-        <v>189.6</v>
+        <v>274.68</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:43:59</t>
+          <t>08:48:10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.67</v>
+        <v>2.83</v>
       </c>
       <c r="F58" t="n">
-        <v>10.58</v>
+        <v>7.69</v>
       </c>
       <c r="G58" t="n">
-        <v>167.6</v>
+        <v>168</v>
       </c>
       <c r="H58" t="n">
-        <v>40.5</v>
+        <v>40.9</v>
       </c>
       <c r="I58" t="n">
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>81.81</v>
+        <v>137.74</v>
       </c>
       <c r="K58" t="n">
-        <v>-217.27</v>
+        <v>-140.28</v>
       </c>
       <c r="L58" t="n">
-        <v>232.16</v>
+        <v>196.6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:52:52</t>
+          <t>08:57:55</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.15</v>
+        <v>3.33</v>
       </c>
       <c r="F59" t="n">
-        <v>7.3</v>
+        <v>10.58</v>
       </c>
       <c r="G59" t="n">
-        <v>167.6</v>
+        <v>162.8</v>
       </c>
       <c r="H59" t="n">
-        <v>52.1</v>
+        <v>42.3</v>
       </c>
       <c r="I59" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-33.92</v>
+        <v>-50.58</v>
       </c>
       <c r="K59" t="n">
-        <v>53.84</v>
+        <v>-2.68</v>
       </c>
       <c r="L59" t="n">
-        <v>63.63</v>
+        <v>50.65</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:54:13</t>
+          <t>09:00:31</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.18</v>
+        <v>3.38</v>
       </c>
       <c r="F60" t="n">
-        <v>10.21</v>
+        <v>7.25</v>
       </c>
       <c r="G60" t="n">
-        <v>147.5</v>
+        <v>160.4</v>
       </c>
       <c r="H60" t="n">
-        <v>63.1</v>
+        <v>57.4</v>
       </c>
       <c r="I60" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-24.44</v>
+        <v>-51.8</v>
       </c>
       <c r="K60" t="n">
-        <v>60.42</v>
+        <v>37.56</v>
       </c>
       <c r="L60" t="n">
-        <v>65.18000000000001</v>
+        <v>63.99</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:55:54</t>
+          <t>09:02:15</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.82</v>
+        <v>3.31</v>
       </c>
       <c r="F61" t="n">
-        <v>10.58</v>
+        <v>9.81</v>
       </c>
       <c r="G61" t="n">
-        <v>152.2</v>
+        <v>160.8</v>
       </c>
       <c r="H61" t="n">
-        <v>55.1</v>
+        <v>79</v>
       </c>
       <c r="I61" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-47.49</v>
+        <v>-19.49</v>
       </c>
       <c r="K61" t="n">
-        <v>47.15</v>
+        <v>-42.68</v>
       </c>
       <c r="L61" t="n">
-        <v>66.92</v>
+        <v>46.92</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:01:16</t>
+          <t>09:05:59</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.67</v>
+        <v>4.22</v>
       </c>
       <c r="F62" t="n">
-        <v>9.630000000000001</v>
+        <v>10.58</v>
       </c>
       <c r="G62" t="n">
-        <v>151.6</v>
+        <v>160.8</v>
       </c>
       <c r="H62" t="n">
-        <v>63</v>
+        <v>37.6</v>
       </c>
       <c r="I62" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>74.03</v>
+        <v>-73.89</v>
       </c>
       <c r="K62" t="n">
-        <v>-54.05</v>
+        <v>-29.78</v>
       </c>
       <c r="L62" t="n">
-        <v>91.66</v>
+        <v>79.67</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:02:29</t>
+          <t>09:07:15</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.59</v>
+        <v>3.2</v>
       </c>
       <c r="F63" t="n">
-        <v>10.58</v>
+        <v>7.51</v>
       </c>
       <c r="G63" t="n">
-        <v>164.9</v>
+        <v>167.6</v>
       </c>
       <c r="H63" t="n">
-        <v>70.8</v>
+        <v>52.1</v>
       </c>
       <c r="I63" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>105.18</v>
+        <v>-38.5</v>
       </c>
       <c r="K63" t="n">
-        <v>-12.05</v>
+        <v>72.17</v>
       </c>
       <c r="L63" t="n">
-        <v>105.87</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:03:57</t>
+          <t>09:08:56</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.8</v>
+        <v>3.23</v>
       </c>
       <c r="F64" t="n">
-        <v>9.25</v>
+        <v>10.42</v>
       </c>
       <c r="G64" t="n">
-        <v>173</v>
+        <v>147.5</v>
       </c>
       <c r="H64" t="n">
-        <v>56.6</v>
+        <v>63.1</v>
       </c>
       <c r="I64" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>-90.83</v>
+        <v>-34.43</v>
       </c>
       <c r="K64" t="n">
-        <v>-40.94</v>
+        <v>76.44</v>
       </c>
       <c r="L64" t="n">
-        <v>99.63</v>
+        <v>83.84</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:09:17</t>
+          <t>09:13:00</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.48</v>
+        <v>3.87</v>
       </c>
       <c r="F65" t="n">
-        <v>8.34</v>
+        <v>10.58</v>
       </c>
       <c r="G65" t="n">
-        <v>174</v>
+        <v>152.2</v>
       </c>
       <c r="H65" t="n">
-        <v>61.4</v>
+        <v>55.1</v>
       </c>
       <c r="I65" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>72.83</v>
+        <v>-77.42</v>
       </c>
       <c r="K65" t="n">
-        <v>44.43</v>
+        <v>88.67</v>
       </c>
       <c r="L65" t="n">
-        <v>85.31</v>
+        <v>117.71</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:10:50</t>
+          <t>09:14:27</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.76</v>
+        <v>3.71</v>
       </c>
       <c r="F66" t="n">
-        <v>10.58</v>
+        <v>9.82</v>
       </c>
       <c r="G66" t="n">
-        <v>172.4</v>
+        <v>151.6</v>
       </c>
       <c r="H66" t="n">
-        <v>55.2</v>
+        <v>63</v>
       </c>
       <c r="I66" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-101.65</v>
+        <v>102.1</v>
       </c>
       <c r="K66" t="n">
-        <v>82.66</v>
+        <v>-56.15</v>
       </c>
       <c r="L66" t="n">
-        <v>131.01</v>
+        <v>116.52</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:12:11</t>
+          <t>09:15:09</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.76</v>
+        <v>3.63</v>
       </c>
       <c r="F67" t="n">
         <v>10.58</v>
       </c>
       <c r="G67" t="n">
-        <v>168.3</v>
+        <v>164.9</v>
       </c>
       <c r="H67" t="n">
-        <v>66.90000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="I67" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-11</v>
+        <v>133.72</v>
       </c>
       <c r="K67" t="n">
-        <v>-126.46</v>
+        <v>18.45</v>
       </c>
       <c r="L67" t="n">
-        <v>126.94</v>
+        <v>134.98</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:16:45</t>
+          <t>09:19:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.4</v>
+        <v>3.84</v>
       </c>
       <c r="F68" t="n">
-        <v>7.89</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="G68" t="n">
-        <v>172.8</v>
+        <v>173</v>
       </c>
       <c r="H68" t="n">
-        <v>24.6</v>
+        <v>56.6</v>
       </c>
       <c r="I68" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>4.68</v>
+        <v>-211.6</v>
       </c>
       <c r="K68" t="n">
-        <v>-137.09</v>
+        <v>-33.79</v>
       </c>
       <c r="L68" t="n">
-        <v>137.17</v>
+        <v>214.28</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:17:21</t>
+          <t>09:20:35</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.61</v>
+        <v>3.52</v>
       </c>
       <c r="F69" t="n">
-        <v>10.58</v>
+        <v>8.51</v>
       </c>
       <c r="G69" t="n">
-        <v>154.5</v>
+        <v>174</v>
       </c>
       <c r="H69" t="n">
-        <v>65.09999999999999</v>
+        <v>61.4</v>
       </c>
       <c r="I69" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>166.46</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>51.05</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="L69" t="n">
-        <v>174.11</v>
+        <v>126.25</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:18:59</t>
+          <t>09:21:28</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.42</v>
+        <v>3.79</v>
       </c>
       <c r="F70" t="n">
-        <v>10.43</v>
+        <v>10.58</v>
       </c>
       <c r="G70" t="n">
-        <v>158.4</v>
+        <v>172.4</v>
       </c>
       <c r="H70" t="n">
-        <v>52.2</v>
+        <v>55.2</v>
       </c>
       <c r="I70" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J70" t="n">
-        <v>66.81</v>
+        <v>-129.88</v>
       </c>
       <c r="K70" t="n">
-        <v>-187.95</v>
+        <v>147.6</v>
       </c>
       <c r="L70" t="n">
-        <v>199.47</v>
+        <v>196.61</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:23:14</t>
+          <t>09:25:57</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.61</v>
+        <v>3.8</v>
       </c>
       <c r="F71" t="n">
-        <v>9.49</v>
+        <v>10.58</v>
       </c>
       <c r="G71" t="n">
-        <v>171.1</v>
+        <v>168.3</v>
       </c>
       <c r="H71" t="n">
-        <v>45.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-285.57</v>
+        <v>-40.12</v>
       </c>
       <c r="K71" t="n">
-        <v>-77.61</v>
+        <v>-227.79</v>
       </c>
       <c r="L71" t="n">
-        <v>295.93</v>
+        <v>231.29</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:24:39</t>
+          <t>09:28:24</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.51</v>
+        <v>3.43</v>
       </c>
       <c r="F72" t="n">
-        <v>8.19</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>151.6</v>
+        <v>172.8</v>
       </c>
       <c r="H72" t="n">
-        <v>81.7</v>
+        <v>24.6</v>
       </c>
       <c r="I72" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-66.61</v>
+        <v>1.26</v>
       </c>
       <c r="K72" t="n">
-        <v>186.77</v>
+        <v>-158.21</v>
       </c>
       <c r="L72" t="n">
-        <v>198.29</v>
+        <v>158.22</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:26:50</t>
+          <t>09:29:14</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.83</v>
+        <v>3.65</v>
       </c>
       <c r="F73" t="n">
-        <v>10.24</v>
+        <v>10.58</v>
       </c>
       <c r="G73" t="n">
-        <v>156.2</v>
+        <v>154.5</v>
       </c>
       <c r="H73" t="n">
-        <v>87</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>-13.26</v>
+        <v>174.89</v>
       </c>
       <c r="K73" t="n">
-        <v>-224.42</v>
+        <v>109.13</v>
       </c>
       <c r="L73" t="n">
-        <v>224.81</v>
+        <v>206.15</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:35:45</t>
+          <t>09:40:40</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.66</v>
+        <v>3.48</v>
       </c>
       <c r="F74" t="n">
-        <v>6.9</v>
+        <v>10.58</v>
       </c>
       <c r="G74" t="n">
-        <v>152.6</v>
+        <v>158.4</v>
       </c>
       <c r="H74" t="n">
-        <v>53.6</v>
+        <v>52.2</v>
       </c>
       <c r="I74" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>58.59</v>
+        <v>18.9</v>
       </c>
       <c r="K74" t="n">
-        <v>-3.28</v>
+        <v>-54.93</v>
       </c>
       <c r="L74" t="n">
-        <v>58.68</v>
+        <v>58.09</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:36:39</t>
+          <t>09:42:33</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.11</v>
+        <v>3.66</v>
       </c>
       <c r="F75" t="n">
-        <v>9.25</v>
+        <v>9.73</v>
       </c>
       <c r="G75" t="n">
-        <v>157.4</v>
+        <v>171.1</v>
       </c>
       <c r="H75" t="n">
-        <v>79.3</v>
+        <v>45.5</v>
       </c>
       <c r="I75" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>56.84</v>
+        <v>-67.48999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>-2.8</v>
+        <v>-0.38</v>
       </c>
       <c r="L75" t="n">
-        <v>56.91</v>
+        <v>67.48999999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:37:59</t>
+          <t>09:44:10</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.42</v>
+        <v>3.56</v>
       </c>
       <c r="F76" t="n">
-        <v>10.18</v>
+        <v>8.43</v>
       </c>
       <c r="G76" t="n">
-        <v>163.6</v>
+        <v>151.6</v>
       </c>
       <c r="H76" t="n">
-        <v>59.4</v>
+        <v>81.7</v>
       </c>
       <c r="I76" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>20.4</v>
+        <v>-16.46</v>
       </c>
       <c r="K76" t="n">
-        <v>-55.9</v>
+        <v>41.57</v>
       </c>
       <c r="L76" t="n">
-        <v>59.51</v>
+        <v>44.71</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:41:36</t>
+          <t>09:48:31</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3274,31 +3274,31 @@
         <v>3.88</v>
       </c>
       <c r="F77" t="n">
-        <v>10.58</v>
+        <v>10.5</v>
       </c>
       <c r="G77" t="n">
-        <v>168.4</v>
+        <v>156.2</v>
       </c>
       <c r="H77" t="n">
-        <v>70.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="I77" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>-87.31999999999999</v>
+        <v>-13.54</v>
       </c>
       <c r="K77" t="n">
-        <v>-37.84</v>
+        <v>-67.34999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>95.17</v>
+        <v>68.69</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:42:43</t>
+          <t>09:49:45</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.43</v>
+        <v>3.7</v>
       </c>
       <c r="F78" t="n">
-        <v>7.62</v>
+        <v>7.09</v>
       </c>
       <c r="G78" t="n">
-        <v>171.4</v>
+        <v>152.6</v>
       </c>
       <c r="H78" t="n">
-        <v>69</v>
+        <v>53.6</v>
       </c>
       <c r="I78" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-38.38</v>
+        <v>67.39</v>
       </c>
       <c r="K78" t="n">
-        <v>-81.93000000000001</v>
+        <v>12.57</v>
       </c>
       <c r="L78" t="n">
-        <v>90.47</v>
+        <v>68.55</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:43:39</t>
+          <t>09:52:03</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="F79" t="n">
-        <v>9.31</v>
+        <v>9.43</v>
       </c>
       <c r="G79" t="n">
-        <v>169</v>
+        <v>157.4</v>
       </c>
       <c r="H79" t="n">
-        <v>69.8</v>
+        <v>79.3</v>
       </c>
       <c r="I79" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>82.81</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>-33.97</v>
+        <v>12.45</v>
       </c>
       <c r="L79" t="n">
-        <v>89.51000000000001</v>
+        <v>72.23</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:48:04</t>
+          <t>09:56:19</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.29</v>
+        <v>3.47</v>
       </c>
       <c r="F80" t="n">
-        <v>10.54</v>
+        <v>10.41</v>
       </c>
       <c r="G80" t="n">
-        <v>179.7</v>
+        <v>163.6</v>
       </c>
       <c r="H80" t="n">
-        <v>60.9</v>
+        <v>59.4</v>
       </c>
       <c r="I80" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>-85.89</v>
+        <v>36.16</v>
       </c>
       <c r="K80" t="n">
-        <v>-64.48</v>
+        <v>-93.77</v>
       </c>
       <c r="L80" t="n">
-        <v>107.4</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:50:44</t>
+          <t>09:58:03</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.44</v>
+        <v>3.92</v>
       </c>
       <c r="F81" t="n">
-        <v>9.789999999999999</v>
+        <v>10.58</v>
       </c>
       <c r="G81" t="n">
-        <v>171.5</v>
+        <v>168.4</v>
       </c>
       <c r="H81" t="n">
-        <v>31.7</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>-3.67</v>
+        <v>-117.56</v>
       </c>
       <c r="K81" t="n">
-        <v>116.55</v>
+        <v>-16.22</v>
       </c>
       <c r="L81" t="n">
-        <v>116.6</v>
+        <v>118.68</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:51:20</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.56</v>
+        <v>3.47</v>
       </c>
       <c r="F82" t="n">
-        <v>10.58</v>
+        <v>7.81</v>
       </c>
       <c r="G82" t="n">
-        <v>175</v>
+        <v>171.4</v>
       </c>
       <c r="H82" t="n">
-        <v>51.9</v>
+        <v>69</v>
       </c>
       <c r="I82" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>108.18</v>
+        <v>-61.03</v>
       </c>
       <c r="K82" t="n">
-        <v>-102.22</v>
+        <v>-90.47</v>
       </c>
       <c r="L82" t="n">
-        <v>148.83</v>
+        <v>109.13</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:55:36</t>
+          <t>10:02:43</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.28</v>
+        <v>3.55</v>
       </c>
       <c r="F83" t="n">
-        <v>10.54</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G83" t="n">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="H83" t="n">
-        <v>63.2</v>
+        <v>69.8</v>
       </c>
       <c r="I83" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J83" t="n">
-        <v>161.32</v>
+        <v>179.45</v>
       </c>
       <c r="K83" t="n">
-        <v>-133.88</v>
+        <v>-29.36</v>
       </c>
       <c r="L83" t="n">
-        <v>209.64</v>
+        <v>181.83</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:58:10</t>
+          <t>10:05:15</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.86</v>
+        <v>3.34</v>
       </c>
       <c r="F84" t="n">
-        <v>8.19</v>
+        <v>10.58</v>
       </c>
       <c r="G84" t="n">
-        <v>158.3</v>
+        <v>179.7</v>
       </c>
       <c r="H84" t="n">
-        <v>49.1</v>
+        <v>60.9</v>
       </c>
       <c r="I84" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>232.89</v>
+        <v>-137.77</v>
       </c>
       <c r="K84" t="n">
-        <v>-11.92</v>
+        <v>-63.82</v>
       </c>
       <c r="L84" t="n">
-        <v>233.19</v>
+        <v>151.84</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:00:15</t>
+          <t>10:06:30</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>5.01</v>
+        <v>3.48</v>
       </c>
       <c r="F85" t="n">
-        <v>10.58</v>
+        <v>9.98</v>
       </c>
       <c r="G85" t="n">
-        <v>151.2</v>
+        <v>171.5</v>
       </c>
       <c r="H85" t="n">
-        <v>33</v>
+        <v>31.7</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>-48.72</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>-472.3</v>
+        <v>162.86</v>
       </c>
       <c r="L85" t="n">
-        <v>474.81</v>
+        <v>163.13</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:04:47</t>
+          <t>10:11:05</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="F86" t="n">
-        <v>7.2</v>
+        <v>10.58</v>
       </c>
       <c r="G86" t="n">
-        <v>170.3</v>
+        <v>175</v>
       </c>
       <c r="H86" t="n">
-        <v>42.8</v>
+        <v>51.9</v>
       </c>
       <c r="I86" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>264.17</v>
+        <v>214.7</v>
       </c>
       <c r="K86" t="n">
-        <v>-78.41</v>
+        <v>-137.17</v>
       </c>
       <c r="L86" t="n">
-        <v>275.57</v>
+        <v>254.78</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:06:25</t>
+          <t>10:11:39</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.85</v>
+        <v>3.32</v>
       </c>
       <c r="F87" t="n">
         <v>10.58</v>
       </c>
       <c r="G87" t="n">
-        <v>167.8</v>
+        <v>158</v>
       </c>
       <c r="H87" t="n">
-        <v>77.5</v>
+        <v>63.2</v>
       </c>
       <c r="I87" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>-242.6</v>
+        <v>203.65</v>
       </c>
       <c r="K87" t="n">
-        <v>59.68</v>
+        <v>-128.66</v>
       </c>
       <c r="L87" t="n">
-        <v>249.84</v>
+        <v>240.89</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:08:09</t>
+          <t>10:13:27</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="F88" t="n">
-        <v>10.58</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>158.6</v>
+        <v>158.3</v>
       </c>
       <c r="H88" t="n">
-        <v>89.2</v>
+        <v>49.1</v>
       </c>
       <c r="I88" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>135.94</v>
+        <v>259.16</v>
       </c>
       <c r="K88" t="n">
-        <v>-278.9</v>
+        <v>54.75</v>
       </c>
       <c r="L88" t="n">
-        <v>310.26</v>
+        <v>264.88</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-02.xlsx
+++ b/output/2024-04-02.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>9.970000000000001</v>
+        <v>11.67</v>
       </c>
       <c r="K14" t="n">
-        <v>58.73</v>
+        <v>68.79000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>59.57</v>
+        <v>69.77</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>-25.79</v>
+        <v>-29.98</v>
       </c>
       <c r="K15" t="n">
-        <v>51.23</v>
+        <v>59.54</v>
       </c>
       <c r="L15" t="n">
-        <v>57.36</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>-66.48</v>
+        <v>-76.75</v>
       </c>
       <c r="K16" t="n">
-        <v>1.96</v>
+        <v>2.26</v>
       </c>
       <c r="L16" t="n">
-        <v>66.51000000000001</v>
+        <v>76.78</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>-107.42</v>
+        <v>-115.77</v>
       </c>
       <c r="K17" t="n">
-        <v>-20.48</v>
+        <v>-22.07</v>
       </c>
       <c r="L17" t="n">
-        <v>109.35</v>
+        <v>117.86</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-46.63</v>
+        <v>-55.43</v>
       </c>
       <c r="K18" t="n">
-        <v>42.64</v>
+        <v>50.68</v>
       </c>
       <c r="L18" t="n">
-        <v>63.18</v>
+        <v>75.11</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>60.87</v>
+        <v>68.77</v>
       </c>
       <c r="K19" t="n">
-        <v>41.26</v>
+        <v>46.61</v>
       </c>
       <c r="L19" t="n">
-        <v>73.54000000000001</v>
+        <v>83.06999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>38.68</v>
+        <v>45.09</v>
       </c>
       <c r="K20" t="n">
-        <v>-110.51</v>
+        <v>-128.82</v>
       </c>
       <c r="L20" t="n">
-        <v>117.08</v>
+        <v>136.49</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>26.19</v>
+        <v>33.99</v>
       </c>
       <c r="K21" t="n">
-        <v>80.72</v>
+        <v>104.77</v>
       </c>
       <c r="L21" t="n">
-        <v>84.86</v>
+        <v>110.14</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-115.04</v>
+        <v>-137.28</v>
       </c>
       <c r="K22" t="n">
-        <v>40.94</v>
+        <v>48.85</v>
       </c>
       <c r="L22" t="n">
-        <v>122.1</v>
+        <v>145.71</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>34.49</v>
+        <v>42.58</v>
       </c>
       <c r="K23" t="n">
-        <v>157.91</v>
+        <v>194.94</v>
       </c>
       <c r="L23" t="n">
-        <v>161.63</v>
+        <v>199.54</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>22.2</v>
+        <v>29.94</v>
       </c>
       <c r="K24" t="n">
-        <v>-8.27</v>
+        <v>-11.16</v>
       </c>
       <c r="L24" t="n">
-        <v>23.69</v>
+        <v>31.95</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>132.83</v>
+        <v>169.2</v>
       </c>
       <c r="K25" t="n">
-        <v>11.67</v>
+        <v>14.86</v>
       </c>
       <c r="L25" t="n">
-        <v>133.34</v>
+        <v>169.85</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>177.27</v>
+        <v>218.19</v>
       </c>
       <c r="K26" t="n">
-        <v>140.25</v>
+        <v>172.62</v>
       </c>
       <c r="L26" t="n">
-        <v>226.04</v>
+        <v>278.21</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>215.62</v>
+        <v>269.98</v>
       </c>
       <c r="K27" t="n">
-        <v>110.05</v>
+        <v>137.79</v>
       </c>
       <c r="L27" t="n">
-        <v>242.08</v>
+        <v>303.11</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>211.48</v>
+        <v>270.18</v>
       </c>
       <c r="K28" t="n">
-        <v>-95.65000000000001</v>
+        <v>-122.2</v>
       </c>
       <c r="L28" t="n">
-        <v>232.1</v>
+        <v>296.53</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-12.32</v>
+        <v>-13.4</v>
       </c>
       <c r="K29" t="n">
-        <v>82.13</v>
+        <v>89.34</v>
       </c>
       <c r="L29" t="n">
-        <v>83.05</v>
+        <v>90.33</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>76.04000000000001</v>
+        <v>84.25</v>
       </c>
       <c r="K30" t="n">
-        <v>-10.24</v>
+        <v>-11.34</v>
       </c>
       <c r="L30" t="n">
-        <v>76.73</v>
+        <v>85.01000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-89.73</v>
+        <v>-96.31</v>
       </c>
       <c r="K31" t="n">
-        <v>-25.6</v>
+        <v>-27.47</v>
       </c>
       <c r="L31" t="n">
-        <v>93.31</v>
+        <v>100.16</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>14.66</v>
+        <v>17.14</v>
       </c>
       <c r="K32" t="n">
-        <v>69.41</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>70.94</v>
+        <v>82.94</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-78.13</v>
+        <v>-85.90000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>-68.08</v>
+        <v>-74.84</v>
       </c>
       <c r="L33" t="n">
-        <v>103.63</v>
+        <v>113.92</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>94.40000000000001</v>
+        <v>102.41</v>
       </c>
       <c r="K34" t="n">
-        <v>-23.3</v>
+        <v>-25.27</v>
       </c>
       <c r="L34" t="n">
-        <v>97.23</v>
+        <v>105.48</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-94.83</v>
+        <v>-118.2</v>
       </c>
       <c r="K35" t="n">
-        <v>9.76</v>
+        <v>12.17</v>
       </c>
       <c r="L35" t="n">
-        <v>95.34</v>
+        <v>118.83</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.14</v>
+        <v>-0.16</v>
       </c>
       <c r="K36" t="n">
-        <v>-123.94</v>
+        <v>-144.64</v>
       </c>
       <c r="L36" t="n">
-        <v>123.94</v>
+        <v>144.64</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>51.12</v>
+        <v>57.48</v>
       </c>
       <c r="K37" t="n">
-        <v>126.23</v>
+        <v>141.95</v>
       </c>
       <c r="L37" t="n">
-        <v>136.19</v>
+        <v>153.15</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-116.34</v>
+        <v>-155.49</v>
       </c>
       <c r="K38" t="n">
-        <v>66.56999999999999</v>
+        <v>88.97</v>
       </c>
       <c r="L38" t="n">
-        <v>134.04</v>
+        <v>179.14</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>133.14</v>
+        <v>166.38</v>
       </c>
       <c r="K39" t="n">
-        <v>-86.52</v>
+        <v>-108.11</v>
       </c>
       <c r="L39" t="n">
-        <v>158.78</v>
+        <v>198.42</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-126.61</v>
+        <v>-150.18</v>
       </c>
       <c r="K40" t="n">
-        <v>134.17</v>
+        <v>159.14</v>
       </c>
       <c r="L40" t="n">
-        <v>184.48</v>
+        <v>218.81</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>-134.29</v>
+        <v>-181.7</v>
       </c>
       <c r="K41" t="n">
-        <v>104.76</v>
+        <v>141.75</v>
       </c>
       <c r="L41" t="n">
-        <v>170.31</v>
+        <v>230.45</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-182.17</v>
+        <v>-244.59</v>
       </c>
       <c r="K42" t="n">
-        <v>-33.37</v>
+        <v>-44.8</v>
       </c>
       <c r="L42" t="n">
-        <v>185.21</v>
+        <v>248.66</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>202.88</v>
+        <v>263.67</v>
       </c>
       <c r="K43" t="n">
-        <v>-17.19</v>
+        <v>-22.34</v>
       </c>
       <c r="L43" t="n">
-        <v>203.61</v>
+        <v>264.62</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-60.31</v>
+        <v>-70.92</v>
       </c>
       <c r="K44" t="n">
-        <v>21.48</v>
+        <v>25.26</v>
       </c>
       <c r="L44" t="n">
-        <v>64.02</v>
+        <v>75.28</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>6.84</v>
+        <v>7.99</v>
       </c>
       <c r="K45" t="n">
-        <v>54.46</v>
+        <v>63.57</v>
       </c>
       <c r="L45" t="n">
-        <v>54.89</v>
+        <v>64.06999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>29.84</v>
+        <v>32.77</v>
       </c>
       <c r="K46" t="n">
-        <v>75.08</v>
+        <v>82.45999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>80.79000000000001</v>
+        <v>88.73</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>54.02</v>
+        <v>67.58</v>
       </c>
       <c r="K47" t="n">
-        <v>-38.14</v>
+        <v>-47.72</v>
       </c>
       <c r="L47" t="n">
-        <v>66.13</v>
+        <v>82.73</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>-80.88</v>
+        <v>-90.95999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.25</v>
+        <v>-4.78</v>
       </c>
       <c r="L48" t="n">
-        <v>80.98999999999999</v>
+        <v>91.09</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>51.08</v>
+        <v>56.68</v>
       </c>
       <c r="K49" t="n">
-        <v>-96.48</v>
+        <v>-107.06</v>
       </c>
       <c r="L49" t="n">
-        <v>109.17</v>
+        <v>121.14</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>92.91</v>
+        <v>114.48</v>
       </c>
       <c r="K50" t="n">
-        <v>-39.65</v>
+        <v>-48.86</v>
       </c>
       <c r="L50" t="n">
-        <v>101.01</v>
+        <v>124.47</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-73.39</v>
+        <v>-89.05</v>
       </c>
       <c r="K51" t="n">
-        <v>37.94</v>
+        <v>46.03</v>
       </c>
       <c r="L51" t="n">
-        <v>82.62</v>
+        <v>100.24</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-84.34999999999999</v>
+        <v>-103.53</v>
       </c>
       <c r="K52" t="n">
-        <v>-73.42</v>
+        <v>-90.12</v>
       </c>
       <c r="L52" t="n">
-        <v>111.82</v>
+        <v>137.26</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>80.44</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>-210.47</v>
+        <v>-248.49</v>
       </c>
       <c r="L53" t="n">
-        <v>225.32</v>
+        <v>266.02</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>62.56</v>
+        <v>71.44</v>
       </c>
       <c r="K54" t="n">
-        <v>239.68</v>
+        <v>273.69</v>
       </c>
       <c r="L54" t="n">
-        <v>247.71</v>
+        <v>282.86</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>60.27</v>
+        <v>77.25</v>
       </c>
       <c r="K55" t="n">
-        <v>-141.16</v>
+        <v>-180.92</v>
       </c>
       <c r="L55" t="n">
-        <v>153.49</v>
+        <v>196.72</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>114.32</v>
+        <v>141.99</v>
       </c>
       <c r="K56" t="n">
-        <v>263.85</v>
+        <v>327.72</v>
       </c>
       <c r="L56" t="n">
-        <v>287.55</v>
+        <v>357.16</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-269</v>
+        <v>-335.38</v>
       </c>
       <c r="K57" t="n">
-        <v>109.86</v>
+        <v>136.97</v>
       </c>
       <c r="L57" t="n">
-        <v>290.57</v>
+        <v>362.27</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-212.11</v>
+        <v>-261.07</v>
       </c>
       <c r="K58" t="n">
-        <v>93.12</v>
+        <v>114.61</v>
       </c>
       <c r="L58" t="n">
-        <v>231.65</v>
+        <v>285.11</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>68.39</v>
+        <v>73.98</v>
       </c>
       <c r="K59" t="n">
-        <v>55.5</v>
+        <v>60.04</v>
       </c>
       <c r="L59" t="n">
-        <v>88.08</v>
+        <v>95.28</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-61.63</v>
+        <v>-68.95999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>18.22</v>
+        <v>20.39</v>
       </c>
       <c r="L60" t="n">
-        <v>64.27</v>
+        <v>71.91</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>52.15</v>
+        <v>61.99</v>
       </c>
       <c r="K61" t="n">
-        <v>-17.75</v>
+        <v>-21.1</v>
       </c>
       <c r="L61" t="n">
-        <v>55.09</v>
+        <v>65.48</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-49.12</v>
+        <v>-58.51</v>
       </c>
       <c r="K62" t="n">
-        <v>56.22</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>74.65000000000001</v>
+        <v>88.92</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>70.47</v>
+        <v>77.59</v>
       </c>
       <c r="K63" t="n">
-        <v>73.3</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>101.68</v>
+        <v>111.96</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-30.23</v>
+        <v>-37.83</v>
       </c>
       <c r="K64" t="n">
-        <v>51.4</v>
+        <v>64.33</v>
       </c>
       <c r="L64" t="n">
-        <v>59.63</v>
+        <v>74.63</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>-31.61</v>
+        <v>-39.12</v>
       </c>
       <c r="K65" t="n">
-        <v>-124.28</v>
+        <v>-153.79</v>
       </c>
       <c r="L65" t="n">
-        <v>128.24</v>
+        <v>158.69</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-99.14</v>
+        <v>-114.85</v>
       </c>
       <c r="K66" t="n">
-        <v>84.05</v>
+        <v>97.37</v>
       </c>
       <c r="L66" t="n">
-        <v>129.98</v>
+        <v>150.57</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>124.75</v>
+        <v>145.38</v>
       </c>
       <c r="K67" t="n">
-        <v>-31.49</v>
+        <v>-36.69</v>
       </c>
       <c r="L67" t="n">
-        <v>128.66</v>
+        <v>149.94</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-8.279999999999999</v>
+        <v>-9.67</v>
       </c>
       <c r="K68" t="n">
-        <v>214.85</v>
+        <v>250.77</v>
       </c>
       <c r="L68" t="n">
-        <v>215.01</v>
+        <v>250.96</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>157.52</v>
+        <v>199.94</v>
       </c>
       <c r="K69" t="n">
-        <v>-13.28</v>
+        <v>-16.85</v>
       </c>
       <c r="L69" t="n">
-        <v>158.08</v>
+        <v>200.65</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>3.81</v>
+        <v>4.35</v>
       </c>
       <c r="K70" t="n">
-        <v>-219.43</v>
+        <v>-250.91</v>
       </c>
       <c r="L70" t="n">
-        <v>219.46</v>
+        <v>250.95</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>181.84</v>
+        <v>247.99</v>
       </c>
       <c r="K71" t="n">
-        <v>-16.26</v>
+        <v>-22.18</v>
       </c>
       <c r="L71" t="n">
-        <v>182.56</v>
+        <v>248.98</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>52.5</v>
+        <v>70.89</v>
       </c>
       <c r="K72" t="n">
-        <v>-211.91</v>
+        <v>-286.14</v>
       </c>
       <c r="L72" t="n">
-        <v>218.32</v>
+        <v>294.79</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>125.06</v>
+        <v>157.03</v>
       </c>
       <c r="K73" t="n">
-        <v>-216.49</v>
+        <v>-271.84</v>
       </c>
       <c r="L73" t="n">
-        <v>250.01</v>
+        <v>313.93</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>-93.72</v>
+        <v>-100.55</v>
       </c>
       <c r="K74" t="n">
-        <v>-3.06</v>
+        <v>-3.28</v>
       </c>
       <c r="L74" t="n">
-        <v>93.77</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>18.08</v>
+        <v>21.55</v>
       </c>
       <c r="K75" t="n">
-        <v>-63.19</v>
+        <v>-75.31999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>65.73</v>
+        <v>78.34</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-21.48</v>
+        <v>-26.3</v>
       </c>
       <c r="K76" t="n">
-        <v>-54.98</v>
+        <v>-67.3</v>
       </c>
       <c r="L76" t="n">
-        <v>59.03</v>
+        <v>72.26000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>60.7</v>
+        <v>67.52</v>
       </c>
       <c r="K77" t="n">
-        <v>-74.53</v>
+        <v>-82.91</v>
       </c>
       <c r="L77" t="n">
-        <v>96.12</v>
+        <v>106.92</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-23.92</v>
+        <v>-28.94</v>
       </c>
       <c r="K78" t="n">
-        <v>79.90000000000001</v>
+        <v>96.67</v>
       </c>
       <c r="L78" t="n">
-        <v>83.40000000000001</v>
+        <v>100.91</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>24.15</v>
+        <v>26.78</v>
       </c>
       <c r="K79" t="n">
-        <v>-93.20999999999999</v>
+        <v>-103.35</v>
       </c>
       <c r="L79" t="n">
-        <v>96.28</v>
+        <v>106.77</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>84.17</v>
+        <v>101.61</v>
       </c>
       <c r="K80" t="n">
-        <v>76.22</v>
+        <v>92.02</v>
       </c>
       <c r="L80" t="n">
-        <v>113.55</v>
+        <v>137.08</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-115.55</v>
+        <v>-138.99</v>
       </c>
       <c r="K81" t="n">
-        <v>8.02</v>
+        <v>9.65</v>
       </c>
       <c r="L81" t="n">
-        <v>115.83</v>
+        <v>139.33</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-125.13</v>
+        <v>-144.83</v>
       </c>
       <c r="K82" t="n">
-        <v>-118.74</v>
+        <v>-137.44</v>
       </c>
       <c r="L82" t="n">
-        <v>172.5</v>
+        <v>199.66</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-137.17</v>
+        <v>-179.52</v>
       </c>
       <c r="K83" t="n">
-        <v>-50.72</v>
+        <v>-66.37</v>
       </c>
       <c r="L83" t="n">
-        <v>146.25</v>
+        <v>191.39</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-161.49</v>
+        <v>-196.44</v>
       </c>
       <c r="K84" t="n">
-        <v>-33.78</v>
+        <v>-41.08</v>
       </c>
       <c r="L84" t="n">
-        <v>164.99</v>
+        <v>200.69</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.83</v>
+        <v>-6.14</v>
       </c>
       <c r="K85" t="n">
-        <v>162.25</v>
+        <v>206.3</v>
       </c>
       <c r="L85" t="n">
-        <v>162.32</v>
+        <v>206.39</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-72.01000000000001</v>
+        <v>-100.6</v>
       </c>
       <c r="K86" t="n">
-        <v>-200.88</v>
+        <v>-280.61</v>
       </c>
       <c r="L86" t="n">
-        <v>213.4</v>
+        <v>298.1</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-306.27</v>
+        <v>-387.59</v>
       </c>
       <c r="K87" t="n">
-        <v>25.79</v>
+        <v>32.64</v>
       </c>
       <c r="L87" t="n">
-        <v>307.36</v>
+        <v>388.96</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>152.85</v>
+        <v>181.51</v>
       </c>
       <c r="K88" t="n">
-        <v>-333.67</v>
+        <v>-396.24</v>
       </c>
       <c r="L88" t="n">
-        <v>367.01</v>
+        <v>435.84</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-02.xlsx
+++ b/output/2024-04-02.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>11.67</v>
+        <v>12.87</v>
       </c>
       <c r="K14" t="n">
-        <v>68.79000000000001</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>69.77</v>
+        <v>76.93000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>-29.98</v>
+        <v>-30.04</v>
       </c>
       <c r="K15" t="n">
-        <v>59.54</v>
+        <v>59.66</v>
       </c>
       <c r="L15" t="n">
-        <v>66.67</v>
+        <v>66.79000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>-76.75</v>
+        <v>-78.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="L16" t="n">
-        <v>76.78</v>
+        <v>78.54000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-13.4</v>
+        <v>-14.13</v>
       </c>
       <c r="K29" t="n">
-        <v>89.34</v>
+        <v>94.2</v>
       </c>
       <c r="L29" t="n">
-        <v>90.33</v>
+        <v>95.25</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>84.25</v>
+        <v>86.77</v>
       </c>
       <c r="K30" t="n">
-        <v>-11.34</v>
+        <v>-11.68</v>
       </c>
       <c r="L30" t="n">
-        <v>85.01000000000001</v>
+        <v>87.55</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-96.31</v>
+        <v>-107.48</v>
       </c>
       <c r="K31" t="n">
-        <v>-27.47</v>
+        <v>-30.66</v>
       </c>
       <c r="L31" t="n">
-        <v>100.16</v>
+        <v>111.77</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>17.14</v>
+        <v>17.64</v>
       </c>
       <c r="K32" t="n">
-        <v>81.15000000000001</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>82.94</v>
+        <v>85.36</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-85.90000000000001</v>
+        <v>-89.36</v>
       </c>
       <c r="K33" t="n">
-        <v>-74.84</v>
+        <v>-77.84999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>113.92</v>
+        <v>118.51</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>102.41</v>
+        <v>104.08</v>
       </c>
       <c r="K34" t="n">
-        <v>-25.27</v>
+        <v>-25.69</v>
       </c>
       <c r="L34" t="n">
-        <v>105.48</v>
+        <v>107.2</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-70.92</v>
+        <v>-73.95</v>
       </c>
       <c r="K44" t="n">
-        <v>25.26</v>
+        <v>26.34</v>
       </c>
       <c r="L44" t="n">
-        <v>75.28</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>7.99</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>63.57</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>64.06999999999999</v>
+        <v>65.87</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>32.77</v>
+        <v>34.23</v>
       </c>
       <c r="K46" t="n">
-        <v>82.45999999999999</v>
+        <v>86.14</v>
       </c>
       <c r="L46" t="n">
-        <v>88.73</v>
+        <v>92.69</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>67.58</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>-47.72</v>
+        <v>-53.5</v>
       </c>
       <c r="L47" t="n">
-        <v>82.73</v>
+        <v>92.73999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>-90.95999999999999</v>
+        <v>-100.89</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.78</v>
+        <v>-5.3</v>
       </c>
       <c r="L48" t="n">
-        <v>91.09</v>
+        <v>101.03</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>56.68</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>-107.06</v>
+        <v>-123.18</v>
       </c>
       <c r="L49" t="n">
-        <v>121.14</v>
+        <v>139.37</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>73.98</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>60.04</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>95.28</v>
+        <v>107.41</v>
       </c>
     </row>
     <row r="60">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>61.99</v>
+        <v>64.87</v>
       </c>
       <c r="K61" t="n">
-        <v>-21.1</v>
+        <v>-22.08</v>
       </c>
       <c r="L61" t="n">
-        <v>65.48</v>
+        <v>68.53</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-58.51</v>
+        <v>-64.5</v>
       </c>
       <c r="K62" t="n">
-        <v>66.95999999999999</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>88.92</v>
+        <v>98.03</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>77.59</v>
+        <v>84.39</v>
       </c>
       <c r="K63" t="n">
-        <v>80.70999999999999</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>111.96</v>
+        <v>121.77</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-37.83</v>
+        <v>-39.3</v>
       </c>
       <c r="K64" t="n">
-        <v>64.33</v>
+        <v>66.83</v>
       </c>
       <c r="L64" t="n">
-        <v>74.63</v>
+        <v>77.53</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>-100.55</v>
+        <v>-109.56</v>
       </c>
       <c r="K74" t="n">
-        <v>-3.28</v>
+        <v>-3.57</v>
       </c>
       <c r="L74" t="n">
-        <v>100.6</v>
+        <v>109.62</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>21.55</v>
+        <v>27.4</v>
       </c>
       <c r="K75" t="n">
-        <v>-75.31999999999999</v>
+        <v>-95.77</v>
       </c>
       <c r="L75" t="n">
-        <v>78.34</v>
+        <v>99.62</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-26.3</v>
+        <v>-32.1</v>
       </c>
       <c r="K76" t="n">
-        <v>-67.3</v>
+        <v>-82.16</v>
       </c>
       <c r="L76" t="n">
-        <v>72.26000000000001</v>
+        <v>88.20999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>67.52</v>
+        <v>77.56</v>
       </c>
       <c r="K77" t="n">
-        <v>-82.91</v>
+        <v>-95.23999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>106.92</v>
+        <v>122.83</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-28.94</v>
+        <v>-34.72</v>
       </c>
       <c r="K78" t="n">
-        <v>96.67</v>
+        <v>115.95</v>
       </c>
       <c r="L78" t="n">
-        <v>100.91</v>
+        <v>121.04</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>26.78</v>
+        <v>29.66</v>
       </c>
       <c r="K79" t="n">
-        <v>-103.35</v>
+        <v>-114.46</v>
       </c>
       <c r="L79" t="n">
-        <v>106.77</v>
+        <v>118.24</v>
       </c>
     </row>
     <row r="80">
